--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="326">
   <si>
     <t>IDSocio</t>
   </si>
@@ -109,37 +109,61 @@
     <t>338639</t>
   </si>
   <si>
+    <t>340367</t>
+  </si>
+  <si>
     <t>338638</t>
   </si>
   <si>
-    <t>340367</t>
-  </si>
-  <si>
     <t>340192</t>
   </si>
   <si>
     <t>340280</t>
   </si>
   <si>
+    <t>342419</t>
+  </si>
+  <si>
+    <t>342533</t>
+  </si>
+  <si>
     <t>340790</t>
   </si>
   <si>
+    <t>342724</t>
+  </si>
+  <si>
+    <t>342360</t>
+  </si>
+  <si>
+    <t>344364</t>
+  </si>
+  <si>
+    <t>344054</t>
+  </si>
+  <si>
+    <t>343355</t>
+  </si>
+  <si>
     <t>341963</t>
   </si>
   <si>
-    <t>342360</t>
-  </si>
-  <si>
-    <t>342419</t>
-  </si>
-  <si>
-    <t>342533</t>
-  </si>
-  <si>
-    <t>342724</t>
-  </si>
-  <si>
-    <t>343355</t>
+    <t>344359</t>
+  </si>
+  <si>
+    <t>344489</t>
+  </si>
+  <si>
+    <t>344557</t>
+  </si>
+  <si>
+    <t>344573</t>
+  </si>
+  <si>
+    <t>344016</t>
+  </si>
+  <si>
+    <t>344493</t>
   </si>
   <si>
     <t>45975</t>
@@ -148,37 +172,61 @@
     <t>16457</t>
   </si>
   <si>
+    <t>18185</t>
+  </si>
+  <si>
     <t>16456</t>
   </si>
   <si>
-    <t>18185</t>
-  </si>
-  <si>
     <t>18010</t>
   </si>
   <si>
     <t>18098</t>
   </si>
   <si>
+    <t>20237</t>
+  </si>
+  <si>
+    <t>20350</t>
+  </si>
+  <si>
     <t>18608</t>
   </si>
   <si>
+    <t>20541</t>
+  </si>
+  <si>
+    <t>20178</t>
+  </si>
+  <si>
+    <t>22181</t>
+  </si>
+  <si>
+    <t>21871</t>
+  </si>
+  <si>
+    <t>21172</t>
+  </si>
+  <si>
     <t>19781</t>
   </si>
   <si>
-    <t>20178</t>
-  </si>
-  <si>
-    <t>20237</t>
-  </si>
-  <si>
-    <t>20350</t>
-  </si>
-  <si>
-    <t>20541</t>
-  </si>
-  <si>
-    <t>21172</t>
+    <t>22176</t>
+  </si>
+  <si>
+    <t>22306</t>
+  </si>
+  <si>
+    <t>22374</t>
+  </si>
+  <si>
+    <t>22390</t>
+  </si>
+  <si>
+    <t>21833</t>
+  </si>
+  <si>
+    <t>22310</t>
   </si>
   <si>
     <t>LOMA BONITA</t>
@@ -190,37 +238,61 @@
     <t>PAMELA</t>
   </si>
   <si>
+    <t xml:space="preserve">JUANA CLAUDIA </t>
+  </si>
+  <si>
     <t>ALMA LORENA</t>
   </si>
   <si>
-    <t xml:space="preserve">JUANA CLAUDIA </t>
-  </si>
-  <si>
     <t>BRANDON</t>
   </si>
   <si>
     <t>ROSA VALERIA</t>
   </si>
   <si>
+    <t xml:space="preserve">IVIS MARLEN </t>
+  </si>
+  <si>
+    <t>MARIBEL</t>
+  </si>
+  <si>
     <t xml:space="preserve">DANIA </t>
   </si>
   <si>
+    <t>JUAN JOSE</t>
+  </si>
+  <si>
+    <t>MARIA DEL ROCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIA </t>
+  </si>
+  <si>
+    <t>SANDRA LETICIA</t>
+  </si>
+  <si>
+    <t>ROBERTO TRINIDAD</t>
+  </si>
+  <si>
     <t xml:space="preserve">LUZ DEL CARMEN </t>
   </si>
   <si>
-    <t>MARIA DEL ROCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVIS MARLEN </t>
-  </si>
-  <si>
-    <t>MARIBEL</t>
-  </si>
-  <si>
-    <t>JUAN JOSE</t>
-  </si>
-  <si>
-    <t>ROBERTO TRINIDAD</t>
+    <t xml:space="preserve">ANTONIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHAEL </t>
+  </si>
+  <si>
+    <t>MARIO ALBERTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERONICA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA KAREN </t>
+  </si>
+  <si>
+    <t>BIRIDIANA</t>
   </si>
   <si>
     <t>CABAÑAS</t>
@@ -229,34 +301,58 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>CAMACENA</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>CAMACENA</t>
-  </si>
-  <si>
     <t>SILVA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>ROCHIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GALVAN </t>
+  </si>
+  <si>
     <t>APODACA</t>
   </si>
   <si>
+    <t>DUEÑAS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTRERAS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUAREZ </t>
+  </si>
+  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>ROCHIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GALVAN </t>
-  </si>
-  <si>
-    <t>DUEÑAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUAREZ </t>
+    <t xml:space="preserve">FLORES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROJAS </t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALCIDO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOSA </t>
   </si>
   <si>
     <t>CARDENAS</t>
@@ -265,37 +361,58 @@
     <t>VALDEZ</t>
   </si>
   <si>
+    <t>GRACIDA</t>
+  </si>
+  <si>
     <t>GOVEA</t>
   </si>
   <si>
-    <t>GRACIDA</t>
-  </si>
-  <si>
     <t>DELGADILLO</t>
   </si>
   <si>
     <t>PORTILLO</t>
   </si>
   <si>
+    <t>SAUCEDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUILAR </t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DE SANTIAGO </t>
+  </si>
+  <si>
+    <t>ABARCA</t>
+  </si>
+  <si>
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>SAUCEDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGUILAR </t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>ABARCA</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENTERIA </t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>ARAOS</t>
+  </si>
+  <si>
+    <t>MAGAÑA</t>
+  </si>
+  <si>
+    <t>MONJARAZ</t>
   </si>
   <si>
     <t>52</t>
@@ -310,37 +427,61 @@
     <t>6644409651</t>
   </si>
   <si>
+    <t>2285111160</t>
+  </si>
+  <si>
     <t>6645112535</t>
   </si>
   <si>
-    <t>2285111160</t>
-  </si>
-  <si>
     <t>6198156515</t>
   </si>
   <si>
     <t>6642708866</t>
   </si>
   <si>
+    <t>6642338869</t>
+  </si>
+  <si>
+    <t>6645692934</t>
+  </si>
+  <si>
     <t>6645530549</t>
   </si>
   <si>
+    <t>6633343468</t>
+  </si>
+  <si>
+    <t>6631107103</t>
+  </si>
+  <si>
+    <t>6647006311</t>
+  </si>
+  <si>
+    <t>6634313589</t>
+  </si>
+  <si>
+    <t>6634586390</t>
+  </si>
+  <si>
     <t>6644151535</t>
   </si>
   <si>
-    <t>6631107103</t>
-  </si>
-  <si>
-    <t>6642338869</t>
-  </si>
-  <si>
-    <t>6645692934</t>
-  </si>
-  <si>
-    <t>6633343468</t>
-  </si>
-  <si>
-    <t>6634586390</t>
+    <t>6644048868</t>
+  </si>
+  <si>
+    <t>6648567901</t>
+  </si>
+  <si>
+    <t>6646691008</t>
+  </si>
+  <si>
+    <t>6612034182</t>
+  </si>
+  <si>
+    <t>6646105596</t>
+  </si>
+  <si>
+    <t>6632474982</t>
   </si>
   <si>
     <t xml:space="preserve">NUEVA AURORA </t>
@@ -349,22 +490,43 @@
     <t>ESTRELLA DEL ORIENTE</t>
   </si>
   <si>
+    <t>AV DEL RUBI</t>
+  </si>
+  <si>
     <t>AV CAN MAYOR</t>
   </si>
   <si>
+    <t>GARDEN 24241</t>
+  </si>
+  <si>
+    <t>PRIV GARDENIA</t>
+  </si>
+  <si>
+    <t>FRANCISCO VILLA 5011</t>
+  </si>
+  <si>
+    <t>EMILIANO ZAPATA</t>
+  </si>
+  <si>
     <t>MONTE TRES PICOS</t>
   </si>
   <si>
-    <t>PRIV GARDENIA</t>
-  </si>
-  <si>
-    <t>AV DEL RUBI</t>
-  </si>
-  <si>
-    <t>GARDEN 24241</t>
-  </si>
-  <si>
-    <t>EMILIANO ZAPATA</t>
+    <t>FRANCISCO VILLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOMA BONITA </t>
+  </si>
+  <si>
+    <t>FELIX PARRA 203</t>
+  </si>
+  <si>
+    <t>MIGUEL ROMERO 6012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANAMERICANO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAS CUMBRES </t>
   </si>
   <si>
     <t>Masculino</t>
@@ -379,37 +541,61 @@
     <t>26-07-1998</t>
   </si>
   <si>
+    <t>22-06-1977</t>
+  </si>
+  <si>
     <t>15-10-1994</t>
   </si>
   <si>
-    <t>22-06-1977</t>
-  </si>
-  <si>
     <t>01-08-2010</t>
   </si>
   <si>
     <t>02-05-1997</t>
   </si>
   <si>
+    <t>03-11-1994</t>
+  </si>
+  <si>
+    <t>24-01-2001</t>
+  </si>
+  <si>
     <t>25-08-2020</t>
   </si>
   <si>
+    <t>09-12-1997</t>
+  </si>
+  <si>
+    <t>24-01-1985</t>
+  </si>
+  <si>
+    <t>26-02-1977</t>
+  </si>
+  <si>
+    <t>04-05-2004</t>
+  </si>
+  <si>
+    <t>18-08-1985</t>
+  </si>
+  <si>
     <t>28-12-1983</t>
   </si>
   <si>
-    <t>24-01-1985</t>
-  </si>
-  <si>
-    <t>03-11-1994</t>
-  </si>
-  <si>
-    <t>24-01-2001</t>
-  </si>
-  <si>
-    <t>09-12-1997</t>
-  </si>
-  <si>
-    <t>18-08-1985</t>
+    <t>14-07-1967</t>
+  </si>
+  <si>
+    <t>12-04-2006</t>
+  </si>
+  <si>
+    <t>22-10-2000</t>
+  </si>
+  <si>
+    <t>20-08-2000</t>
+  </si>
+  <si>
+    <t>26-06-1993</t>
+  </si>
+  <si>
+    <t>20-03-2006</t>
   </si>
   <si>
     <t>AXELCARDENASCA@GMAIL.COM</t>
@@ -418,37 +604,61 @@
     <t>GHFTGDC@GMAIL.COM</t>
   </si>
   <si>
+    <t>CAMACENAJUANA5@GMAIL.COM</t>
+  </si>
+  <si>
     <t>HJJJJJJJJ@GMAIL.COM</t>
   </si>
   <si>
-    <t>CAMACENAJUANA5@GMAIL.COM</t>
-  </si>
-  <si>
     <t>BRANDONSILVA244@GMAIL.COM</t>
   </si>
   <si>
     <t>VALERIA_ROGERS@LIVE.COM</t>
   </si>
   <si>
+    <t>IROCHINSAUCEDO@ICLOUD.COM</t>
+  </si>
+  <si>
+    <t>MARELGALVAN53@GMAIL.COM</t>
+  </si>
+  <si>
     <t>DANIADRAWS@GMAIL.COM</t>
   </si>
   <si>
+    <t>JUANJOSEDUENAS85@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CESARIO_GARCIA@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>SHAPIS277@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CONTRERASSANDRA149@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ROBERTODALIA9852@GMAIL.COM</t>
+  </si>
+  <si>
     <t>LUZ28DOMI@GMAIL.COM</t>
   </si>
   <si>
-    <t>CESARIO_GARCIA@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>IROCHINSAUCEDO@ICLOUD.COM</t>
-  </si>
-  <si>
-    <t>MARELGALVAN53@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>JUANJOSEDUENAS85@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ROBERTODALIA9852@GMAIL.COM</t>
+    <t>ZAPATALABFACTURAS@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>MACHAELRENTERIAROJAS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MARIO.SOTO1403@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>PEREZVERONICA1204@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ANAMAGAÑA371@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>LOSAMONJARAZBIRIDIANA06@GMAIL.COM</t>
   </si>
   <si>
     <t>27-07-2024 08:36:55</t>
@@ -457,42 +667,69 @@
     <t>28-01-2026 08:38:36</t>
   </si>
   <si>
+    <t>02-02-2026 19:31:33</t>
+  </si>
+  <si>
     <t>28-01-2026 08:38:30</t>
   </si>
   <si>
-    <t>02-02-2026 19:31:33</t>
-  </si>
-  <si>
     <t>02-02-2026 14:49:52</t>
   </si>
   <si>
     <t>02-02-2026 16:40:54</t>
   </si>
   <si>
+    <t>09-02-2026 19:02:55</t>
+  </si>
+  <si>
+    <t>10-02-2026 07:33:18</t>
+  </si>
+  <si>
     <t>03-02-2026 18:47:07</t>
   </si>
   <si>
+    <t>10-02-2026 16:51:42</t>
+  </si>
+  <si>
+    <t>09-02-2026 17:54:42</t>
+  </si>
+  <si>
+    <t>16-02-2026 21:48:29</t>
+  </si>
+  <si>
+    <t>16-02-2026 12:48:08</t>
+  </si>
+  <si>
+    <t>12-02-2026 17:57:31</t>
+  </si>
+  <si>
     <t>08-02-2026 15:03:16</t>
   </si>
   <si>
-    <t>09-02-2026 17:54:42</t>
-  </si>
-  <si>
-    <t>09-02-2026 19:02:55</t>
-  </si>
-  <si>
-    <t>10-02-2026 07:33:18</t>
-  </si>
-  <si>
-    <t>10-02-2026 16:51:42</t>
-  </si>
-  <si>
-    <t>12-02-2026 17:57:31</t>
+    <t>16-02-2026 20:52:22</t>
+  </si>
+  <si>
+    <t>17-02-2026 13:55:21</t>
+  </si>
+  <si>
+    <t>17-02-2026 16:14:15</t>
+  </si>
+  <si>
+    <t>17-02-2026 16:35:43</t>
+  </si>
+  <si>
+    <t>16-02-2026 11:21:32</t>
+  </si>
+  <si>
+    <t>17-02-2026 14:01:11</t>
   </si>
   <si>
     <t>Tarifas 2026 LE</t>
   </si>
   <si>
+    <t>inscripcion promo 199</t>
+  </si>
+  <si>
     <t>Sin contrato</t>
   </si>
   <si>
@@ -505,12 +742,12 @@
     <t>PROMO FEBRERO 12 MESES</t>
   </si>
   <si>
+    <t>3 MESES $1,899</t>
+  </si>
+  <si>
     <t>PLAN FAMILIA / AMIGOS X $499</t>
   </si>
   <si>
-    <t>3 MESES $1,899</t>
-  </si>
-  <si>
     <t>COBACH $399</t>
   </si>
   <si>
@@ -532,37 +769,61 @@
     <t>12-02-2026 09:13:35</t>
   </si>
   <si>
+    <t>02-02-2026 19:39:24</t>
+  </si>
+  <si>
     <t>09-02-2026 08:42:24</t>
   </si>
   <si>
-    <t>02-02-2026 19:39:24</t>
-  </si>
-  <si>
     <t>04-02-2026 09:59:45</t>
   </si>
   <si>
     <t>02-02-2026 16:49:59</t>
   </si>
   <si>
+    <t>09-02-2026 19:11:27</t>
+  </si>
+  <si>
+    <t>10-02-2026 07:41:17</t>
+  </si>
+  <si>
     <t>03-02-2026 18:56:39</t>
   </si>
   <si>
+    <t>10-02-2026 16:59:24</t>
+  </si>
+  <si>
+    <t>09-02-2026 18:02:59</t>
+  </si>
+  <si>
+    <t>16-02-2026 21:57:08</t>
+  </si>
+  <si>
+    <t>16-02-2026 12:49:38</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:06:53</t>
+  </si>
+  <si>
     <t>08-02-2026 15:10:44</t>
   </si>
   <si>
-    <t>09-02-2026 18:02:59</t>
-  </si>
-  <si>
-    <t>09-02-2026 19:11:27</t>
-  </si>
-  <si>
-    <t>10-02-2026 07:41:17</t>
-  </si>
-  <si>
-    <t>10-02-2026 16:59:24</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:06:53</t>
+    <t>16-02-2026 21:13:15</t>
+  </si>
+  <si>
+    <t>17-02-2026 13:58:26</t>
+  </si>
+  <si>
+    <t>17-02-2026 16:29:22</t>
+  </si>
+  <si>
+    <t>17-02-2026 16:58:54</t>
+  </si>
+  <si>
+    <t>16-02-2026 11:27:59</t>
+  </si>
+  <si>
+    <t>17-02-2026 14:06:09</t>
   </si>
   <si>
     <t>09-03-2026 23:59:59</t>
@@ -580,13 +841,19 @@
     <t>02-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>10-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>03-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>16-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>08-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>10-03-2026 23:59:59</t>
+    <t>17-03-2026 23:59:59</t>
   </si>
   <si>
     <t>12-02-2026 09:13:05</t>
@@ -598,25 +865,46 @@
     <t>02-02-2026 16:48:59</t>
   </si>
   <si>
+    <t>09-02-2026 19:10:03</t>
+  </si>
+  <si>
+    <t>10-02-2026 07:37:20</t>
+  </si>
+  <si>
     <t>03-02-2026 18:54:43</t>
   </si>
   <si>
+    <t>10-02-2026 16:58:12</t>
+  </si>
+  <si>
+    <t>09-02-2026 18:01:06</t>
+  </si>
+  <si>
+    <t>16-02-2026 21:55:56</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:05:12</t>
+  </si>
+  <si>
     <t>08-02-2026 15:08:28</t>
   </si>
   <si>
-    <t>09-02-2026 18:01:06</t>
-  </si>
-  <si>
-    <t>09-02-2026 19:10:03</t>
-  </si>
-  <si>
-    <t>10-02-2026 07:37:20</t>
-  </si>
-  <si>
-    <t>10-02-2026 16:58:12</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:05:12</t>
+    <t>16-02-2026 21:11:12</t>
+  </si>
+  <si>
+    <t>17-02-2026 13:57:43</t>
+  </si>
+  <si>
+    <t>17-02-2026 16:25:31</t>
+  </si>
+  <si>
+    <t>17-02-2026 16:58:10</t>
+  </si>
+  <si>
+    <t>16-02-2026 11:26:40</t>
+  </si>
+  <si>
+    <t>17-02-2026 14:04:10</t>
   </si>
   <si>
     <t>2</t>
@@ -628,37 +916,61 @@
     <t>26140522289900001357</t>
   </si>
   <si>
+    <t>26140522022420001008</t>
+  </si>
+  <si>
     <t>26140522185240001204</t>
   </si>
   <si>
-    <t>26140522022420001008</t>
-  </si>
-  <si>
     <t>26140522071170001067</t>
   </si>
   <si>
     <t>26140522017370000999</t>
   </si>
   <si>
+    <t>26140522209920001244</t>
+  </si>
+  <si>
+    <t>26140522224470001260</t>
+  </si>
+  <si>
     <t>26140522054580001049</t>
   </si>
   <si>
+    <t>26140522238120001282</t>
+  </si>
+  <si>
+    <t>26140522205100001233</t>
+  </si>
+  <si>
+    <t>26140522411860001500</t>
+  </si>
+  <si>
+    <t>26140522387570001473</t>
+  </si>
+  <si>
+    <t>26140522301540001381</t>
+  </si>
+  <si>
     <t>26140522173200001196</t>
   </si>
   <si>
-    <t>26140522205100001233</t>
-  </si>
-  <si>
-    <t>26140522209920001244</t>
-  </si>
-  <si>
-    <t>26140522224470001260</t>
-  </si>
-  <si>
-    <t>26140522238120001282</t>
-  </si>
-  <si>
-    <t>26140522301540001381</t>
+    <t>26140522411330001499</t>
+  </si>
+  <si>
+    <t>26140522428560001519</t>
+  </si>
+  <si>
+    <t>26140522434170001526</t>
+  </si>
+  <si>
+    <t>26140522435860001527</t>
+  </si>
+  <si>
+    <t>26140522385390001470</t>
+  </si>
+  <si>
+    <t>26140522428740001520</t>
   </si>
   <si>
     <t>PASE 2 DÍAS GRATIS WEB</t>
@@ -1037,7 +1349,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -1134,73 +1446,73 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="G2" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H2" t="s">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="J2" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="K2" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="L2" t="s">
-        <v>132</v>
+        <v>194</v>
       </c>
       <c r="M2" t="s">
-        <v>145</v>
+        <v>215</v>
       </c>
       <c r="N2" t="s">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="O2" t="s">
-        <v>159</v>
+        <v>238</v>
       </c>
       <c r="P2" t="s">
-        <v>161</v>
+        <v>240</v>
       </c>
       <c r="Q2" t="s">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="R2" t="s">
-        <v>170</v>
+        <v>249</v>
       </c>
       <c r="S2" t="s">
-        <v>183</v>
+        <v>270</v>
       </c>
       <c r="U2" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="W2" t="s">
         <v>2</v>
       </c>
       <c r="X2" t="s">
-        <v>202</v>
+        <v>298</v>
       </c>
       <c r="AA2" t="s">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="AB2" t="s">
-        <v>217</v>
+        <v>321</v>
       </c>
       <c r="AC2" t="s">
-        <v>220</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -1208,82 +1520,82 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="F3" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="G3" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H3" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="I3" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="K3" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="L3" t="s">
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="M3" t="s">
-        <v>146</v>
+        <v>216</v>
       </c>
       <c r="O3" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="P3" t="s">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="Q3" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="R3" t="s">
-        <v>171</v>
+        <v>250</v>
       </c>
       <c r="S3" t="s">
-        <v>184</v>
+        <v>271</v>
       </c>
       <c r="T3" t="s">
-        <v>191</v>
+        <v>280</v>
       </c>
       <c r="U3" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="V3" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="W3" t="s">
         <v>2</v>
       </c>
       <c r="X3" t="s">
-        <v>203</v>
+        <v>299</v>
       </c>
       <c r="Y3" t="s">
-        <v>215</v>
+        <v>319</v>
       </c>
       <c r="AA3" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="AB3" t="s">
-        <v>217</v>
+        <v>321</v>
       </c>
       <c r="AC3" t="s">
-        <v>220</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -1291,82 +1603,73 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F4" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="G4" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I4" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="J4" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="K4" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="L4" t="s">
+        <v>196</v>
+      </c>
+      <c r="M4" t="s">
+        <v>217</v>
+      </c>
+      <c r="N4" t="s">
+        <v>236</v>
+      </c>
+      <c r="O4" t="s">
+        <v>238</v>
+      </c>
+      <c r="P4" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>247</v>
+      </c>
+      <c r="R4" t="s">
+        <v>251</v>
+      </c>
+      <c r="S4" t="s">
+        <v>272</v>
+      </c>
+      <c r="U4" t="s">
         <v>134</v>
-      </c>
-      <c r="M4" t="s">
-        <v>147</v>
-      </c>
-      <c r="O4" t="s">
-        <v>160</v>
-      </c>
-      <c r="P4" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>167</v>
-      </c>
-      <c r="R4" t="s">
-        <v>172</v>
-      </c>
-      <c r="S4" t="s">
-        <v>183</v>
-      </c>
-      <c r="T4" t="s">
-        <v>192</v>
-      </c>
-      <c r="U4" t="s">
-        <v>201</v>
-      </c>
-      <c r="V4" t="s">
-        <v>95</v>
       </c>
       <c r="W4" t="s">
         <v>2</v>
       </c>
       <c r="X4" t="s">
-        <v>204</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>215</v>
+        <v>300</v>
       </c>
       <c r="AA4" t="s">
-        <v>167</v>
+        <v>320</v>
       </c>
       <c r="AB4" t="s">
-        <v>217</v>
+        <v>322</v>
       </c>
       <c r="AC4" t="s">
-        <v>220</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1374,73 +1677,82 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="G5" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H5" t="s">
-        <v>99</v>
+        <v>138</v>
+      </c>
+      <c r="I5" t="s">
+        <v>156</v>
       </c>
       <c r="J5" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="K5" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="L5" t="s">
-        <v>135</v>
+        <v>197</v>
       </c>
       <c r="M5" t="s">
-        <v>148</v>
-      </c>
-      <c r="N5" t="s">
-        <v>158</v>
+        <v>218</v>
       </c>
       <c r="O5" t="s">
-        <v>159</v>
+        <v>239</v>
       </c>
       <c r="P5" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="Q5" t="s">
-        <v>168</v>
+        <v>246</v>
       </c>
       <c r="R5" t="s">
-        <v>173</v>
+        <v>252</v>
       </c>
       <c r="S5" t="s">
-        <v>185</v>
+        <v>270</v>
+      </c>
+      <c r="T5" t="s">
+        <v>281</v>
       </c>
       <c r="U5" t="s">
-        <v>95</v>
+        <v>297</v>
+      </c>
+      <c r="V5" t="s">
+        <v>134</v>
       </c>
       <c r="W5" t="s">
         <v>2</v>
       </c>
       <c r="X5" t="s">
-        <v>205</v>
+        <v>301</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>319</v>
       </c>
       <c r="AA5" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="AB5" t="s">
-        <v>218</v>
+        <v>321</v>
       </c>
       <c r="AC5" t="s">
-        <v>221</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1448,76 +1760,76 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="G6" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="H6" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="J6" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="K6" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="L6" t="s">
-        <v>136</v>
+        <v>198</v>
       </c>
       <c r="M6" t="s">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="N6" t="s">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="O6" t="s">
-        <v>159</v>
+        <v>238</v>
       </c>
       <c r="P6" t="s">
-        <v>165</v>
+        <v>244</v>
       </c>
       <c r="Q6" t="s">
-        <v>169</v>
+        <v>248</v>
       </c>
       <c r="R6" t="s">
-        <v>174</v>
+        <v>253</v>
       </c>
       <c r="S6" t="s">
-        <v>186</v>
+        <v>273</v>
       </c>
       <c r="U6" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="W6" t="s">
         <v>2</v>
       </c>
       <c r="X6" t="s">
-        <v>206</v>
+        <v>302</v>
       </c>
       <c r="Y6" t="s">
-        <v>215</v>
+        <v>319</v>
       </c>
       <c r="AA6" t="s">
-        <v>169</v>
+        <v>248</v>
       </c>
       <c r="AB6" t="s">
-        <v>218</v>
+        <v>322</v>
       </c>
       <c r="AC6" t="s">
-        <v>221</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1525,79 +1837,79 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="G7" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H7" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="I7" t="s">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="J7" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="K7" t="s">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="L7" t="s">
-        <v>137</v>
+        <v>199</v>
       </c>
       <c r="M7" t="s">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="O7" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="P7" t="s">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="Q7" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="R7" t="s">
-        <v>175</v>
+        <v>254</v>
       </c>
       <c r="S7" t="s">
-        <v>187</v>
+        <v>274</v>
       </c>
       <c r="T7" t="s">
-        <v>193</v>
+        <v>282</v>
       </c>
       <c r="U7" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="V7" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="W7" t="s">
         <v>2</v>
       </c>
       <c r="X7" t="s">
-        <v>207</v>
+        <v>303</v>
       </c>
       <c r="AA7" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="AB7" t="s">
-        <v>218</v>
+        <v>322</v>
       </c>
       <c r="AC7" t="s">
-        <v>221</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1605,79 +1917,79 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="G8" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H8" t="s">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="I8" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="J8" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="K8" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="L8" t="s">
-        <v>138</v>
+        <v>200</v>
       </c>
       <c r="M8" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="O8" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="P8" t="s">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="Q8" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="R8" t="s">
-        <v>176</v>
+        <v>255</v>
       </c>
       <c r="S8" t="s">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="T8" t="s">
-        <v>194</v>
+        <v>283</v>
       </c>
       <c r="U8" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="V8" t="s">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="W8" t="s">
         <v>2</v>
       </c>
       <c r="X8" t="s">
-        <v>208</v>
+        <v>304</v>
       </c>
       <c r="AA8" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="AB8" t="s">
-        <v>219</v>
+        <v>321</v>
       </c>
       <c r="AC8" t="s">
-        <v>221</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1685,79 +1997,79 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="G9" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H9" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="I9" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="J9" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="K9" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="L9" t="s">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="M9" t="s">
-        <v>152</v>
+        <v>222</v>
       </c>
       <c r="O9" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="P9" t="s">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="Q9" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="R9" t="s">
-        <v>177</v>
+        <v>256</v>
       </c>
       <c r="S9" t="s">
-        <v>189</v>
+        <v>275</v>
       </c>
       <c r="T9" t="s">
-        <v>195</v>
+        <v>284</v>
       </c>
       <c r="U9" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="V9" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="W9" t="s">
         <v>2</v>
       </c>
       <c r="X9" t="s">
-        <v>209</v>
+        <v>305</v>
       </c>
       <c r="AA9" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="AB9" t="s">
-        <v>218</v>
+        <v>321</v>
       </c>
       <c r="AC9" t="s">
-        <v>221</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1765,79 +2077,79 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="F10" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="G10" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H10" t="s">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="I10" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="J10" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="K10" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="L10" t="s">
-        <v>140</v>
+        <v>202</v>
       </c>
       <c r="M10" t="s">
-        <v>153</v>
+        <v>223</v>
       </c>
       <c r="O10" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="P10" t="s">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="Q10" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="R10" t="s">
-        <v>178</v>
+        <v>257</v>
       </c>
       <c r="S10" t="s">
-        <v>183</v>
+        <v>276</v>
       </c>
       <c r="T10" t="s">
-        <v>196</v>
+        <v>285</v>
       </c>
       <c r="U10" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="V10" t="s">
-        <v>95</v>
+        <v>297</v>
       </c>
       <c r="W10" t="s">
         <v>2</v>
       </c>
       <c r="X10" t="s">
-        <v>210</v>
+        <v>306</v>
       </c>
       <c r="AA10" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="AB10" t="s">
-        <v>217</v>
+        <v>323</v>
       </c>
       <c r="AC10" t="s">
-        <v>220</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1845,79 +2157,79 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G11" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="I11" t="s">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="J11" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="K11" t="s">
-        <v>128</v>
+        <v>182</v>
       </c>
       <c r="L11" t="s">
-        <v>141</v>
+        <v>203</v>
       </c>
       <c r="M11" t="s">
-        <v>154</v>
+        <v>224</v>
       </c>
       <c r="O11" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="P11" t="s">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="Q11" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="R11" t="s">
-        <v>179</v>
+        <v>258</v>
       </c>
       <c r="S11" t="s">
-        <v>183</v>
+        <v>275</v>
       </c>
       <c r="T11" t="s">
-        <v>197</v>
+        <v>286</v>
       </c>
       <c r="U11" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="V11" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="W11" t="s">
         <v>2</v>
       </c>
       <c r="X11" t="s">
-        <v>211</v>
+        <v>307</v>
       </c>
       <c r="AA11" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="AB11" t="s">
-        <v>217</v>
+        <v>322</v>
       </c>
       <c r="AC11" t="s">
-        <v>220</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1925,79 +2237,79 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="G12" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H12" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="I12" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="J12" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="K12" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="L12" t="s">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="M12" t="s">
-        <v>155</v>
+        <v>225</v>
       </c>
       <c r="O12" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="P12" t="s">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="Q12" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="R12" t="s">
-        <v>180</v>
+        <v>259</v>
       </c>
       <c r="S12" t="s">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="T12" t="s">
-        <v>198</v>
+        <v>287</v>
       </c>
       <c r="U12" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="V12" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="W12" t="s">
         <v>2</v>
       </c>
       <c r="X12" t="s">
-        <v>212</v>
+        <v>308</v>
       </c>
       <c r="AA12" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="AB12" t="s">
-        <v>217</v>
+        <v>321</v>
       </c>
       <c r="AC12" t="s">
-        <v>220</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -2005,79 +2317,82 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H13" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="I13" t="s">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="J13" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="L13" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="M13" t="s">
-        <v>156</v>
+        <v>226</v>
+      </c>
+      <c r="N13" t="s">
+        <v>237</v>
       </c>
       <c r="O13" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="P13" t="s">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="Q13" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="R13" t="s">
-        <v>181</v>
+        <v>260</v>
       </c>
       <c r="S13" t="s">
-        <v>190</v>
+        <v>277</v>
       </c>
       <c r="T13" t="s">
-        <v>199</v>
+        <v>288</v>
       </c>
       <c r="U13" t="s">
-        <v>201</v>
+        <v>297</v>
       </c>
       <c r="V13" t="s">
-        <v>95</v>
+        <v>297</v>
       </c>
       <c r="W13" t="s">
         <v>2</v>
       </c>
       <c r="X13" t="s">
-        <v>213</v>
+        <v>309</v>
       </c>
       <c r="AA13" t="s">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="AB13" t="s">
-        <v>218</v>
+        <v>321</v>
       </c>
       <c r="AC13" t="s">
-        <v>221</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -2085,79 +2400,731 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="G14" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="H14" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="J14" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
       <c r="K14" t="s">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="L14" t="s">
-        <v>144</v>
+        <v>206</v>
       </c>
       <c r="M14" t="s">
-        <v>157</v>
+        <v>227</v>
+      </c>
+      <c r="N14" t="s">
+        <v>236</v>
       </c>
       <c r="O14" t="s">
-        <v>160</v>
+        <v>238</v>
       </c>
       <c r="P14" t="s">
-        <v>162</v>
+        <v>240</v>
       </c>
       <c r="Q14" t="s">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="R14" t="s">
-        <v>182</v>
+        <v>261</v>
       </c>
       <c r="S14" t="s">
-        <v>184</v>
-      </c>
-      <c r="T14" t="s">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="U14" t="s">
-        <v>201</v>
-      </c>
-      <c r="V14" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="W14" t="s">
         <v>2</v>
       </c>
       <c r="X14" t="s">
+        <v>310</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>245</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>321</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G15" t="s">
+        <v>133</v>
+      </c>
+      <c r="H15" t="s">
+        <v>148</v>
+      </c>
+      <c r="I15" t="s">
+        <v>163</v>
+      </c>
+      <c r="J15" t="s">
+        <v>171</v>
+      </c>
+      <c r="K15" t="s">
+        <v>186</v>
+      </c>
+      <c r="L15" t="s">
+        <v>207</v>
+      </c>
+      <c r="M15" t="s">
+        <v>228</v>
+      </c>
+      <c r="O15" t="s">
+        <v>239</v>
+      </c>
+      <c r="P15" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>246</v>
+      </c>
+      <c r="R15" t="s">
+        <v>262</v>
+      </c>
+      <c r="S15" t="s">
+        <v>271</v>
+      </c>
+      <c r="T15" t="s">
+        <v>289</v>
+      </c>
+      <c r="U15" t="s">
+        <v>297</v>
+      </c>
+      <c r="V15" t="s">
+        <v>134</v>
+      </c>
+      <c r="W15" t="s">
+        <v>2</v>
+      </c>
+      <c r="X15" t="s">
+        <v>311</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>321</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" t="s">
+        <v>126</v>
+      </c>
+      <c r="G16" t="s">
+        <v>133</v>
+      </c>
+      <c r="H16" t="s">
+        <v>149</v>
+      </c>
+      <c r="I16" t="s">
+        <v>164</v>
+      </c>
+      <c r="J16" t="s">
+        <v>172</v>
+      </c>
+      <c r="K16" t="s">
+        <v>187</v>
+      </c>
+      <c r="L16" t="s">
+        <v>208</v>
+      </c>
+      <c r="M16" t="s">
+        <v>229</v>
+      </c>
+      <c r="O16" t="s">
+        <v>239</v>
+      </c>
+      <c r="P16" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>246</v>
+      </c>
+      <c r="R16" t="s">
+        <v>263</v>
+      </c>
+      <c r="S16" t="s">
+        <v>278</v>
+      </c>
+      <c r="T16" t="s">
+        <v>290</v>
+      </c>
+      <c r="U16" t="s">
+        <v>297</v>
+      </c>
+      <c r="V16" t="s">
+        <v>134</v>
+      </c>
+      <c r="W16" t="s">
+        <v>2</v>
+      </c>
+      <c r="X16" t="s">
+        <v>312</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>322</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" t="s">
+        <v>133</v>
+      </c>
+      <c r="H17" t="s">
+        <v>150</v>
+      </c>
+      <c r="I17" t="s">
+        <v>165</v>
+      </c>
+      <c r="J17" t="s">
+        <v>171</v>
+      </c>
+      <c r="K17" t="s">
+        <v>188</v>
+      </c>
+      <c r="L17" t="s">
+        <v>209</v>
+      </c>
+      <c r="M17" t="s">
+        <v>230</v>
+      </c>
+      <c r="N17" t="s">
+        <v>237</v>
+      </c>
+      <c r="O17" t="s">
+        <v>239</v>
+      </c>
+      <c r="P17" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>246</v>
+      </c>
+      <c r="R17" t="s">
+        <v>264</v>
+      </c>
+      <c r="S17" t="s">
+        <v>277</v>
+      </c>
+      <c r="T17" t="s">
+        <v>291</v>
+      </c>
+      <c r="U17" t="s">
+        <v>297</v>
+      </c>
+      <c r="V17" t="s">
+        <v>297</v>
+      </c>
+      <c r="W17" t="s">
+        <v>2</v>
+      </c>
+      <c r="X17" t="s">
+        <v>313</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>321</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" t="s">
+        <v>151</v>
+      </c>
+      <c r="I18" t="s">
+        <v>166</v>
+      </c>
+      <c r="J18" t="s">
+        <v>172</v>
+      </c>
+      <c r="K18" t="s">
+        <v>189</v>
+      </c>
+      <c r="L18" t="s">
+        <v>210</v>
+      </c>
+      <c r="M18" t="s">
+        <v>231</v>
+      </c>
+      <c r="N18" t="s">
+        <v>237</v>
+      </c>
+      <c r="O18" t="s">
+        <v>239</v>
+      </c>
+      <c r="P18" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>246</v>
+      </c>
+      <c r="R18" t="s">
+        <v>265</v>
+      </c>
+      <c r="S18" t="s">
+        <v>279</v>
+      </c>
+      <c r="T18" t="s">
+        <v>292</v>
+      </c>
+      <c r="U18" t="s">
+        <v>297</v>
+      </c>
+      <c r="V18" t="s">
+        <v>134</v>
+      </c>
+      <c r="W18" t="s">
+        <v>2</v>
+      </c>
+      <c r="X18" t="s">
+        <v>314</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>322</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29">
+      <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" t="s">
+        <v>133</v>
+      </c>
+      <c r="H19" t="s">
+        <v>152</v>
+      </c>
+      <c r="I19" t="s">
+        <v>167</v>
+      </c>
+      <c r="J19" t="s">
+        <v>171</v>
+      </c>
+      <c r="K19" t="s">
+        <v>190</v>
+      </c>
+      <c r="L19" t="s">
+        <v>211</v>
+      </c>
+      <c r="M19" t="s">
+        <v>232</v>
+      </c>
+      <c r="N19" t="s">
+        <v>237</v>
+      </c>
+      <c r="O19" t="s">
+        <v>239</v>
+      </c>
+      <c r="P19" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>246</v>
+      </c>
+      <c r="R19" t="s">
+        <v>266</v>
+      </c>
+      <c r="S19" t="s">
+        <v>279</v>
+      </c>
+      <c r="T19" t="s">
+        <v>293</v>
+      </c>
+      <c r="U19" t="s">
+        <v>297</v>
+      </c>
+      <c r="V19" t="s">
+        <v>134</v>
+      </c>
+      <c r="W19" t="s">
+        <v>2</v>
+      </c>
+      <c r="X19" t="s">
+        <v>315</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>321</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>90</v>
+      </c>
+      <c r="E20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" t="s">
+        <v>133</v>
+      </c>
+      <c r="H20" t="s">
+        <v>153</v>
+      </c>
+      <c r="I20" t="s">
+        <v>168</v>
+      </c>
+      <c r="J20" t="s">
+        <v>172</v>
+      </c>
+      <c r="K20" t="s">
+        <v>191</v>
+      </c>
+      <c r="L20" t="s">
+        <v>212</v>
+      </c>
+      <c r="M20" t="s">
+        <v>233</v>
+      </c>
+      <c r="N20" t="s">
+        <v>237</v>
+      </c>
+      <c r="O20" t="s">
+        <v>239</v>
+      </c>
+      <c r="P20" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>246</v>
+      </c>
+      <c r="R20" t="s">
+        <v>267</v>
+      </c>
+      <c r="S20" t="s">
+        <v>279</v>
+      </c>
+      <c r="T20" t="s">
+        <v>294</v>
+      </c>
+      <c r="U20" t="s">
+        <v>297</v>
+      </c>
+      <c r="V20" t="s">
+        <v>134</v>
+      </c>
+      <c r="W20" t="s">
+        <v>2</v>
+      </c>
+      <c r="X20" t="s">
+        <v>316</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>321</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" t="s">
+        <v>133</v>
+      </c>
+      <c r="H21" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" t="s">
+        <v>169</v>
+      </c>
+      <c r="J21" t="s">
+        <v>172</v>
+      </c>
+      <c r="K21" t="s">
+        <v>192</v>
+      </c>
+      <c r="L21" t="s">
+        <v>213</v>
+      </c>
+      <c r="M21" t="s">
+        <v>234</v>
+      </c>
+      <c r="N21" t="s">
+        <v>237</v>
+      </c>
+      <c r="O21" t="s">
+        <v>239</v>
+      </c>
+      <c r="P21" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>246</v>
+      </c>
+      <c r="R21" t="s">
+        <v>268</v>
+      </c>
+      <c r="S21" t="s">
+        <v>277</v>
+      </c>
+      <c r="T21" t="s">
+        <v>295</v>
+      </c>
+      <c r="U21" t="s">
+        <v>297</v>
+      </c>
+      <c r="V21" t="s">
+        <v>134</v>
+      </c>
+      <c r="W21" t="s">
+        <v>2</v>
+      </c>
+      <c r="X21" t="s">
+        <v>317</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>321</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" t="s">
+        <v>112</v>
+      </c>
+      <c r="F22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22" t="s">
+        <v>133</v>
+      </c>
+      <c r="H22" t="s">
+        <v>155</v>
+      </c>
+      <c r="I22" t="s">
+        <v>170</v>
+      </c>
+      <c r="J22" t="s">
+        <v>172</v>
+      </c>
+      <c r="K22" t="s">
+        <v>193</v>
+      </c>
+      <c r="L22" t="s">
         <v>214</v>
       </c>
-      <c r="AA14" t="s">
-        <v>167</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>217</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>220</v>
+      <c r="M22" t="s">
+        <v>235</v>
+      </c>
+      <c r="N22" t="s">
+        <v>237</v>
+      </c>
+      <c r="O22" t="s">
+        <v>239</v>
+      </c>
+      <c r="P22" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>246</v>
+      </c>
+      <c r="R22" t="s">
+        <v>269</v>
+      </c>
+      <c r="S22" t="s">
+        <v>279</v>
+      </c>
+      <c r="T22" t="s">
+        <v>296</v>
+      </c>
+      <c r="U22" t="s">
+        <v>297</v>
+      </c>
+      <c r="V22" t="s">
+        <v>134</v>
+      </c>
+      <c r="W22" t="s">
+        <v>2</v>
+      </c>
+      <c r="X22" t="s">
+        <v>318</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>322</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,12 +844,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>338639</t>
+          <t>340192</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,95 +859,87 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PAMELA</t>
+          <t>BRANDON</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>DELGADILLO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6644409651</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>LOMA BONITA</t>
-        </is>
-      </c>
+          <t>6198156515</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>26-07-1998</t>
+          <t>01-08-2010</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>GHFTGDC@GMAIL.COM</t>
+          <t>BRANDONSILVA244@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>28-01-2026 08:38:36</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>02-02-2026 14:49:52</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>12-02-2026 09:13:35</t>
+          <t>04-02-2026 09:59:45</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>12-02-2026 09:13:05</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -955,7 +947,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26140522289900001357</t>
+          <t>26140522071170001067</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -966,12 +958,12 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -983,12 +975,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>340790</t>
+          <t>340280</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +990,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIA </t>
+          <t>ROSA VALERIA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APODACA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,12 +1010,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6645530549</t>
+          <t>6642708866</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AV CAN MAYOR</t>
+          <t>ESTRELLA DEL ORIENTE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1033,17 +1025,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25-08-2020</t>
+          <t>02-05-1997</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>DANIADRAWS@GMAIL.COM</t>
+          <t>VALERIA_ROGERS@LIVE.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>03-02-2026 18:47:07</t>
+          <t>02-02-2026 16:40:54</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1064,17 +1056,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-02-2026 18:56:39</t>
+          <t>02-02-2026 16:49:59</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>03-02-2026 18:54:43</t>
+          <t>02-02-2026 16:48:59</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1084,7 +1076,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1094,7 +1086,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26140522054580001049</t>
+          <t>26140522017370000999</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1106,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Noemi Carolina Meza Arreola</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1118,12 +1110,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>340192</t>
+          <t>340790</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,87 +1125,95 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BRANDON</t>
+          <t xml:space="preserve">DANIA </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>APODACA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DELGADILLO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6198156515</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6645530549</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AV CAN MAYOR</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>01-08-2010</t>
+          <t>25-08-2020</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>BRANDONSILVA244@GMAIL.COM</t>
+          <t>DANIADRAWS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-02-2026 14:49:52</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 18:47:07</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>04-02-2026 09:59:45</t>
+          <t>03-02-2026 18:56:39</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>03-02-2026 18:54:43</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1221,23 +1221,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26140522071170001067</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26140522054580001049</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Noemi Carolina Meza Arreola</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1249,12 +1245,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>340280</t>
+          <t>338639</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18098</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1260,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ROSA VALERIA</t>
+          <t>PAMELA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,12 +1280,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6642708866</t>
+          <t>6644409651</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ESTRELLA DEL ORIENTE</t>
+          <t>LOMA BONITA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1299,17 +1295,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>02-05-1997</t>
+          <t>26-07-1998</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>VALERIA_ROGERS@LIVE.COM</t>
+          <t>GHFTGDC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-02-2026 16:40:54</t>
+          <t>28-01-2026 08:38:36</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1330,17 +1326,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 16:49:59</t>
+          <t>12-02-2026 09:13:35</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-02-2026 16:48:59</t>
+          <t>12-02-2026 09:13:05</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1360,10 +1356,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26140522017370000999</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26140522289900001357</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>342419</t>
+          <t>342360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVIS MARLEN </t>
+          <t>MARIA DEL ROCIO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ROCHIN</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAUCEDO</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6642338869</t>
+          <t>6631107103</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AV DEL RUBI</t>
+          <t>PRIV GARDENIA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1569,17 +1569,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>03-11-1994</t>
+          <t>24-01-1985</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>IROCHINSAUCEDO@ICLOUD.COM</t>
+          <t>CESARIO_GARCIA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>09-02-2026 19:02:55</t>
+          <t>09-02-2026 17:54:42</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>09-02-2026 19:11:27</t>
+          <t>09-02-2026 18:02:59</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:03</t>
+          <t>09-02-2026 18:01:06</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26140522209920001244</t>
+          <t>26140522205100001233</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1654,12 +1654,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>342533</t>
+          <t>342419</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MARIBEL</t>
+          <t xml:space="preserve">IVIS MARLEN </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALVAN </t>
+          <t>ROCHIN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILAR </t>
+          <t>SAUCEDO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6645692934</t>
+          <t>6642338869</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUEVA AURORA </t>
+          <t>AV DEL RUBI</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>24-01-2001</t>
+          <t>03-11-1994</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>MARELGALVAN53@GMAIL.COM</t>
+          <t>IROCHINSAUCEDO@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10-02-2026 07:33:18</t>
+          <t>09-02-2026 19:02:55</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1735,17 +1735,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>10-02-2026 07:41:17</t>
+          <t>09-02-2026 19:11:27</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>10-02-2026 07:37:20</t>
+          <t>09-02-2026 19:10:03</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26140522224470001260</t>
+          <t>26140522209920001244</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1789,12 +1789,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>342360</t>
+          <t>342533</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20178</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,17 +1804,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MARIA DEL ROCIO</t>
+          <t>MARIBEL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">GALVAN </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6631107103</t>
+          <t>6645692934</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PRIV GARDENIA</t>
+          <t xml:space="preserve">NUEVA AURORA </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1839,17 +1839,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>24-01-1985</t>
+          <t>24-01-2001</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CESARIO_GARCIA@HOTMAIL.COM</t>
+          <t>MARELGALVAN53@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>09-02-2026 17:54:42</t>
+          <t>10-02-2026 07:33:18</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1870,17 +1870,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>09-02-2026 18:02:59</t>
+          <t>10-02-2026 07:41:17</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>09-02-2026 18:01:06</t>
+          <t>10-02-2026 07:37:20</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26140522205100001233</t>
+          <t>26140522224470001260</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1924,12 +1924,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>344364</t>
+          <t>340367</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22181</t>
+          <t>18185</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1939,17 +1939,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIA </t>
+          <t xml:space="preserve">JUANA CLAUDIA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>CAMACENA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GRACIDA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1959,14 +1959,10 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6647006311</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>FRANCISCO VILLA 5011</t>
-        </is>
-      </c>
+          <t>2285111160</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1974,64 +1970,56 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26-02-1977</t>
+          <t>22-06-1977</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>SHAPIS277@GMAIL.COM</t>
+          <t>CAMACENAJUANA5@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>16-02-2026 21:48:29</t>
+          <t>02-02-2026 19:31:33</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>16-02-2026 21:57:08</t>
+          <t>02-02-2026 19:39:24</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>16-02-2026 21:55:56</t>
-        </is>
-      </c>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2039,19 +2027,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26140522411860001500</t>
+          <t>26140522022420001008</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2198,12 +2186,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340367</t>
+          <t>344016</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>21833</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2213,17 +2201,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUANA CLAUDIA </t>
+          <t xml:space="preserve">ANA KAREN </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CAMACENA</t>
+          <t xml:space="preserve">SALCIDO </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GRACIDA</t>
+          <t>MAGAÑA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2233,10 +2221,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2285111160</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6646105596</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PANAMERICANO </t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2244,56 +2236,64 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22-06-1977</t>
+          <t>26-06-1993</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CAMACENAJUANA5@GMAIL.COM</t>
+          <t>ANAMAGAÑA371@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-02-2026 19:31:33</t>
+          <t>16-02-2026 11:21:32</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-02-2026 19:39:24</t>
+          <t>16-02-2026 11:27:59</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>16-02-2026 11:26:40</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2301,36 +2301,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26140522022420001008</t>
+          <t>26140522385390001470</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>344016</t>
+          <t>344573</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21833</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2340,17 +2340,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA KAREN </t>
+          <t xml:space="preserve">VERONICA </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALCIDO </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MAGAÑA</t>
+          <t>ARAOS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6646105596</t>
+          <t>6612034182</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PANAMERICANO </t>
+          <t>MIGUEL ROMERO 6012</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2375,17 +2375,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>26-06-1993</t>
+          <t>20-08-2000</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ANAMAGAÑA371@GMAIL.COM</t>
+          <t>PEREZVERONICA1204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>16-02-2026 11:21:32</t>
+          <t>17-02-2026 16:35:43</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2410,17 +2410,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>16-02-2026 11:27:59</t>
+          <t>17-02-2026 16:58:54</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>16-02-2026 11:26:40</t>
+          <t>17-02-2026 16:58:10</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26140522385390001470</t>
+          <t>26140522435860001527</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2452,24 +2452,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>342724</t>
+          <t>344489</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>22306</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2479,17 +2479,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t xml:space="preserve">MICHAEL </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DUEÑAS</t>
+          <t xml:space="preserve">ROJAS </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t xml:space="preserve">RENTERIA </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2499,35 +2499,39 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6633343468</t>
+          <t>6648567901</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>GARDEN 24241</t>
+          <t xml:space="preserve">LOMA BONITA </t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>09-12-1997</t>
+          <t>12-04-2006</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>JUANJOSEDUENAS85@GMAIL.COM</t>
+          <t>MACHAELRENTERIAROJAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10-02-2026 16:51:42</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>17-02-2026 13:55:21</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2545,17 +2549,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>10-02-2026 16:59:24</t>
+          <t>17-02-2026 13:58:26</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>10-02-2026 16:58:12</t>
+          <t>17-02-2026 13:57:43</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2575,7 +2579,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26140522238120001282</t>
+          <t>26140522428560001519</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2599,12 +2603,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>344493</t>
+          <t>344557</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2614,17 +2618,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BIRIDIANA</t>
+          <t>MARIO ALBERTO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOSA </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MONJARAZ</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2634,32 +2638,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6632474982</t>
+          <t>6646691008</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAS CUMBRES </t>
+          <t>FELIX PARRA 203</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>20-03-2006</t>
+          <t>22-10-2000</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>LOSAMONJARAZBIRIDIANA06@GMAIL.COM</t>
+          <t>MARIO.SOTO1403@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>17-02-2026 14:01:11</t>
+          <t>17-02-2026 16:14:15</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2684,7 +2688,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>17-02-2026 14:06:09</t>
+          <t>17-02-2026 16:29:22</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2694,7 +2698,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>17-02-2026 14:04:10</t>
+          <t>17-02-2026 16:25:31</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2714,7 +2718,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26140522428740001520</t>
+          <t>26140522434170001526</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2726,7 +2730,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2738,12 +2742,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>344489</t>
+          <t>344493</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2753,17 +2757,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">MICHAEL </t>
+          <t>BIRIDIANA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROJAS </t>
+          <t xml:space="preserve">LOSA </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTERIA </t>
+          <t>MONJARAZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2773,12 +2777,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6648567901</t>
+          <t>6632474982</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOMA BONITA </t>
+          <t xml:space="preserve">LAS CUMBRES </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2788,17 +2792,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>12-04-2006</t>
+          <t>20-03-2006</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MACHAELRENTERIAROJAS@GMAIL.COM</t>
+          <t>LOSAMONJARAZBIRIDIANA06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17-02-2026 13:55:21</t>
+          <t>17-02-2026 14:01:11</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2823,7 +2827,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>17-02-2026 13:58:26</t>
+          <t>17-02-2026 14:06:09</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2833,7 +2837,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>17-02-2026 13:57:43</t>
+          <t>17-02-2026 14:04:10</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2853,7 +2857,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26140522428560001519</t>
+          <t>26140522428740001520</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2877,12 +2881,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>344557</t>
+          <t>342724</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2892,17 +2896,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MARIO ALBERTO</t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>DUEÑAS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2912,12 +2916,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6646691008</t>
+          <t>6633343468</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FELIX PARRA 203</t>
+          <t>GARDEN 24241</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2927,24 +2931,20 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22-10-2000</t>
+          <t>09-12-1997</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MARIO.SOTO1403@GMAIL.COM</t>
+          <t>JUANJOSEDUENAS85@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>17-02-2026 16:14:15</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 16:51:42</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2962,17 +2962,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>17-02-2026 16:29:22</t>
+          <t>10-02-2026 16:59:24</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>17-02-2026 16:25:31</t>
+          <t>10-02-2026 16:58:12</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26140522434170001526</t>
+          <t>26140522238120001282</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3016,12 +3016,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>344573</t>
+          <t>345602</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22390</t>
+          <t>87767</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3031,17 +3031,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERONICA </t>
+          <t>MARIA NATIVIDAD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ARAOS</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6612034182</t>
+          <t>6643774656</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MIGUEL ROMERO 6012</t>
+          <t>FCO I MADERO 6852 -B</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>20-08-2000</t>
+          <t>08-09-2003</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PEREZVERONICA1204@GMAIL.COM</t>
+          <t>GUEVARAKINBOYU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>17-02-2026 16:35:43</t>
+          <t>22-02-2026 12:04:37</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>17-02-2026 16:58:54</t>
+          <t>22-02-2026 12:11:16</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>22-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>17-02-2026 16:58:10</t>
+          <t>22-02-2026 12:09:53</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26140522435860001527</t>
+          <t>26140522562650001628</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3294,12 +3294,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>344054</t>
+          <t>344364</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>22181</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3309,17 +3309,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SANDRA LETICIA</t>
+          <t xml:space="preserve">ELIA </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRERAS </t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE SANTIAGO </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3329,10 +3329,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6634313589</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6647006311</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>FRANCISCO VILLA 5011</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3340,42 +3344,42 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>04-05-2004</t>
+          <t>26-02-1977</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CONTRERASSANDRA149@GMAIL.COM</t>
+          <t>SHAPIS277@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>16-02-2026 12:48:08</t>
+          <t>16-02-2026 21:48:29</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>16-02-2026 12:49:38</t>
+          <t>16-02-2026 21:57:08</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3383,13 +3387,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>16-02-2026 21:55:56</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3397,22 +3409,149 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26140522387570001473</t>
+          <t>26140522411860001500</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>344054</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>21871</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SANDRA LETICIA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRERAS </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE SANTIAGO </t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6634313589</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>04-05-2004</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>CONTRERASSANDRA149@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>16-02-2026 12:48:08</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>16-02-2026 12:49:38</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26140522387570001473</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
         <is>
           <t>Saul  Ramirez Damian</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>248471</t>
+          <t>338638</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45975</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AXEL</t>
+          <t>ALMA LORENA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CABAÑAS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>GOVEA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,53 +613,53 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6634050813</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>6645112535</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NUEVA AURORA </t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>07-06-2000</t>
+          <t>15-10-1994</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>AXELCARDENASCA@GMAIL.COM</t>
+          <t>HJJJJJJJJ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>27-07-2024 08:36:55</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>28-01-2026 08:38:30</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>09-02-2026 10:49:17</t>
+          <t>09-02-2026 08:42:24</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -667,13 +667,21 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>09-02-2026 08:41:47</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -681,36 +689,40 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26090522188180001350</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+          <t>26140522185240001204</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>338638</t>
+          <t>340192</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16456</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,95 +732,87 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ALMA LORENA</t>
+          <t>BRANDON</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GOVEA</t>
+          <t>DELGADILLO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6645112535</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NUEVA AURORA </t>
-        </is>
-      </c>
+          <t>6198156515</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15-10-1994</t>
+          <t>01-08-2010</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HJJJJJJJJ@GMAIL.COM</t>
+          <t>BRANDONSILVA244@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>28-01-2026 08:38:30</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>02-02-2026 14:49:52</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>09-02-2026 08:42:24</t>
+          <t>04-02-2026 09:59:45</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>09-02-2026 08:41:47</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -816,7 +820,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26140522185240001204</t>
+          <t>26140522071170001067</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -827,12 +831,12 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -844,12 +848,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>340192</t>
+          <t>340280</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,87 +863,95 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BRANDON</t>
+          <t>ROSA VALERIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DELGADILLO</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6642708866</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ESTRELLA DEL ORIENTE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>02-05-1997</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>VALERIA_ROGERS@LIVE.COM</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:40:54</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:49:59</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:48:59</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>6198156515</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>01-08-2010</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>BRANDONSILVA244@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>02-02-2026 14:49:52</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>COBACH $399</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>04-02-2026 09:59:45</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -947,18 +959,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26140522071170001067</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26140522017370000999</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -975,12 +983,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>340280</t>
+          <t>340790</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18098</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ROSA VALERIA</t>
+          <t xml:space="preserve">DANIA </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>APODACA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1010,12 +1018,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6642708866</t>
+          <t>6645530549</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ESTRELLA DEL ORIENTE</t>
+          <t>AV CAN MAYOR</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1025,17 +1033,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>02-05-1997</t>
+          <t>25-08-2020</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>VALERIA_ROGERS@LIVE.COM</t>
+          <t>DANIADRAWS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-02-2026 16:40:54</t>
+          <t>03-02-2026 18:47:07</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1056,17 +1064,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-02-2026 16:49:59</t>
+          <t>03-02-2026 18:56:39</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-02-2026 16:48:59</t>
+          <t>03-02-2026 18:54:43</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1076,7 +1084,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1086,7 +1094,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26140522017370000999</t>
+          <t>26140522054580001049</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1098,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Noemi Carolina Meza Arreola</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1110,12 +1118,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>340790</t>
+          <t>248471</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>45975</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1125,17 +1133,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIA </t>
+          <t>AXEL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>APODACA</t>
+          <t>CABAÑAS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1145,75 +1153,67 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6645530549</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>AV CAN MAYOR</t>
-        </is>
-      </c>
+          <t>6634050813</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>25-08-2020</t>
+          <t>07-06-2000</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>DANIADRAWS@GMAIL.COM</t>
+          <t>AXELCARDENASCA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>03-02-2026 18:47:07</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>27-07-2024 08:36:55</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-02-2026 18:56:39</t>
+          <t>09-02-2026 10:49:17</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>03-02-2026 18:54:43</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1221,36 +1221,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26140522054580001049</t>
+          <t>26090522188180001350</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Noemi Carolina Meza Arreola</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>338639</t>
+          <t>341963</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1260,17 +1260,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PAMELA</t>
+          <t xml:space="preserve">LUZ DEL CARMEN </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6644409651</t>
+          <t>6644151535</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>LOMA BONITA</t>
+          <t>MONTE TRES PICOS</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1295,17 +1295,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>26-07-1998</t>
+          <t>28-12-1983</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>GHFTGDC@GMAIL.COM</t>
+          <t>LUZ28DOMI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>28-01-2026 08:38:36</t>
+          <t>08-02-2026 15:03:16</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12-02-2026 09:13:35</t>
+          <t>08-02-2026 15:10:44</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>12-02-2026 09:13:05</t>
+          <t>08-02-2026 15:08:28</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1356,14 +1356,10 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26140522289900001357</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26140522173200001196</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1372,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1384,12 +1380,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>341963</t>
+          <t>342419</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1399,17 +1395,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUZ DEL CARMEN </t>
+          <t xml:space="preserve">IVIS MARLEN </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>ROCHIN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>SAUCEDO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1419,12 +1415,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6644151535</t>
+          <t>6642338869</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MONTE TRES PICOS</t>
+          <t>AV DEL RUBI</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1434,17 +1430,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28-12-1983</t>
+          <t>03-11-1994</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>LUZ28DOMI@GMAIL.COM</t>
+          <t>IROCHINSAUCEDO@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>08-02-2026 15:03:16</t>
+          <t>09-02-2026 19:02:55</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1465,17 +1461,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>08-02-2026 15:10:44</t>
+          <t>09-02-2026 19:11:27</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>08-02-2026 15:08:28</t>
+          <t>09-02-2026 19:10:03</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1495,7 +1491,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26140522173200001196</t>
+          <t>26140522209920001244</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1507,7 +1503,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1519,12 +1515,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>342360</t>
+          <t>342533</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20178</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1534,17 +1530,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MARIA DEL ROCIO</t>
+          <t>MARIBEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">GALVAN </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1554,12 +1550,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6631107103</t>
+          <t>6645692934</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PRIV GARDENIA</t>
+          <t xml:space="preserve">NUEVA AURORA </t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1569,17 +1565,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>24-01-1985</t>
+          <t>24-01-2001</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CESARIO_GARCIA@HOTMAIL.COM</t>
+          <t>MARELGALVAN53@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>09-02-2026 17:54:42</t>
+          <t>10-02-2026 07:33:18</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1600,17 +1596,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>09-02-2026 18:02:59</t>
+          <t>10-02-2026 07:41:17</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>09-02-2026 18:01:06</t>
+          <t>10-02-2026 07:37:20</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1630,7 +1626,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26140522205100001233</t>
+          <t>26140522224470001260</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1654,12 +1650,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>342419</t>
+          <t>342360</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1669,17 +1665,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVIS MARLEN </t>
+          <t>MARIA DEL ROCIO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ROCHIN</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SAUCEDO</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1689,12 +1685,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6642338869</t>
+          <t>6631107103</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AV DEL RUBI</t>
+          <t>PRIV GARDENIA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1704,17 +1700,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>03-11-1994</t>
+          <t>24-01-1985</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>IROCHINSAUCEDO@ICLOUD.COM</t>
+          <t>CESARIO_GARCIA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>09-02-2026 19:02:55</t>
+          <t>09-02-2026 17:54:42</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1735,7 +1731,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>09-02-2026 19:11:27</t>
+          <t>09-02-2026 18:02:59</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1745,7 +1741,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:03</t>
+          <t>09-02-2026 18:01:06</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1765,7 +1761,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26140522209920001244</t>
+          <t>26140522205100001233</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1789,12 +1785,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>342533</t>
+          <t>338639</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,17 +1800,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MARIBEL</t>
+          <t>PAMELA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALVAN </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILAR </t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1824,12 +1820,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6645692934</t>
+          <t>6644409651</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUEVA AURORA </t>
+          <t>LOMA BONITA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1839,17 +1835,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>24-01-2001</t>
+          <t>26-07-1998</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MARELGALVAN53@GMAIL.COM</t>
+          <t>GHFTGDC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10-02-2026 07:33:18</t>
+          <t>28-01-2026 08:38:36</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1870,17 +1866,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>10-02-2026 07:41:17</t>
+          <t>12-02-2026 09:13:35</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>10-02-2026 07:37:20</t>
+          <t>12-02-2026 09:13:05</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1900,10 +1896,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26140522224470001260</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
+          <t>26140522289900001357</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -2325,12 +2325,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>344573</t>
+          <t>346001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22390</t>
+          <t>88166</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2340,17 +2340,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERONICA </t>
+          <t>TANIA LISSET</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ARAOS</t>
+          <t>MIRAMONTES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6612034182</t>
+          <t>6631184694</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MIGUEL ROMERO 6012</t>
+          <t>PRIV SAN LUCAS 4251</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2375,17 +2375,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>20-08-2000</t>
+          <t>06-05-1998</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PEREZVERONICA1204@GMAIL.COM</t>
+          <t>TANIAR758@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>17-02-2026 16:35:43</t>
+          <t>23-02-2026 18:46:02</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2410,17 +2410,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>17-02-2026 16:58:54</t>
+          <t>23-02-2026 18:52:25</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>17-02-2026 16:58:10</t>
+          <t>23-02-2026 18:50:28</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26140522435860001527</t>
+          <t>26140522597500001688</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2452,24 +2452,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>344489</t>
+          <t>344573</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2479,17 +2479,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MICHAEL </t>
+          <t xml:space="preserve">VERONICA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROJAS </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTERIA </t>
+          <t>ARAOS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6648567901</t>
+          <t>6612034182</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOMA BONITA </t>
+          <t>MIGUEL ROMERO 6012</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2514,17 +2514,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>12-04-2006</t>
+          <t>20-08-2000</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MACHAELRENTERIAROJAS@GMAIL.COM</t>
+          <t>PEREZVERONICA1204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>17-02-2026 13:55:21</t>
+          <t>17-02-2026 16:35:43</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>17-02-2026 13:58:26</t>
+          <t>17-02-2026 16:58:54</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>17-02-2026 13:57:43</t>
+          <t>17-02-2026 16:58:10</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26140522428560001519</t>
+          <t>26140522435860001527</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>344557</t>
+          <t>344493</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2618,17 +2618,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MARIO ALBERTO</t>
+          <t>BIRIDIANA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t xml:space="preserve">LOSA </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>MONJARAZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2638,32 +2638,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6646691008</t>
+          <t>6632474982</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FELIX PARRA 203</t>
+          <t xml:space="preserve">LAS CUMBRES </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22-10-2000</t>
+          <t>20-03-2006</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MARIO.SOTO1403@GMAIL.COM</t>
+          <t>LOSAMONJARAZBIRIDIANA06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>17-02-2026 16:14:15</t>
+          <t>17-02-2026 14:01:11</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>17-02-2026 16:29:22</t>
+          <t>17-02-2026 14:06:09</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>17-02-2026 16:25:31</t>
+          <t>17-02-2026 14:04:10</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26140522434170001526</t>
+          <t>26140522428740001520</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2742,12 +2742,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>344493</t>
+          <t>344489</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>22306</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2757,17 +2757,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BIRIDIANA</t>
+          <t xml:space="preserve">MICHAEL </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOSA </t>
+          <t xml:space="preserve">ROJAS </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MONJARAZ</t>
+          <t xml:space="preserve">RENTERIA </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6632474982</t>
+          <t>6648567901</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAS CUMBRES </t>
+          <t xml:space="preserve">LOMA BONITA </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2792,17 +2792,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>20-03-2006</t>
+          <t>12-04-2006</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>LOSAMONJARAZBIRIDIANA06@GMAIL.COM</t>
+          <t>MACHAELRENTERIAROJAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17-02-2026 14:01:11</t>
+          <t>17-02-2026 13:55:21</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>17-02-2026 14:06:09</t>
+          <t>17-02-2026 13:58:26</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>17-02-2026 14:04:10</t>
+          <t>17-02-2026 13:57:43</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26140522428740001520</t>
+          <t>26140522428560001519</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2881,12 +2881,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>342724</t>
+          <t>344557</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t>MARIO ALBERTO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DUEÑAS</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6633343468</t>
+          <t>6646691008</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>GARDEN 24241</t>
+          <t>FELIX PARRA 203</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2931,20 +2931,24 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>09-12-1997</t>
+          <t>22-10-2000</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>JUANJOSEDUENAS85@GMAIL.COM</t>
+          <t>MARIO.SOTO1403@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>10-02-2026 16:51:42</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>17-02-2026 16:14:15</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2962,17 +2966,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>10-02-2026 16:59:24</t>
+          <t>17-02-2026 16:29:22</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>10-02-2026 16:58:12</t>
+          <t>17-02-2026 16:25:31</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2992,7 +2996,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26140522238120001282</t>
+          <t>26140522434170001526</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3004,7 +3008,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3016,12 +3020,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>345602</t>
+          <t>345927</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>87767</t>
+          <t>88092</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3031,17 +3035,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MARIA NATIVIDAD</t>
+          <t>LILIA NAYELI</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">CORTES </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>OLIVARES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3051,12 +3055,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6643774656</t>
+          <t>6646572937</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>FCO I MADERO 6852 -B</t>
+          <t>TAMPICO 3572</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3066,17 +3070,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>08-09-2003</t>
+          <t>06-11-1996</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>GUEVARAKINBOYU@GMAIL.COM</t>
+          <t>LILICORTES5@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>22-02-2026 12:04:37</t>
+          <t>23-02-2026 17:36:15</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3101,17 +3105,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>22-02-2026 12:11:16</t>
+          <t>23-02-2026 17:42:37</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>22-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>22-02-2026 12:09:53</t>
+          <t>23-02-2026 17:41:36</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3131,7 +3135,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26140522562650001628</t>
+          <t>26140522591970001671</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3143,24 +3147,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>344359</t>
+          <t>345602</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>87767</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3170,17 +3174,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANTONIO </t>
+          <t>MARIA NATIVIDAD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3190,32 +3194,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6644048868</t>
+          <t>6643774656</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>FRANCISCO VILLA</t>
+          <t>FCO I MADERO 6852 -B</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>14-07-1967</t>
+          <t>08-09-2003</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ZAPATALABFACTURAS@HOTMAIL.COM</t>
+          <t>GUEVARAKINBOYU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>16-02-2026 20:52:22</t>
+          <t>22-02-2026 12:04:37</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3240,17 +3244,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>16-02-2026 21:13:15</t>
+          <t>22-02-2026 12:11:16</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>22-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>16-02-2026 21:11:12</t>
+          <t>22-02-2026 12:09:53</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3260,7 +3264,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3270,7 +3274,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26140522411330001499</t>
+          <t>26140522562650001628</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3282,7 +3286,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3294,12 +3298,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>344364</t>
+          <t>342724</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22181</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3309,17 +3313,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIA </t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>DUEÑAS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3329,39 +3333,35 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6647006311</t>
+          <t>6633343468</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FRANCISCO VILLA 5011</t>
+          <t>GARDEN 24241</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>26-02-1977</t>
+          <t>09-12-1997</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SHAPIS277@GMAIL.COM</t>
+          <t>JUANJOSEDUENAS85@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>16-02-2026 21:48:29</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 16:51:42</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3379,17 +3379,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>16-02-2026 21:57:08</t>
+          <t>10-02-2026 16:59:24</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>16-02-2026 21:55:56</t>
+          <t>10-02-2026 16:58:12</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26140522411860001500</t>
+          <t>26140522238120001282</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3433,12 +3433,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>344054</t>
+          <t>345993</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>88158</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3448,17 +3448,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SANDRA LETICIA</t>
+          <t>JHOVANNY</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRERAS </t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE SANTIAGO </t>
+          <t>BENITEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3468,67 +3468,79 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6634313589</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6643012921</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRIV SAN LUCAS </t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>04-05-2004</t>
+          <t>25-09-1994</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CONTRERASSANDRA149@GMAIL.COM</t>
+          <t>JHOVANNYTORRESBENITEZ031@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>16-02-2026 12:48:08</t>
+          <t>23-02-2026 18:36:29</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>16-02-2026 12:49:38</t>
+          <t>23-02-2026 18:41:47</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:40:26</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3536,24 +3548,556 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26140522387570001473</t>
+          <t>26140522596840001685</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>344364</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>22181</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELIA </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6647006311</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>FRANCISCO VILLA 5011</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>26-02-1977</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>SHAPIS277@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>16-02-2026 21:48:29</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>16-02-2026 21:57:08</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>16-02-2026 21:55:56</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26140522411860001500</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>344054</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21871</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SANDRA LETICIA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRERAS </t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE SANTIAGO </t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6634313589</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>04-05-2004</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>CONTRERASSANDRA149@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>16-02-2026 12:48:08</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>16-02-2026 12:49:38</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26140522387570001473</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>Saul  Ramirez Damian</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>344359</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>22176</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANTONIO </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES </t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6644048868</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>FRANCISCO VILLA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>14-07-1967</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ZAPATALABFACTURAS@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>16-02-2026 20:52:22</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>16-02-2026 21:13:15</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>16-02-2026 21:11:12</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26140522411330001499</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>345989</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>88154</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YOSELIN </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENCINAS </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>MIRAMONTES</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6644643065</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>24-04-2012</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>TANIAMIRA758@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:30:03</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:32:11</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26140522595960001682</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,12 +983,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>340790</t>
+          <t>248471</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>45975</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIA </t>
+          <t>AXEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APODACA</t>
+          <t>CABAÑAS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,75 +1018,67 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6645530549</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>AV CAN MAYOR</t>
-        </is>
-      </c>
+          <t>6634050813</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25-08-2020</t>
+          <t>07-06-2000</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>DANIADRAWS@GMAIL.COM</t>
+          <t>AXELCARDENASCA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>03-02-2026 18:47:07</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>27-07-2024 08:36:55</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-02-2026 18:56:39</t>
+          <t>09-02-2026 10:49:17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>03-02-2026 18:54:43</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1094,36 +1086,36 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26140522054580001049</t>
+          <t>26090522188180001350</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Noemi Carolina Meza Arreola</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>248471</t>
+          <t>340790</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>45975</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1133,17 +1125,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AXEL</t>
+          <t xml:space="preserve">DANIA </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CABAÑAS</t>
+          <t>APODACA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1153,67 +1145,75 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6634050813</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6645530549</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AV CAN MAYOR</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>07-06-2000</t>
+          <t>25-08-2020</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>AXELCARDENASCA@GMAIL.COM</t>
+          <t>DANIADRAWS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>27-07-2024 08:36:55</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 18:47:07</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>09-02-2026 10:49:17</t>
+          <t>03-02-2026 18:56:39</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>03-02-2026 18:54:43</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1221,36 +1221,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26090522188180001350</t>
+          <t>26140522054580001049</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Noemi Carolina Meza Arreola</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>341963</t>
+          <t>342419</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1260,17 +1260,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUZ DEL CARMEN </t>
+          <t xml:space="preserve">IVIS MARLEN </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>ROCHIN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>SAUCEDO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6644151535</t>
+          <t>6642338869</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MONTE TRES PICOS</t>
+          <t>AV DEL RUBI</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1295,17 +1295,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>28-12-1983</t>
+          <t>03-11-1994</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>LUZ28DOMI@GMAIL.COM</t>
+          <t>IROCHINSAUCEDO@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>08-02-2026 15:03:16</t>
+          <t>09-02-2026 19:02:55</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>08-02-2026 15:10:44</t>
+          <t>09-02-2026 19:11:27</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>08-02-2026 15:08:28</t>
+          <t>09-02-2026 19:10:03</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26140522173200001196</t>
+          <t>26140522209920001244</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1380,12 +1380,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>342419</t>
+          <t>342533</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1395,17 +1395,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVIS MARLEN </t>
+          <t>MARIBEL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ROCHIN</t>
+          <t xml:space="preserve">GALVAN </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SAUCEDO</t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6642338869</t>
+          <t>6645692934</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AV DEL RUBI</t>
+          <t xml:space="preserve">NUEVA AURORA </t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1430,17 +1430,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>03-11-1994</t>
+          <t>24-01-2001</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>IROCHINSAUCEDO@ICLOUD.COM</t>
+          <t>MARELGALVAN53@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>09-02-2026 19:02:55</t>
+          <t>10-02-2026 07:33:18</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>09-02-2026 19:11:27</t>
+          <t>10-02-2026 07:41:17</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:03</t>
+          <t>10-02-2026 07:37:20</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26140522209920001244</t>
+          <t>26140522224470001260</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1515,12 +1515,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>342533</t>
+          <t>342360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1530,17 +1530,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MARIBEL</t>
+          <t>MARIA DEL ROCIO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALVAN </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILAR </t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6645692934</t>
+          <t>6631107103</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUEVA AURORA </t>
+          <t>PRIV GARDENIA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1565,17 +1565,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>24-01-2001</t>
+          <t>24-01-1985</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MARELGALVAN53@GMAIL.COM</t>
+          <t>CESARIO_GARCIA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10-02-2026 07:33:18</t>
+          <t>09-02-2026 17:54:42</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1596,17 +1596,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>10-02-2026 07:41:17</t>
+          <t>09-02-2026 18:02:59</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>10-02-2026 07:37:20</t>
+          <t>09-02-2026 18:01:06</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26140522224470001260</t>
+          <t>26140522205100001233</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1650,12 +1650,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>342360</t>
+          <t>338639</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20178</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MARIA DEL ROCIO</t>
+          <t>PAMELA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6631107103</t>
+          <t>6644409651</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PRIV GARDENIA</t>
+          <t>LOMA BONITA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1700,17 +1700,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>24-01-1985</t>
+          <t>26-07-1998</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CESARIO_GARCIA@HOTMAIL.COM</t>
+          <t>GHFTGDC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>09-02-2026 17:54:42</t>
+          <t>28-01-2026 08:38:36</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1731,17 +1731,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>09-02-2026 18:02:59</t>
+          <t>12-02-2026 09:13:35</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>09-02-2026 18:01:06</t>
+          <t>12-02-2026 09:13:05</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1761,10 +1761,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26140522205100001233</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
+          <t>26140522289900001357</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1785,12 +1789,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>338639</t>
+          <t>341963</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1800,17 +1804,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PAMELA</t>
+          <t xml:space="preserve">LUZ DEL CARMEN </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1820,12 +1824,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6644409651</t>
+          <t>6644151535</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LOMA BONITA</t>
+          <t>MONTE TRES PICOS</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1835,17 +1839,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26-07-1998</t>
+          <t>28-12-1983</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>GHFTGDC@GMAIL.COM</t>
+          <t>LUZ28DOMI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>28-01-2026 08:38:36</t>
+          <t>08-02-2026 15:03:16</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1866,17 +1870,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>12-02-2026 09:13:35</t>
+          <t>08-02-2026 15:10:44</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>12-02-2026 09:13:05</t>
+          <t>08-02-2026 15:08:28</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1896,14 +1900,10 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26140522289900001357</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26140522173200001196</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>343355</t>
+          <t>344573</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ROBERTO TRINIDAD</t>
+          <t xml:space="preserve">VERONICA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAREZ </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ABARCA</t>
+          <t>ARAOS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2086,35 +2086,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6634586390</t>
+          <t>6612034182</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>EMILIANO ZAPATA</t>
+          <t>MIGUEL ROMERO 6012</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18-08-1985</t>
+          <t>20-08-2000</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ROBERTODALIA9852@GMAIL.COM</t>
+          <t>PEREZVERONICA1204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>12-02-2026 17:57:31</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>17-02-2026 16:35:43</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2132,17 +2136,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>12-02-2026 18:06:53</t>
+          <t>17-02-2026 16:58:54</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>12-02-2026 18:05:12</t>
+          <t>17-02-2026 16:58:10</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2162,7 +2166,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26140522301540001381</t>
+          <t>26140522435860001527</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2186,12 +2190,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>344016</t>
+          <t>346001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21833</t>
+          <t>88166</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2201,17 +2205,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA KAREN </t>
+          <t>TANIA LISSET</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALCIDO </t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MAGAÑA</t>
+          <t>MIRAMONTES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2221,12 +2225,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6646105596</t>
+          <t>6631184694</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PANAMERICANO </t>
+          <t>PRIV SAN LUCAS 4251</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2236,17 +2240,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>26-06-1993</t>
+          <t>06-05-1998</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ANAMAGAÑA371@GMAIL.COM</t>
+          <t>TANIAR758@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>16-02-2026 11:21:32</t>
+          <t>23-02-2026 18:46:02</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2271,17 +2275,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>16-02-2026 11:27:59</t>
+          <t>23-02-2026 18:52:25</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>16-02-2026 11:26:40</t>
+          <t>23-02-2026 18:50:28</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2291,7 +2295,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2301,7 +2305,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26140522385390001470</t>
+          <t>26140522597500001688</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2313,24 +2317,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>346001</t>
+          <t>344921</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>88166</t>
+          <t>22738</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2340,17 +2344,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TANIA LISSET</t>
+          <t>SONIA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MIRAMONTES</t>
+          <t>CASILLAS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2360,12 +2364,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6631184694</t>
+          <t>6641215195</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PRIV SAN LUCAS 4251</t>
+          <t>C MONTE TRES PICOS 6917</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2375,17 +2379,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>06-05-1998</t>
+          <t>26-05-1979</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>TANIAR758@GMAIL.COM</t>
+          <t>VZ0BBD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>23-02-2026 18:46:02</t>
+          <t>18-02-2026 18:06:57</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2410,17 +2414,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>23-02-2026 18:52:25</t>
+          <t>25-02-2026 18:43:45</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>23-02-2026 18:50:28</t>
+          <t>25-02-2026 18:40:28</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2440,10 +2444,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26140522597500001688</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+          <t>26140522664110001785</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2464,12 +2472,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>344573</t>
+          <t>344016</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22390</t>
+          <t>21833</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2479,17 +2487,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERONICA </t>
+          <t xml:space="preserve">ANA KAREN </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">SALCIDO </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ARAOS</t>
+          <t>MAGAÑA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2499,12 +2507,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6612034182</t>
+          <t>6646105596</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MIGUEL ROMERO 6012</t>
+          <t xml:space="preserve">PANAMERICANO </t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2514,17 +2522,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20-08-2000</t>
+          <t>26-06-1993</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PEREZVERONICA1204@GMAIL.COM</t>
+          <t>ANAMAGAÑA371@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>17-02-2026 16:35:43</t>
+          <t>16-02-2026 11:21:32</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2549,17 +2557,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>17-02-2026 16:58:54</t>
+          <t>16-02-2026 11:27:59</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>17-02-2026 16:58:10</t>
+          <t>16-02-2026 11:26:40</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2579,7 +2587,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26140522435860001527</t>
+          <t>26140522385390001470</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2591,12 +2599,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2750,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>344489</t>
+          <t>342724</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2757,17 +2765,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">MICHAEL </t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROJAS </t>
+          <t>DUEÑAS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTERIA </t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2777,39 +2785,35 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6648567901</t>
+          <t>6633343468</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOMA BONITA </t>
+          <t>GARDEN 24241</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>12-04-2006</t>
+          <t>09-12-1997</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MACHAELRENTERIAROJAS@GMAIL.COM</t>
+          <t>JUANJOSEDUENAS85@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17-02-2026 13:55:21</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 16:51:42</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2827,17 +2831,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>17-02-2026 13:58:26</t>
+          <t>10-02-2026 16:59:24</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>17-02-2026 13:57:43</t>
+          <t>10-02-2026 16:58:12</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2857,7 +2861,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26140522428560001519</t>
+          <t>26140522238120001282</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2881,12 +2885,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>344557</t>
+          <t>343355</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2896,17 +2900,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MARIO ALBERTO</t>
+          <t>ROBERTO TRINIDAD</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t xml:space="preserve">JUAREZ </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>ABARCA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2916,12 +2920,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6646691008</t>
+          <t>6634586390</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FELIX PARRA 203</t>
+          <t>EMILIANO ZAPATA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2931,24 +2935,20 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22-10-2000</t>
+          <t>18-08-1985</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MARIO.SOTO1403@GMAIL.COM</t>
+          <t>ROBERTODALIA9852@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>17-02-2026 16:14:15</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 17:57:31</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2966,17 +2966,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>17-02-2026 16:29:22</t>
+          <t>12-02-2026 18:06:53</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>17-02-2026 16:25:31</t>
+          <t>12-02-2026 18:05:12</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26140522434170001526</t>
+          <t>26140522301540001381</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3020,12 +3020,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>345927</t>
+          <t>344794</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>88092</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LILIA NAYELI</t>
+          <t xml:space="preserve">BLANCA ESTELA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORTES </t>
+          <t xml:space="preserve">BORJA </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OLIVARES</t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3055,14 +3055,10 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6646572937</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>TAMPICO 3572</t>
-        </is>
-      </c>
+          <t>6643577880</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3070,64 +3066,56 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>06-11-1996</t>
+          <t>19-08-1977</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>LILICORTES5@ICLOUD.COM</t>
+          <t>GFGFFGEUYRFGUY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>23-02-2026 17:36:15</t>
+          <t>18-02-2026 11:37:29</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>23-02-2026 17:42:37</t>
+          <t>24-02-2026 12:06:24</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>23-02-2026 17:41:36</t>
-        </is>
-      </c>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3135,14 +3123,22 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26140522591970001671</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>26140522617050001721</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>MARIA LUISA VALDEZ MAYORGA</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3159,12 +3155,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>345602</t>
+          <t>346247</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>87767</t>
+          <t>88412</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3174,17 +3170,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MARIA NATIVIDAD</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3194,12 +3190,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6643774656</t>
+          <t>2296582638</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>FCO I MADERO 6852 -B</t>
+          <t>RESIDENCIAL ESMERALDA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3209,17 +3205,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>08-09-2003</t>
+          <t>05-12-2000</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>GUEVARAKINBOYU@GMAIL.COM</t>
+          <t>ELIZABETH.HERRERAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>22-02-2026 12:04:37</t>
+          <t>24-02-2026 17:18:41</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3244,17 +3240,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>22-02-2026 12:11:16</t>
+          <t>24-02-2026 17:32:02</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>22-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>22-02-2026 12:09:53</t>
+          <t>24-02-2026 17:28:39</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3274,7 +3270,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26140522562650001628</t>
+          <t>26140522628100001733</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3286,24 +3282,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342724</t>
+          <t>346365</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>88530</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3313,17 +3309,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t xml:space="preserve">SAMUEL AARON </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>DUEÑAS</t>
+          <t xml:space="preserve">MACARIO </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3333,12 +3329,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6633343468</t>
+          <t>6647589644</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>GARDEN 24241</t>
+          <t>PLAYAS ROSARITO</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3348,20 +3344,24 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>09-12-1997</t>
+          <t>08-02-2003</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>JUANJOSEDUENAS85@GMAIL.COM</t>
+          <t>MACARIOSAMUEL7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>10-02-2026 16:51:42</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>25-02-2026 06:48:49</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3379,17 +3379,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>10-02-2026 16:59:24</t>
+          <t>25-02-2026 06:52:37</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>10-02-2026 16:58:12</t>
+          <t>25-02-2026 06:51:27</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26140522238120001282</t>
+          <t>26140522645120001756</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3421,12 +3421,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -3560,24 +3560,24 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>344364</t>
+          <t>345602</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22181</t>
+          <t>87767</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3587,17 +3587,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIA </t>
+          <t>MARIA NATIVIDAD</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6647006311</t>
+          <t>6643774656</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>FRANCISCO VILLA 5011</t>
+          <t>FCO I MADERO 6852 -B</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3622,17 +3622,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>26-02-1977</t>
+          <t>08-09-2003</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>SHAPIS277@GMAIL.COM</t>
+          <t>GUEVARAKINBOYU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>16-02-2026 21:48:29</t>
+          <t>22-02-2026 12:04:37</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>16-02-2026 21:57:08</t>
+          <t>22-02-2026 12:11:16</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>22-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>16-02-2026 21:55:56</t>
+          <t>22-02-2026 12:09:53</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26140522411860001500</t>
+          <t>26140522562650001628</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3711,12 +3711,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>344054</t>
+          <t>344364</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>22181</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3726,17 +3726,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SANDRA LETICIA</t>
+          <t xml:space="preserve">ELIA </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRERAS </t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE SANTIAGO </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3746,10 +3746,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6634313589</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>6647006311</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>FRANCISCO VILLA 5011</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3757,42 +3761,42 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>04-05-2004</t>
+          <t>26-02-1977</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CONTRERASSANDRA149@GMAIL.COM</t>
+          <t>SHAPIS277@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>16-02-2026 12:48:08</t>
+          <t>16-02-2026 21:48:29</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>16-02-2026 12:49:38</t>
+          <t>16-02-2026 21:57:08</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3800,13 +3804,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>16-02-2026 21:55:56</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3814,14 +3826,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26140522387570001473</t>
+          <t>26140522411860001500</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3838,12 +3850,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>344359</t>
+          <t>344489</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>22306</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3853,17 +3865,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANTONIO </t>
+          <t xml:space="preserve">MICHAEL </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t xml:space="preserve">ROJAS </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t xml:space="preserve">RENTERIA </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3873,32 +3885,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6644048868</t>
+          <t>6648567901</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>FRANCISCO VILLA</t>
+          <t xml:space="preserve">LOMA BONITA </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>14-07-1967</t>
+          <t>12-04-2006</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ZAPATALABFACTURAS@HOTMAIL.COM</t>
+          <t>MACHAELRENTERIAROJAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>16-02-2026 20:52:22</t>
+          <t>17-02-2026 13:55:21</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3923,17 +3935,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>16-02-2026 21:13:15</t>
+          <t>17-02-2026 13:58:26</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>16-02-2026 21:11:12</t>
+          <t>17-02-2026 13:57:43</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3943,7 +3955,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3953,7 +3965,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26140522411330001499</t>
+          <t>26140522428560001519</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3965,7 +3977,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3977,12 +3989,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>345989</t>
+          <t>344557</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>88154</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3992,17 +4004,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">YOSELIN </t>
+          <t>MARIO ALBERTO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENCINAS </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MIRAMONTES</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4012,67 +4024,79 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6644643065</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6646691008</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>FELIX PARRA 203</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>24-04-2012</t>
+          <t>22-10-2000</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TANIAMIRA758@GMAIL.COM</t>
+          <t>MARIO.SOTO1403@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>23-02-2026 18:30:03</t>
+          <t>17-02-2026 16:14:15</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>23-02-2026 18:32:11</t>
+          <t>17-02-2026 16:29:22</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>17-02-2026 16:25:31</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4080,22 +4104,824 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26140522595960001682</t>
+          <t>26140522434170001526</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>344054</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>21871</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SANDRA LETICIA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTRERAS </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DE SANTIAGO </t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6634313589</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>04-05-2004</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>CONTRERASSANDRA149@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>16-02-2026 12:48:08</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>16-02-2026 12:49:38</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26140522387570001473</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>344359</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>22176</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANTONIO </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6644048868</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>FRANCISCO VILLA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>14-07-1967</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>ZAPATALABFACTURAS@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>16-02-2026 20:52:22</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>16-02-2026 21:13:15</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>16-02-2026 21:11:12</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26140522411330001499</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>345927</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>88092</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LILIA NAYELI</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORTES </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>OLIVARES</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6646572937</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>TAMPICO 3572</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>06-11-1996</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>LILICORTES5@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:36:15</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:42:37</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:41:36</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26140522591970001671</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>345989</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>88154</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YOSELIN </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENCINAS </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>MIRAMONTES</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6644643065</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>24-04-2012</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>TANIAMIRA758@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:30:03</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:32:11</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26140522595960001682</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Etzon  Pizano Cazares</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>345850</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>88015</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ERICKA ISABEL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FUENTES </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>HERRAN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6642294144</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE MA MORELOS </t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>31-10-1995</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>ERICKAFUENTES111@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:51:57</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>25-02-2026 18:15:35</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>25-02-2026 18:06:31</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26140522662810001783</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>346512</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>88677</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>GLENDA ACEVER</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CARBAJAL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>AVITIA</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6641171074</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>07-10-1997</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>GLEN412@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>25-02-2026 15:39:54</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>25-02-2026 15:41:38</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26140522655870001771</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
@@ -717,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>340192</t>
+          <t>248471</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>45975</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,27 +732,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BRANDON</t>
+          <t>AXEL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>CABAÑAS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DELGADILLO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6198156515</t>
+          <t>6634050813</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -763,17 +763,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>01-08-2010</t>
+          <t>07-06-2000</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>BRANDONSILVA244@GMAIL.COM</t>
+          <t>AXELCARDENASCA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-02-2026 14:49:52</t>
+          <t>27-07-2024 08:36:55</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>04-02-2026 09:59:45</t>
+          <t>09-02-2026 10:49:17</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -820,40 +820,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26140522071170001067</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26090522188180001350</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>340280</t>
+          <t>340192</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18098</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -863,95 +859,87 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ROSA VALERIA</t>
+          <t>BRANDON</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>DELGADILLO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6642708866</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ESTRELLA DEL ORIENTE</t>
-        </is>
-      </c>
+          <t>6198156515</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>02-05-1997</t>
+          <t>01-08-2010</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>VALERIA_ROGERS@LIVE.COM</t>
+          <t>BRANDONSILVA244@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-02-2026 16:40:54</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>02-02-2026 14:49:52</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-02-2026 16:49:59</t>
+          <t>04-02-2026 09:59:45</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-02-2026 16:48:59</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -959,14 +947,18 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26140522017370000999</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+          <t>26140522071170001067</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -983,12 +975,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>248471</t>
+          <t>340280</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45975</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +990,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AXEL</t>
+          <t>ROSA VALERIA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CABAÑAS</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,67 +1010,75 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6634050813</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>6642708866</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ESTRELLA DEL ORIENTE</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>07-06-2000</t>
+          <t>02-05-1997</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>AXELCARDENASCA@GMAIL.COM</t>
+          <t>VALERIA_ROGERS@LIVE.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>27-07-2024 08:36:55</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 16:40:54</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>09-02-2026 10:49:17</t>
+          <t>02-02-2026 16:49:59</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:48:59</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1086,24 +1086,24 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26090522188180001350</t>
+          <t>26140522017370000999</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>342419</t>
+          <t>338639</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1260,17 +1260,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVIS MARLEN </t>
+          <t>PAMELA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ROCHIN</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAUCEDO</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6642338869</t>
+          <t>6644409651</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AV DEL RUBI</t>
+          <t>LOMA BONITA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1295,17 +1295,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>03-11-1994</t>
+          <t>26-07-1998</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>IROCHINSAUCEDO@ICLOUD.COM</t>
+          <t>GHFTGDC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>09-02-2026 19:02:55</t>
+          <t>28-01-2026 08:38:36</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>09-02-2026 19:11:27</t>
+          <t>12-02-2026 09:13:35</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:03</t>
+          <t>12-02-2026 09:13:05</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1356,10 +1356,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26140522209920001244</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26140522289900001357</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1380,12 +1384,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>342533</t>
+          <t>341963</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1395,17 +1399,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MARIBEL</t>
+          <t xml:space="preserve">LUZ DEL CARMEN </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALVAN </t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILAR </t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1415,12 +1419,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6645692934</t>
+          <t>6644151535</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUEVA AURORA </t>
+          <t>MONTE TRES PICOS</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1430,17 +1434,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>24-01-2001</t>
+          <t>28-12-1983</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MARELGALVAN53@GMAIL.COM</t>
+          <t>LUZ28DOMI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10-02-2026 07:33:18</t>
+          <t>08-02-2026 15:03:16</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1461,17 +1465,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>10-02-2026 07:41:17</t>
+          <t>08-02-2026 15:10:44</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>10-02-2026 07:37:20</t>
+          <t>08-02-2026 15:08:28</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1491,7 +1495,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26140522224470001260</t>
+          <t>26140522173200001196</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1503,7 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1650,12 +1654,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>338639</t>
+          <t>340367</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>18185</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1665,17 +1669,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PAMELA</t>
+          <t xml:space="preserve">JUANA CLAUDIA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>CAMACENA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>GRACIDA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1685,14 +1689,10 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6644409651</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>LOMA BONITA</t>
-        </is>
-      </c>
+          <t>2285111160</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1700,60 +1700,56 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26-07-1998</t>
+          <t>22-06-1977</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>GHFTGDC@GMAIL.COM</t>
+          <t>CAMACENAJUANA5@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>28-01-2026 08:38:36</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>02-02-2026 19:31:33</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>12-02-2026 09:13:35</t>
+          <t>02-02-2026 19:39:24</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>12-02-2026 09:13:05</t>
-        </is>
-      </c>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1761,23 +1757,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26140522289900001357</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26140522022420001008</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1789,12 +1781,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>341963</t>
+          <t>344016</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>21833</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,17 +1796,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUZ DEL CARMEN </t>
+          <t xml:space="preserve">ANA KAREN </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t xml:space="preserve">SALCIDO </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>MAGAÑA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1824,12 +1816,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6644151535</t>
+          <t>6646105596</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MONTE TRES PICOS</t>
+          <t xml:space="preserve">PANAMERICANO </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1839,20 +1831,24 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>28-12-1983</t>
+          <t>26-06-1993</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>LUZ28DOMI@GMAIL.COM</t>
+          <t>ANAMAGAÑA371@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>08-02-2026 15:03:16</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>16-02-2026 11:21:32</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1870,17 +1866,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>08-02-2026 15:10:44</t>
+          <t>16-02-2026 11:27:59</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>08-02-2026 15:08:28</t>
+          <t>16-02-2026 11:26:40</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1900,7 +1896,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26140522173200001196</t>
+          <t>26140522385390001470</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1912,24 +1908,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340367</t>
+          <t>342724</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1939,17 +1935,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUANA CLAUDIA </t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CAMACENA</t>
+          <t>DUEÑAS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GRACIDA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1959,67 +1955,75 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2285111160</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6633343468</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>GARDEN 24241</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>22-06-1977</t>
+          <t>09-12-1997</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CAMACENAJUANA5@GMAIL.COM</t>
+          <t>JUANJOSEDUENAS85@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-02-2026 19:31:33</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 16:51:42</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-02-2026 19:39:24</t>
+          <t>10-02-2026 16:59:24</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>10-02-2026 16:58:12</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2027,14 +2031,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26140522022420001008</t>
+          <t>26140522238120001282</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2190,12 +2194,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>346001</t>
+          <t>343355</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>88166</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2205,17 +2209,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TANIA LISSET</t>
+          <t>ROBERTO TRINIDAD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t xml:space="preserve">JUAREZ </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MIRAMONTES</t>
+          <t>ABARCA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2225,39 +2229,35 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6631184694</t>
+          <t>6634586390</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>PRIV SAN LUCAS 4251</t>
+          <t>EMILIANO ZAPATA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>06-05-1998</t>
+          <t>18-08-1985</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>TANIAR758@GMAIL.COM</t>
+          <t>ROBERTODALIA9852@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>23-02-2026 18:46:02</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 17:57:31</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2275,17 +2275,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>23-02-2026 18:52:25</t>
+          <t>12-02-2026 18:06:53</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>23-02-2026 18:50:28</t>
+          <t>12-02-2026 18:05:12</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26140522597500001688</t>
+          <t>26140522301540001381</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2460,24 +2460,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>344016</t>
+          <t>342419</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21833</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2487,17 +2487,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA KAREN </t>
+          <t xml:space="preserve">IVIS MARLEN </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALCIDO </t>
+          <t>ROCHIN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MAGAÑA</t>
+          <t>SAUCEDO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6646105596</t>
+          <t>6642338869</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">PANAMERICANO </t>
+          <t>AV DEL RUBI</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2522,24 +2522,20 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>26-06-1993</t>
+          <t>03-11-1994</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ANAMAGAÑA371@GMAIL.COM</t>
+          <t>IROCHINSAUCEDO@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>16-02-2026 11:21:32</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 19:02:55</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2557,17 +2553,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>16-02-2026 11:27:59</t>
+          <t>09-02-2026 19:11:27</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>16-02-2026 11:26:40</t>
+          <t>09-02-2026 19:10:03</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2587,7 +2583,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26140522385390001470</t>
+          <t>26140522209920001244</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2599,24 +2595,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>344493</t>
+          <t>342533</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2626,17 +2622,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BIRIDIANA</t>
+          <t>MARIBEL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOSA </t>
+          <t xml:space="preserve">GALVAN </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MONJARAZ</t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2646,12 +2642,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6632474982</t>
+          <t>6645692934</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAS CUMBRES </t>
+          <t xml:space="preserve">NUEVA AURORA </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2661,24 +2657,20 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>20-03-2006</t>
+          <t>24-01-2001</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>LOSAMONJARAZBIRIDIANA06@GMAIL.COM</t>
+          <t>MARELGALVAN53@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>17-02-2026 14:01:11</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 07:33:18</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2696,17 +2688,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>17-02-2026 14:06:09</t>
+          <t>10-02-2026 07:41:17</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>17-02-2026 14:04:10</t>
+          <t>10-02-2026 07:37:20</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2726,7 +2718,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26140522428740001520</t>
+          <t>26140522224470001260</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2738,7 +2730,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2750,12 +2742,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>342724</t>
+          <t>344493</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2765,17 +2757,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t>BIRIDIANA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DUEÑAS</t>
+          <t xml:space="preserve">LOSA </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>MONJARAZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2785,35 +2777,39 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6633343468</t>
+          <t>6632474982</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>GARDEN 24241</t>
+          <t xml:space="preserve">LAS CUMBRES </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>09-12-1997</t>
+          <t>20-03-2006</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>JUANJOSEDUENAS85@GMAIL.COM</t>
+          <t>LOSAMONJARAZBIRIDIANA06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>10-02-2026 16:51:42</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>17-02-2026 14:01:11</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2831,17 +2827,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>10-02-2026 16:59:24</t>
+          <t>17-02-2026 14:06:09</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>10-02-2026 16:58:12</t>
+          <t>17-02-2026 14:04:10</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2861,7 +2857,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26140522238120001282</t>
+          <t>26140522428740001520</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2885,12 +2881,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>343355</t>
+          <t>344364</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>22181</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2900,17 +2896,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ROBERTO TRINIDAD</t>
+          <t xml:space="preserve">ELIA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAREZ </t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ABARCA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2920,35 +2916,39 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6634586390</t>
+          <t>6647006311</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>EMILIANO ZAPATA</t>
+          <t>FRANCISCO VILLA 5011</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>18-08-1985</t>
+          <t>26-02-1977</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ROBERTODALIA9852@GMAIL.COM</t>
+          <t>SHAPIS277@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>12-02-2026 17:57:31</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>16-02-2026 21:48:29</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2966,17 +2966,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>12-02-2026 18:06:53</t>
+          <t>16-02-2026 21:57:08</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>12-02-2026 18:05:12</t>
+          <t>16-02-2026 21:55:56</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26140522301540001381</t>
+          <t>26140522411860001500</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3020,12 +3020,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>344794</t>
+          <t>346247</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22611</t>
+          <t>88412</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLANCA ESTELA </t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORJA </t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3055,10 +3055,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6643577880</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>2296582638</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL ESMERALDA</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3066,42 +3070,42 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19-08-1977</t>
+          <t>05-12-2000</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>GFGFFGEUYRFGUY@GMAIL.COM</t>
+          <t>ELIZABETH.HERRERAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>18-02-2026 11:37:29</t>
+          <t>24-02-2026 17:18:41</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>24-02-2026 12:06:24</t>
+          <t>24-02-2026 17:32:02</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3109,13 +3113,21 @@
           <t>24-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>24-02-2026 17:28:39</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3123,22 +3135,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26140522617050001721</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>MARIA LUISA VALDEZ MAYORGA</t>
-        </is>
-      </c>
+          <t>26140522628100001733</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3155,12 +3159,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>346247</t>
+          <t>346365</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>88412</t>
+          <t>88530</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3170,17 +3174,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t xml:space="preserve">SAMUEL AARON </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t xml:space="preserve">MACARIO </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3190,32 +3194,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2296582638</t>
+          <t>6647589644</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>RESIDENCIAL ESMERALDA</t>
+          <t>PLAYAS ROSARITO</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>05-12-2000</t>
+          <t>08-02-2003</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ELIZABETH.HERRERAS@GMAIL.COM</t>
+          <t>MACARIOSAMUEL7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>24-02-2026 17:18:41</t>
+          <t>25-02-2026 06:48:49</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3240,17 +3244,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>24-02-2026 17:32:02</t>
+          <t>25-02-2026 06:52:37</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>24-02-2026 17:28:39</t>
+          <t>25-02-2026 06:51:27</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3260,7 +3264,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3270,7 +3274,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26140522628100001733</t>
+          <t>26140522645120001756</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3294,12 +3298,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>346365</t>
+          <t>344054</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>88530</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3309,17 +3313,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAMUEL AARON </t>
+          <t>SANDRA LETICIA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACARIO </t>
+          <t xml:space="preserve">CONTRERAS </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t xml:space="preserve">DE SANTIAGO </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3329,79 +3333,67 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6647589644</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>PLAYAS ROSARITO</t>
-        </is>
-      </c>
+          <t>6634313589</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>08-02-2003</t>
+          <t>04-05-2004</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MACARIOSAMUEL7@GMAIL.COM</t>
+          <t>CONTRERASSANDRA149@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>25-02-2026 06:48:49</t>
+          <t>16-02-2026 12:48:08</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>25-02-2026 06:52:37</t>
+          <t>16-02-2026 12:49:38</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>25-02-2026 06:51:27</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3409,36 +3401,36 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26140522645120001756</t>
+          <t>26140522387570001473</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>345993</t>
+          <t>344359</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>88158</t>
+          <t>22176</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3448,17 +3440,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JHOVANNY</t>
+          <t xml:space="preserve">ANTONIO </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BENITEZ</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3468,12 +3460,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6643012921</t>
+          <t>6644048868</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRIV SAN LUCAS </t>
+          <t>FRANCISCO VILLA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3483,17 +3475,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>25-09-1994</t>
+          <t>14-07-1967</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>JHOVANNYTORRESBENITEZ031@GMAIL.COM</t>
+          <t>ZAPATALABFACTURAS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>23-02-2026 18:36:29</t>
+          <t>16-02-2026 20:52:22</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3518,17 +3510,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>23-02-2026 18:41:47</t>
+          <t>16-02-2026 21:13:15</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>23-02-2026 18:40:26</t>
+          <t>16-02-2026 21:11:12</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3548,7 +3540,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26140522596840001685</t>
+          <t>26140522411330001499</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3560,7 +3552,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3572,12 +3564,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>345602</t>
+          <t>344489</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>87767</t>
+          <t>22306</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3587,17 +3579,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MARIA NATIVIDAD</t>
+          <t xml:space="preserve">MICHAEL </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">ROJAS </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t xml:space="preserve">RENTERIA </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3607,12 +3599,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6643774656</t>
+          <t>6648567901</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>FCO I MADERO 6852 -B</t>
+          <t xml:space="preserve">LOMA BONITA </t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3622,17 +3614,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>08-09-2003</t>
+          <t>12-04-2006</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>GUEVARAKINBOYU@GMAIL.COM</t>
+          <t>MACHAELRENTERIAROJAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>22-02-2026 12:04:37</t>
+          <t>17-02-2026 13:55:21</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3657,17 +3649,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>22-02-2026 12:11:16</t>
+          <t>17-02-2026 13:58:26</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>22-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>22-02-2026 12:09:53</t>
+          <t>17-02-2026 13:57:43</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3687,7 +3679,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26140522562650001628</t>
+          <t>26140522428560001519</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3711,12 +3703,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>344364</t>
+          <t>344557</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22181</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3726,17 +3718,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIA </t>
+          <t>MARIO ALBERTO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3746,32 +3738,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6647006311</t>
+          <t>6646691008</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FRANCISCO VILLA 5011</t>
+          <t>FELIX PARRA 203</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>26-02-1977</t>
+          <t>22-10-2000</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>SHAPIS277@GMAIL.COM</t>
+          <t>MARIO.SOTO1403@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>16-02-2026 21:48:29</t>
+          <t>17-02-2026 16:14:15</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3796,17 +3788,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>16-02-2026 21:57:08</t>
+          <t>17-02-2026 16:29:22</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>16-02-2026 21:55:56</t>
+          <t>17-02-2026 16:25:31</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3816,7 +3808,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3826,7 +3818,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26140522411860001500</t>
+          <t>26140522434170001526</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3850,12 +3842,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>344489</t>
+          <t>344794</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3865,17 +3857,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">MICHAEL </t>
+          <t xml:space="preserve">BLANCA ESTELA </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROJAS </t>
+          <t xml:space="preserve">BORJA </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTERIA </t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3885,14 +3877,10 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6648567901</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOMA BONITA </t>
-        </is>
-      </c>
+          <t>6643577880</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3900,64 +3888,56 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>12-04-2006</t>
+          <t>19-08-1977</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>MACHAELRENTERIAROJAS@GMAIL.COM</t>
+          <t>GFGFFGEUYRFGUY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>17-02-2026 13:55:21</t>
+          <t>18-02-2026 11:37:29</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>17-02-2026 13:58:26</t>
+          <t>24-02-2026 12:06:24</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>17-02-2026 13:57:43</t>
-        </is>
-      </c>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3965,36 +3945,44 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26140522428560001519</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26140522617050001721</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>MARIA LUISA VALDEZ MAYORGA</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>344557</t>
+          <t>345993</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>88158</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4004,17 +3992,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MARIO ALBERTO</t>
+          <t>JHOVANNY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>BENITEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4024,12 +4012,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6646691008</t>
+          <t>6643012921</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>FELIX PARRA 203</t>
+          <t xml:space="preserve">PRIV SAN LUCAS </t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4039,17 +4027,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>22-10-2000</t>
+          <t>25-09-1994</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>MARIO.SOTO1403@GMAIL.COM</t>
+          <t>JHOVANNYTORRESBENITEZ031@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>17-02-2026 16:14:15</t>
+          <t>23-02-2026 18:36:29</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4074,17 +4062,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>17-02-2026 16:29:22</t>
+          <t>23-02-2026 18:41:47</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>17-02-2026 16:25:31</t>
+          <t>23-02-2026 18:40:26</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4094,7 +4082,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4104,7 +4092,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26140522434170001526</t>
+          <t>26140522596840001685</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -4116,7 +4104,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4128,12 +4116,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>344054</t>
+          <t>345602</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>87767</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4143,17 +4131,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SANDRA LETICIA</t>
+          <t>MARIA NATIVIDAD</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRERAS </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE SANTIAGO </t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4163,10 +4151,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6634313589</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6643774656</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>FCO I MADERO 6852 -B</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4174,56 +4166,64 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>04-05-2004</t>
+          <t>08-09-2003</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CONTRERASSANDRA149@GMAIL.COM</t>
+          <t>GUEVARAKINBOYU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>16-02-2026 12:48:08</t>
+          <t>22-02-2026 12:04:37</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>16-02-2026 12:49:38</t>
+          <t>22-02-2026 12:11:16</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>22-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>22-02-2026 12:09:53</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4231,19 +4231,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26140522387570001473</t>
+          <t>26140522562650001628</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4255,12 +4255,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>344359</t>
+          <t>345989</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>88154</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANTONIO </t>
+          <t xml:space="preserve">YOSELIN </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t xml:space="preserve">ENCINAS </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>MIRAMONTES</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4290,79 +4290,67 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6644048868</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>FRANCISCO VILLA</t>
-        </is>
-      </c>
+          <t>6644643065</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>14-07-1967</t>
+          <t>24-04-2012</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ZAPATALABFACTURAS@HOTMAIL.COM</t>
+          <t>TANIAMIRA758@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>16-02-2026 20:52:22</t>
+          <t>23-02-2026 18:30:03</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>16-02-2026 21:13:15</t>
+          <t>23-02-2026 18:32:11</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>16-02-2026 21:11:12</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4370,19 +4358,19 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26140522411330001499</t>
+          <t>26140522595960001682</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4394,12 +4382,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>345927</t>
+          <t>345850</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>88092</t>
+          <t>88015</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4409,17 +4397,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LILIA NAYELI</t>
+          <t>ERICKA ISABEL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORTES </t>
+          <t xml:space="preserve">FUENTES </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>OLIVARES</t>
+          <t>HERRAN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4429,12 +4417,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6646572937</t>
+          <t>6642294144</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TAMPICO 3572</t>
+          <t xml:space="preserve">JOSE MA MORELOS </t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4444,17 +4432,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>06-11-1996</t>
+          <t>31-10-1995</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>LILICORTES5@ICLOUD.COM</t>
+          <t>ERICKAFUENTES111@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>23-02-2026 17:36:15</t>
+          <t>23-02-2026 15:51:57</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4479,17 +4467,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>23-02-2026 17:42:37</t>
+          <t>25-02-2026 18:15:35</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>23-02-2026 17:41:36</t>
+          <t>25-02-2026 18:06:31</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4509,10 +4497,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26140522591970001671</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
+          <t>26140522662810001783</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
@@ -4521,24 +4513,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>345989</t>
+          <t>345927</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>88154</t>
+          <t>88092</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4548,17 +4540,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">YOSELIN </t>
+          <t>LILIA NAYELI</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENCINAS </t>
+          <t xml:space="preserve">CORTES </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIRAMONTES</t>
+          <t>OLIVARES</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4568,10 +4560,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6644643065</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>6646572937</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>TAMPICO 3572</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4579,42 +4575,42 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>24-04-2012</t>
+          <t>06-11-1996</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>TANIAMIRA758@GMAIL.COM</t>
+          <t>LILICORTES5@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>23-02-2026 18:30:03</t>
+          <t>23-02-2026 17:36:15</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>23-02-2026 18:32:11</t>
+          <t>23-02-2026 17:42:37</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4622,13 +4618,21 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:41:36</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4636,36 +4640,36 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26140522595960001682</t>
+          <t>26140522591970001671</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>345850</t>
+          <t>346512</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>88015</t>
+          <t>88677</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4675,17 +4679,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ERICKA ISABEL</t>
+          <t>GLENDA ACEVER</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">FUENTES </t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HERRAN</t>
+          <t>AVITIA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4695,14 +4699,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6642294144</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JOSE MA MORELOS </t>
-        </is>
-      </c>
+          <t>6641171074</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4710,42 +4710,42 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>31-10-1995</t>
+          <t>07-10-1997</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ERICKAFUENTES111@GMAIL.COM</t>
+          <t>GLEN412@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>23-02-2026 15:51:57</t>
+          <t>25-02-2026 15:39:54</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>25-02-2026 18:15:35</t>
+          <t>25-02-2026 15:41:38</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4753,21 +4753,13 @@
           <t>25-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>25-02-2026 18:06:31</t>
-        </is>
-      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4775,40 +4767,36 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26140522662810001783</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26140522655870001771</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>346512</t>
+          <t>346001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>88677</t>
+          <t>88166</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4818,17 +4806,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GLENDA ACEVER</t>
+          <t>TANIA LISSET</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AVITIA</t>
+          <t>MIRAMONTES</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4838,10 +4826,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6641171074</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>6631184694</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>PRIV SAN LUCAS 4251</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4849,56 +4841,64 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>07-10-1997</t>
+          <t>06-05-1998</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>GLEN412@GMAIL.COM</t>
+          <t>TANIAR758@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>25-02-2026 15:39:54</t>
+          <t>23-02-2026 18:46:02</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>25-02-2026 15:41:38</t>
+          <t>23-02-2026 18:52:25</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:50:28</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4906,24 +4906,24 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26140522655870001771</t>
+          <t>26140522597500001688</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>248471</t>
+          <t>340192</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>45975</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,27 +732,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AXEL</t>
+          <t>BRANDON</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CABAÑAS</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>DELGADILLO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6634050813</t>
+          <t>6198156515</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -763,17 +763,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>07-06-2000</t>
+          <t>01-08-2010</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>AXELCARDENASCA@GMAIL.COM</t>
+          <t>BRANDONSILVA244@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>27-07-2024 08:36:55</t>
+          <t>02-02-2026 14:49:52</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>09-02-2026 10:49:17</t>
+          <t>04-02-2026 09:59:45</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -820,36 +820,40 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26090522188180001350</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>26140522071170001067</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>340192</t>
+          <t>340280</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>18098</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,87 +863,95 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BRANDON</t>
+          <t>ROSA VALERIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DELGADILLO</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6642708866</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ESTRELLA DEL ORIENTE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>02-05-1997</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>VALERIA_ROGERS@LIVE.COM</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:40:54</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:49:59</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:48:59</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>6198156515</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>01-08-2010</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>BRANDONSILVA244@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>02-02-2026 14:49:52</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>COBACH $399</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>04-02-2026 09:59:45</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -947,18 +959,14 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26140522071170001067</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26140522017370000999</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -975,12 +983,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>340280</t>
+          <t>248471</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18098</t>
+          <t>45975</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ROSA VALERIA</t>
+          <t>AXEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CABAÑAS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1010,75 +1018,67 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6642708866</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ESTRELLA DEL ORIENTE</t>
-        </is>
-      </c>
+          <t>6634050813</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>02-05-1997</t>
+          <t>07-06-2000</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>VALERIA_ROGERS@LIVE.COM</t>
+          <t>AXELCARDENASCA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-02-2026 16:40:54</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>27-07-2024 08:36:55</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-02-2026 16:49:59</t>
+          <t>09-02-2026 10:49:17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>02-02-2026 16:48:59</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1086,24 +1086,24 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26140522017370000999</t>
+          <t>26090522188180001350</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>341963</t>
+          <t>342419</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUZ DEL CARMEN </t>
+          <t xml:space="preserve">IVIS MARLEN </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>ROCHIN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>SAUCEDO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6644151535</t>
+          <t>6642338869</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MONTE TRES PICOS</t>
+          <t>AV DEL RUBI</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1434,17 +1434,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28-12-1983</t>
+          <t>03-11-1994</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>LUZ28DOMI@GMAIL.COM</t>
+          <t>IROCHINSAUCEDO@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>08-02-2026 15:03:16</t>
+          <t>09-02-2026 19:02:55</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>08-02-2026 15:10:44</t>
+          <t>09-02-2026 19:11:27</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>08-02-2026 15:08:28</t>
+          <t>09-02-2026 19:10:03</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26140522173200001196</t>
+          <t>26140522209920001244</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1519,12 +1519,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>342360</t>
+          <t>342533</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20178</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MARIA DEL ROCIO</t>
+          <t>MARIBEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">GALVAN </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6631107103</t>
+          <t>6645692934</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PRIV GARDENIA</t>
+          <t xml:space="preserve">NUEVA AURORA </t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1569,17 +1569,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>24-01-1985</t>
+          <t>24-01-2001</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CESARIO_GARCIA@HOTMAIL.COM</t>
+          <t>MARELGALVAN53@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>09-02-2026 17:54:42</t>
+          <t>10-02-2026 07:33:18</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1600,17 +1600,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>09-02-2026 18:02:59</t>
+          <t>10-02-2026 07:41:17</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>09-02-2026 18:01:06</t>
+          <t>10-02-2026 07:37:20</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26140522205100001233</t>
+          <t>26140522224470001260</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1654,12 +1654,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340367</t>
+          <t>342360</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUANA CLAUDIA </t>
+          <t>MARIA DEL ROCIO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CAMACENA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GRACIDA</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1689,10 +1689,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2285111160</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6631107103</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PRIV GARDENIA</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1700,56 +1704,60 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22-06-1977</t>
+          <t>24-01-1985</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CAMACENAJUANA5@GMAIL.COM</t>
+          <t>CESARIO_GARCIA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-02-2026 19:31:33</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:54:42</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-02-2026 19:39:24</t>
+          <t>09-02-2026 18:02:59</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>09-02-2026 18:01:06</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1757,19 +1765,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26140522022420001008</t>
+          <t>26140522205100001233</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1781,12 +1789,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>344016</t>
+          <t>341963</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21833</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1796,17 +1804,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA KAREN </t>
+          <t xml:space="preserve">LUZ DEL CARMEN </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALCIDO </t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MAGAÑA</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1816,12 +1824,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6646105596</t>
+          <t>6644151535</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PANAMERICANO </t>
+          <t>MONTE TRES PICOS</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1831,24 +1839,20 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26-06-1993</t>
+          <t>28-12-1983</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ANAMAGAÑA371@GMAIL.COM</t>
+          <t>LUZ28DOMI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>16-02-2026 11:21:32</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>08-02-2026 15:03:16</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1866,17 +1870,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>16-02-2026 11:27:59</t>
+          <t>08-02-2026 15:10:44</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>08-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>16-02-2026 11:26:40</t>
+          <t>08-02-2026 15:08:28</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1896,7 +1900,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26140522385390001470</t>
+          <t>26140522173200001196</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1908,24 +1912,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>342724</t>
+          <t>340367</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>18185</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1935,17 +1939,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>JUAN JOSE</t>
+          <t xml:space="preserve">JUANA CLAUDIA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DUEÑAS</t>
+          <t>CAMACENA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>GRACIDA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1955,75 +1959,67 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6633343468</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>GARDEN 24241</t>
-        </is>
-      </c>
+          <t>2285111160</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>09-12-1997</t>
+          <t>22-06-1977</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>JUANJOSEDUENAS85@GMAIL.COM</t>
+          <t>CAMACENAJUANA5@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>10-02-2026 16:51:42</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>02-02-2026 19:31:33</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>10-02-2026 16:59:24</t>
+          <t>02-02-2026 19:39:24</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>10-02-2026 16:58:12</t>
-        </is>
-      </c>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2031,14 +2027,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26140522238120001282</t>
+          <t>26140522022420001008</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2055,12 +2051,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>344573</t>
+          <t>346001</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22390</t>
+          <t>88166</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2070,17 +2066,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERONICA </t>
+          <t>TANIA LISSET</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ARAOS</t>
+          <t>MIRAMONTES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2090,12 +2086,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6612034182</t>
+          <t>6631184694</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MIGUEL ROMERO 6012</t>
+          <t>PRIV SAN LUCAS 4251</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2105,17 +2101,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>20-08-2000</t>
+          <t>06-05-1998</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PEREZVERONICA1204@GMAIL.COM</t>
+          <t>TANIAR758@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>17-02-2026 16:35:43</t>
+          <t>23-02-2026 18:46:02</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2140,17 +2136,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>17-02-2026 16:58:54</t>
+          <t>23-02-2026 18:52:25</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>17-02-2026 16:58:10</t>
+          <t>23-02-2026 18:50:28</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2160,7 +2156,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2170,7 +2166,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26140522435860001527</t>
+          <t>26140522597500001688</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2182,7 +2178,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2194,12 +2190,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>343355</t>
+          <t>344573</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2209,17 +2205,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ROBERTO TRINIDAD</t>
+          <t xml:space="preserve">VERONICA </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAREZ </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ABARCA</t>
+          <t>ARAOS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2229,35 +2225,39 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6634586390</t>
+          <t>6612034182</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EMILIANO ZAPATA</t>
+          <t>MIGUEL ROMERO 6012</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>18-08-1985</t>
+          <t>20-08-2000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ROBERTODALIA9852@GMAIL.COM</t>
+          <t>PEREZVERONICA1204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>12-02-2026 17:57:31</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>17-02-2026 16:35:43</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2275,17 +2275,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>12-02-2026 18:06:53</t>
+          <t>17-02-2026 16:58:54</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>12-02-2026 18:05:12</t>
+          <t>17-02-2026 16:58:10</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26140522301540001381</t>
+          <t>26140522435860001527</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2472,12 +2472,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>342419</t>
+          <t>342724</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2487,17 +2487,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">IVIS MARLEN </t>
+          <t>JUAN JOSE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ROCHIN</t>
+          <t>DUEÑAS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SAUCEDO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2507,32 +2507,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6642338869</t>
+          <t>6633343468</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AV DEL RUBI</t>
+          <t>GARDEN 24241</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>03-11-1994</t>
+          <t>09-12-1997</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>IROCHINSAUCEDO@ICLOUD.COM</t>
+          <t>JUANJOSEDUENAS85@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>09-02-2026 19:02:55</t>
+          <t>10-02-2026 16:51:42</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2553,17 +2553,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>09-02-2026 19:11:27</t>
+          <t>10-02-2026 16:59:24</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>09-02-2026 19:10:03</t>
+          <t>10-02-2026 16:58:12</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26140522209920001244</t>
+          <t>26140522238120001282</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2607,12 +2607,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>342533</t>
+          <t>344016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>21833</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2622,17 +2622,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MARIBEL</t>
+          <t xml:space="preserve">ANA KAREN </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALVAN </t>
+          <t xml:space="preserve">SALCIDO </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILAR </t>
+          <t>MAGAÑA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6645692934</t>
+          <t>6646105596</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NUEVA AURORA </t>
+          <t xml:space="preserve">PANAMERICANO </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2657,20 +2657,24 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>24-01-2001</t>
+          <t>26-06-1993</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MARELGALVAN53@GMAIL.COM</t>
+          <t>ANAMAGAÑA371@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>10-02-2026 07:33:18</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>16-02-2026 11:21:32</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2688,17 +2692,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>10-02-2026 07:41:17</t>
+          <t>16-02-2026 11:27:59</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>10-02-2026 07:37:20</t>
+          <t>16-02-2026 11:26:40</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2718,7 +2722,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26140522224470001260</t>
+          <t>26140522385390001470</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2730,24 +2734,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>344493</t>
+          <t>343355</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2757,17 +2761,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BIRIDIANA</t>
+          <t>ROBERTO TRINIDAD</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOSA </t>
+          <t xml:space="preserve">JUAREZ </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MONJARAZ</t>
+          <t>ABARCA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2777,39 +2781,35 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6632474982</t>
+          <t>6634586390</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAS CUMBRES </t>
+          <t>EMILIANO ZAPATA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>20-03-2006</t>
+          <t>18-08-1985</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>LOSAMONJARAZBIRIDIANA06@GMAIL.COM</t>
+          <t>ROBERTODALIA9852@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17-02-2026 14:01:11</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 17:57:31</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2827,17 +2827,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>17-02-2026 14:06:09</t>
+          <t>12-02-2026 18:06:53</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>17-02-2026 14:04:10</t>
+          <t>12-02-2026 18:05:12</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26140522428740001520</t>
+          <t>26140522301540001381</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2881,12 +2881,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>344364</t>
+          <t>344493</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22181</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIA </t>
+          <t>BIRIDIANA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t xml:space="preserve">LOSA </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MONJARAZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6647006311</t>
+          <t>6632474982</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>FRANCISCO VILLA 5011</t>
+          <t xml:space="preserve">LAS CUMBRES </t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2931,17 +2931,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>26-02-1977</t>
+          <t>20-03-2006</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>SHAPIS277@GMAIL.COM</t>
+          <t>LOSAMONJARAZBIRIDIANA06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>16-02-2026 21:48:29</t>
+          <t>17-02-2026 14:01:11</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>16-02-2026 21:57:08</t>
+          <t>17-02-2026 14:06:09</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>16-02-2026 21:55:56</t>
+          <t>17-02-2026 14:04:10</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26140522411860001500</t>
+          <t>26140522428740001520</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3298,12 +3298,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>344054</t>
+          <t>344364</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>22181</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3313,17 +3313,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SANDRA LETICIA</t>
+          <t xml:space="preserve">ELIA </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRERAS </t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE SANTIAGO </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3333,10 +3333,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6634313589</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6647006311</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>FRANCISCO VILLA 5011</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3344,42 +3348,42 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>04-05-2004</t>
+          <t>26-02-1977</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CONTRERASSANDRA149@GMAIL.COM</t>
+          <t>SHAPIS277@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>16-02-2026 12:48:08</t>
+          <t>16-02-2026 21:48:29</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>16-02-2026 12:49:38</t>
+          <t>16-02-2026 21:57:08</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3387,13 +3391,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>16-02-2026 21:55:56</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3401,14 +3413,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26140522387570001473</t>
+          <t>26140522411860001500</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3425,12 +3437,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>344359</t>
+          <t>344794</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3440,17 +3452,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANTONIO </t>
+          <t xml:space="preserve">BLANCA ESTELA </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t xml:space="preserve">BORJA </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3460,79 +3472,67 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6644048868</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>FRANCISCO VILLA</t>
-        </is>
-      </c>
+          <t>6643577880</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>14-07-1967</t>
+          <t>19-08-1977</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ZAPATALABFACTURAS@HOTMAIL.COM</t>
+          <t>GFGFFGEUYRFGUY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>16-02-2026 20:52:22</t>
+          <t>18-02-2026 11:37:29</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>16-02-2026 21:13:15</t>
+          <t>24-02-2026 12:06:24</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>16-02-2026 21:11:12</t>
-        </is>
-      </c>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3540,24 +3540,32 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26140522411330001499</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+          <t>26140522617050001721</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>MARIA LUISA VALDEZ MAYORGA</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -3842,12 +3850,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>344794</t>
+          <t>345602</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>22611</t>
+          <t>87767</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3857,17 +3865,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLANCA ESTELA </t>
+          <t>MARIA NATIVIDAD</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORJA </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3877,10 +3885,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6643577880</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>6643774656</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>FCO I MADERO 6852 -B</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3888,56 +3900,64 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19-08-1977</t>
+          <t>08-09-2003</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>GFGFFGEUYRFGUY@GMAIL.COM</t>
+          <t>GUEVARAKINBOYU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>18-02-2026 11:37:29</t>
+          <t>22-02-2026 12:04:37</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>24-02-2026 12:06:24</t>
+          <t>22-02-2026 12:11:16</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>22-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>22-02-2026 12:09:53</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3945,44 +3965,36 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26140522617050001721</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>MARIA LUISA VALDEZ MAYORGA</t>
-        </is>
-      </c>
+          <t>26140522562650001628</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>345993</t>
+          <t>344359</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>88158</t>
+          <t>22176</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3992,17 +4004,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JHOVANNY</t>
+          <t xml:space="preserve">ANTONIO </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BENITEZ</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4012,12 +4024,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6643012921</t>
+          <t>6644048868</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRIV SAN LUCAS </t>
+          <t>FRANCISCO VILLA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4027,17 +4039,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>25-09-1994</t>
+          <t>14-07-1967</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>JHOVANNYTORRESBENITEZ031@GMAIL.COM</t>
+          <t>ZAPATALABFACTURAS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>23-02-2026 18:36:29</t>
+          <t>16-02-2026 20:52:22</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4062,17 +4074,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>23-02-2026 18:41:47</t>
+          <t>16-02-2026 21:13:15</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>23-02-2026 18:40:26</t>
+          <t>16-02-2026 21:11:12</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4092,7 +4104,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26140522596840001685</t>
+          <t>26140522411330001499</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -4104,7 +4116,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4116,12 +4128,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>345602</t>
+          <t>344054</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>87767</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4131,17 +4143,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MARIA NATIVIDAD</t>
+          <t>SANDRA LETICIA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">CONTRERAS </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t xml:space="preserve">DE SANTIAGO </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4151,14 +4163,10 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6643774656</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>FCO I MADERO 6852 -B</t>
-        </is>
-      </c>
+          <t>6634313589</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4166,64 +4174,56 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>08-09-2003</t>
+          <t>04-05-2004</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>GUEVARAKINBOYU@GMAIL.COM</t>
+          <t>CONTRERASSANDRA149@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>22-02-2026 12:04:37</t>
+          <t>16-02-2026 12:48:08</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>22-02-2026 12:11:16</t>
+          <t>16-02-2026 12:49:38</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>22-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>22-02-2026 12:09:53</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4231,19 +4231,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26140522562650001628</t>
+          <t>26140522387570001473</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4255,12 +4255,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>345989</t>
+          <t>345927</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>88154</t>
+          <t>88092</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">YOSELIN </t>
+          <t>LILIA NAYELI</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENCINAS </t>
+          <t xml:space="preserve">CORTES </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MIRAMONTES</t>
+          <t>OLIVARES</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4290,10 +4290,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6644643065</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>6646572937</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TAMPICO 3572</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4301,42 +4305,42 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>24-04-2012</t>
+          <t>06-11-1996</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TANIAMIRA758@GMAIL.COM</t>
+          <t>LILICORTES5@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>23-02-2026 18:30:03</t>
+          <t>23-02-2026 17:36:15</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>23-02-2026 18:32:11</t>
+          <t>23-02-2026 17:42:37</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -4344,13 +4348,21 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>23-02-2026 17:41:36</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4358,36 +4370,36 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26140522595960001682</t>
+          <t>26140522591970001671</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>345850</t>
+          <t>346950</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>88015</t>
+          <t>89115</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4397,17 +4409,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ERICKA ISABEL</t>
+          <t xml:space="preserve">EDGAR FABIAN </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">FUENTES </t>
+          <t>GALLEGOS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HERRAN</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4417,32 +4429,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6642294144</t>
+          <t>6645182446</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE MA MORELOS </t>
+          <t>LOMA BONITA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>31-10-1995</t>
+          <t>18-08-1989</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ERICKAFUENTES111@GMAIL.COM</t>
+          <t>EDGARFAB123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>23-02-2026 15:51:57</t>
+          <t>27-02-2026 13:48:12</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4467,17 +4479,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>25-02-2026 18:15:35</t>
+          <t>27-02-2026 13:53:10</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>25-02-2026 18:06:31</t>
+          <t>27-02-2026 13:52:34</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4497,14 +4509,10 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26140522662810001783</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26140522711730001849</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
@@ -4513,24 +4521,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>345927</t>
+          <t>346979</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>88092</t>
+          <t>89144</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4540,17 +4548,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LILIA NAYELI</t>
+          <t>ELIAM</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">CORTES </t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OLIVARES</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4560,79 +4568,67 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6646572937</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>TAMPICO 3572</t>
-        </is>
-      </c>
+          <t>6648537656</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>06-11-1996</t>
+          <t>28-12-2008</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>LILICORTES5@ICLOUD.COM</t>
+          <t>ELIAMTIJ2017@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>23-02-2026 17:36:15</t>
+          <t>27-02-2026 15:30:07</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>23-02-2026 17:42:37</t>
+          <t>27-02-2026 15:32:24</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>23-02-2026 17:41:36</t>
-        </is>
-      </c>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4640,36 +4636,36 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26140522591970001671</t>
+          <t>26140522716110001855</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>346512</t>
+          <t>345993</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>88677</t>
+          <t>88158</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4679,17 +4675,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GLENDA ACEVER</t>
+          <t>JHOVANNY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AVITIA</t>
+          <t>BENITEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4699,67 +4695,79 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6641171074</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6643012921</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRIV SAN LUCAS </t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>07-10-1997</t>
+          <t>25-09-1994</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>GLEN412@GMAIL.COM</t>
+          <t>JHOVANNYTORRESBENITEZ031@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>25-02-2026 15:39:54</t>
+          <t>23-02-2026 18:36:29</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>25-02-2026 15:41:38</t>
+          <t>23-02-2026 18:41:47</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>23-02-2026 18:40:26</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4767,36 +4775,36 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26140522655870001771</t>
+          <t>26140522596840001685</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>346001</t>
+          <t>345989</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>88166</t>
+          <t>88154</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4806,12 +4814,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TANIA LISSET</t>
+          <t xml:space="preserve">YOSELIN </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t xml:space="preserve">ENCINAS </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4826,14 +4834,10 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6631184694</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>PRIV SAN LUCAS 4251</t>
-        </is>
-      </c>
+          <t>6644643065</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4841,42 +4845,42 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>06-05-1998</t>
+          <t>24-04-2012</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>TANIAR758@GMAIL.COM</t>
+          <t>TANIAMIRA758@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>23-02-2026 18:46:02</t>
+          <t>23-02-2026 18:30:03</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>23-02-2026 18:52:25</t>
+          <t>23-02-2026 18:32:11</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4884,21 +4888,13 @@
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>23-02-2026 18:50:28</t>
-        </is>
-      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4906,22 +4902,431 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26140522597500001688</t>
+          <t>26140522595960001682</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Etzon  Pizano Cazares</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>345850</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>88015</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ERICKA ISABEL</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FUENTES </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>HERRAN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6642294144</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE MA MORELOS </t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>31-10-1995</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>ERICKAFUENTES111@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:51:57</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>25-02-2026 18:15:35</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>25-02-2026 18:06:31</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26140522662810001783</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>346944</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>89109</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MONICA GEORGINA </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARTINEZ </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAGAÑA </t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>4341160435</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOMA BONITA </t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>22-10-1997</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>EFGM757@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>27-02-2026 13:34:59</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>27-02-2026 13:45:08</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>27-02-2026 13:44:23</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26140522711590001848</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>346512</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>88677</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>GLENDA ACEVER</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CARBAJAL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>AVITIA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6641171074</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>07-10-1997</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>GLEN412@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>25-02-2026 15:39:54</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>25-02-2026 15:41:38</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26140522655870001771</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
         <is>
           <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
@@ -1789,12 +1789,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>341963</t>
+          <t>340367</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>18185</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,17 +1804,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUZ DEL CARMEN </t>
+          <t xml:space="preserve">JUANA CLAUDIA </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>CAMACENA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>GRACIDA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1824,14 +1824,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6644151535</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>MONTE TRES PICOS</t>
-        </is>
-      </c>
+          <t>2285111160</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1839,60 +1835,56 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>28-12-1983</t>
+          <t>22-06-1977</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>LUZ28DOMI@GMAIL.COM</t>
+          <t>CAMACENAJUANA5@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>08-02-2026 15:03:16</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>02-02-2026 19:31:33</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>08-02-2026 15:10:44</t>
+          <t>02-02-2026 19:39:24</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>08-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>08-02-2026 15:08:28</t>
-        </is>
-      </c>
+          <t>02-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1900,14 +1892,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26140522173200001196</t>
+          <t>26140522022420001008</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1924,12 +1916,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340367</t>
+          <t>341963</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18185</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1939,17 +1931,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUANA CLAUDIA </t>
+          <t xml:space="preserve">LUZ DEL CARMEN </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CAMACENA</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GRACIDA</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1959,10 +1951,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2285111160</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6644151535</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MONTE TRES PICOS</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1970,56 +1966,60 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>22-06-1977</t>
+          <t>28-12-1983</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CAMACENAJUANA5@GMAIL.COM</t>
+          <t>LUZ28DOMI@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-02-2026 19:31:33</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>08-02-2026 15:03:16</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-02-2026 19:39:24</t>
+          <t>08-02-2026 15:10:44</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>08-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>08-02-2026 15:08:28</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2027,14 +2027,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26140522022420001008</t>
+          <t>26140522173200001196</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>346001</t>
+          <t>344573</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>88166</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TANIA LISSET</t>
+          <t xml:space="preserve">VERONICA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MIRAMONTES</t>
+          <t>ARAOS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6631184694</t>
+          <t>6612034182</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PRIV SAN LUCAS 4251</t>
+          <t>MIGUEL ROMERO 6012</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2101,17 +2101,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>06-05-1998</t>
+          <t>20-08-2000</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>TANIAR758@GMAIL.COM</t>
+          <t>PEREZVERONICA1204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>23-02-2026 18:46:02</t>
+          <t>17-02-2026 16:35:43</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2136,17 +2136,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>23-02-2026 18:52:25</t>
+          <t>17-02-2026 16:58:54</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>23-02-2026 18:50:28</t>
+          <t>17-02-2026 16:58:10</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26140522597500001688</t>
+          <t>26140522435860001527</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2190,12 +2190,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>344573</t>
+          <t>346001</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22390</t>
+          <t>88166</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2205,17 +2205,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERONICA </t>
+          <t>TANIA LISSET</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ARAOS</t>
+          <t>MIRAMONTES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6612034182</t>
+          <t>6631184694</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MIGUEL ROMERO 6012</t>
+          <t>PRIV SAN LUCAS 4251</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2240,17 +2240,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>20-08-2000</t>
+          <t>06-05-1998</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PEREZVERONICA1204@GMAIL.COM</t>
+          <t>TANIAR758@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>17-02-2026 16:35:43</t>
+          <t>23-02-2026 18:46:02</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2275,17 +2275,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>17-02-2026 16:58:54</t>
+          <t>23-02-2026 18:52:25</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>17-02-2026 16:58:10</t>
+          <t>23-02-2026 18:50:28</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26140522435860001527</t>
+          <t>26140522597500001688</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2607,12 +2607,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>344016</t>
+          <t>343355</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21833</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2622,17 +2622,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA KAREN </t>
+          <t>ROBERTO TRINIDAD</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALCIDO </t>
+          <t xml:space="preserve">JUAREZ </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MAGAÑA</t>
+          <t>ABARCA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2642,39 +2642,35 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6646105596</t>
+          <t>6634586390</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">PANAMERICANO </t>
+          <t>EMILIANO ZAPATA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26-06-1993</t>
+          <t>18-08-1985</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ANAMAGAÑA371@GMAIL.COM</t>
+          <t>ROBERTODALIA9852@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>16-02-2026 11:21:32</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 17:57:31</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2692,17 +2688,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>16-02-2026 11:27:59</t>
+          <t>12-02-2026 18:06:53</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>16-02-2026 11:26:40</t>
+          <t>12-02-2026 18:05:12</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2722,7 +2718,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26140522385390001470</t>
+          <t>26140522301540001381</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2734,24 +2730,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>343355</t>
+          <t>344016</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>21833</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2761,17 +2757,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ROBERTO TRINIDAD</t>
+          <t xml:space="preserve">ANA KAREN </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAREZ </t>
+          <t xml:space="preserve">SALCIDO </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ABARCA</t>
+          <t>MAGAÑA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2781,35 +2777,39 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6634586390</t>
+          <t>6646105596</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>EMILIANO ZAPATA</t>
+          <t xml:space="preserve">PANAMERICANO </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18-08-1985</t>
+          <t>26-06-1993</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ROBERTODALIA9852@GMAIL.COM</t>
+          <t>ANAMAGAÑA371@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>12-02-2026 17:57:31</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>16-02-2026 11:21:32</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2827,17 +2827,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>12-02-2026 18:06:53</t>
+          <t>16-02-2026 11:27:59</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>12-02-2026 18:05:12</t>
+          <t>16-02-2026 11:26:40</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26140522301540001381</t>
+          <t>26140522385390001470</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2869,24 +2869,24 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>344493</t>
+          <t>346247</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22310</t>
+          <t>88412</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BIRIDIANA</t>
+          <t>ELIZABETH</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOSA </t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MONJARAZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6632474982</t>
+          <t>2296582638</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAS CUMBRES </t>
+          <t>RESIDENCIAL ESMERALDA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2931,17 +2931,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20-03-2006</t>
+          <t>05-12-2000</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>LOSAMONJARAZBIRIDIANA06@GMAIL.COM</t>
+          <t>ELIZABETH.HERRERAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>17-02-2026 14:01:11</t>
+          <t>24-02-2026 17:18:41</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>17-02-2026 14:06:09</t>
+          <t>24-02-2026 17:32:02</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>17-02-2026 14:04:10</t>
+          <t>24-02-2026 17:28:39</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26140522428740001520</t>
+          <t>26140522628100001733</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3008,24 +3008,24 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>346247</t>
+          <t>346365</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>88412</t>
+          <t>88530</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t xml:space="preserve">SAMUEL AARON </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t xml:space="preserve">MACARIO </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3055,32 +3055,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2296582638</t>
+          <t>6647589644</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>RESIDENCIAL ESMERALDA</t>
+          <t>PLAYAS ROSARITO</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>05-12-2000</t>
+          <t>08-02-2003</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ELIZABETH.HERRERAS@GMAIL.COM</t>
+          <t>MACARIOSAMUEL7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>24-02-2026 17:18:41</t>
+          <t>25-02-2026 06:48:49</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3105,17 +3105,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>24-02-2026 17:32:02</t>
+          <t>25-02-2026 06:52:37</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>24-02-2026 17:28:39</t>
+          <t>25-02-2026 06:51:27</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26140522628100001733</t>
+          <t>26140522645120001756</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3159,12 +3159,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>346365</t>
+          <t>344364</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>88530</t>
+          <t>22181</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3174,17 +3174,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAMUEL AARON </t>
+          <t xml:space="preserve">ELIA </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">MACARIO </t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3194,32 +3194,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6647589644</t>
+          <t>6647006311</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PLAYAS ROSARITO</t>
+          <t>FRANCISCO VILLA 5011</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>08-02-2003</t>
+          <t>26-02-1977</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MACARIOSAMUEL7@GMAIL.COM</t>
+          <t>SHAPIS277@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>25-02-2026 06:48:49</t>
+          <t>16-02-2026 21:48:29</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3244,17 +3244,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>25-02-2026 06:52:37</t>
+          <t>16-02-2026 21:57:08</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>25-02-2026 06:51:27</t>
+          <t>16-02-2026 21:55:56</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26140522645120001756</t>
+          <t>26140522411860001500</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3286,24 +3286,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>344364</t>
+          <t>344493</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22181</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3313,17 +3313,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIA </t>
+          <t>BIRIDIANA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t xml:space="preserve">LOSA </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MONJARAZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6647006311</t>
+          <t>6632474982</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>FRANCISCO VILLA 5011</t>
+          <t xml:space="preserve">LAS CUMBRES </t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3348,17 +3348,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>26-02-1977</t>
+          <t>20-03-2006</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SHAPIS277@GMAIL.COM</t>
+          <t>LOSAMONJARAZBIRIDIANA06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>16-02-2026 21:48:29</t>
+          <t>17-02-2026 14:01:11</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>16-02-2026 21:57:08</t>
+          <t>17-02-2026 14:06:09</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>16-02-2026 21:55:56</t>
+          <t>17-02-2026 14:04:10</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26140522411860001500</t>
+          <t>26140522428740001520</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>344794</t>
+          <t>344489</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22611</t>
+          <t>22306</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3452,17 +3452,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">BLANCA ESTELA </t>
+          <t xml:space="preserve">MICHAEL </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">BORJA </t>
+          <t xml:space="preserve">ROJAS </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t xml:space="preserve">RENTERIA </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3472,10 +3472,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6643577880</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6648567901</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOMA BONITA </t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3483,56 +3487,64 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19-08-1977</t>
+          <t>12-04-2006</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>GFGFFGEUYRFGUY@GMAIL.COM</t>
+          <t>MACHAELRENTERIAROJAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>18-02-2026 11:37:29</t>
+          <t>17-02-2026 13:55:21</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>24-02-2026 12:06:24</t>
+          <t>17-02-2026 13:58:26</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>17-02-2026 13:57:43</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3540,44 +3552,36 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26140522617050001721</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>MARIA LUISA VALDEZ MAYORGA</t>
-        </is>
-      </c>
+          <t>26140522428560001519</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>344489</t>
+          <t>344557</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3587,17 +3591,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">MICHAEL </t>
+          <t>MARIO ALBERTO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROJAS </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTERIA </t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3607,32 +3611,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6648567901</t>
+          <t>6646691008</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOMA BONITA </t>
+          <t>FELIX PARRA 203</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12-04-2006</t>
+          <t>22-10-2000</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MACHAELRENTERIAROJAS@GMAIL.COM</t>
+          <t>MARIO.SOTO1403@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>17-02-2026 13:55:21</t>
+          <t>17-02-2026 16:14:15</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3657,7 +3661,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>17-02-2026 13:58:26</t>
+          <t>17-02-2026 16:29:22</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3667,7 +3671,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>17-02-2026 13:57:43</t>
+          <t>17-02-2026 16:25:31</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3687,7 +3691,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26140522428560001519</t>
+          <t>26140522434170001526</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3699,7 +3703,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3711,12 +3715,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>344557</t>
+          <t>344794</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3726,17 +3730,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MARIO ALBERTO</t>
+          <t xml:space="preserve">BLANCA ESTELA </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t xml:space="preserve">BORJA </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3746,79 +3750,67 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6646691008</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>FELIX PARRA 203</t>
-        </is>
-      </c>
+          <t>6643577880</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>22-10-2000</t>
+          <t>19-08-1977</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>MARIO.SOTO1403@GMAIL.COM</t>
+          <t>GFGFFGEUYRFGUY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>17-02-2026 16:14:15</t>
+          <t>18-02-2026 11:37:29</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>17-02-2026 16:29:22</t>
+          <t>24-02-2026 12:06:24</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>17-02-2026 16:25:31</t>
-        </is>
-      </c>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3826,36 +3818,44 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26140522434170001526</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>26140522617050001721</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>MARIA LUISA VALDEZ MAYORGA</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>345602</t>
+          <t>344359</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>87767</t>
+          <t>22176</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3865,17 +3865,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MARIA NATIVIDAD</t>
+          <t xml:space="preserve">ANTONIO </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GUEVARA</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3885,32 +3885,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6643774656</t>
+          <t>6644048868</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>FCO I MADERO 6852 -B</t>
+          <t>FRANCISCO VILLA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>08-09-2003</t>
+          <t>14-07-1967</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>GUEVARAKINBOYU@GMAIL.COM</t>
+          <t>ZAPATALABFACTURAS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>22-02-2026 12:04:37</t>
+          <t>16-02-2026 20:52:22</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3935,17 +3935,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>22-02-2026 12:11:16</t>
+          <t>16-02-2026 21:13:15</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>22-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>22-02-2026 12:09:53</t>
+          <t>16-02-2026 21:11:12</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26140522562650001628</t>
+          <t>26140522411330001499</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3989,12 +3989,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>344359</t>
+          <t>344054</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22176</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4004,17 +4004,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANTONIO </t>
+          <t>SANDRA LETICIA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t xml:space="preserve">CONTRERAS </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t xml:space="preserve">DE SANTIAGO </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4024,57 +4024,53 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6644048868</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>FRANCISCO VILLA</t>
-        </is>
-      </c>
+          <t>6634313589</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>14-07-1967</t>
+          <t>04-05-2004</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ZAPATALABFACTURAS@HOTMAIL.COM</t>
+          <t>CONTRERASSANDRA149@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>16-02-2026 20:52:22</t>
+          <t>16-02-2026 12:48:08</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>16-02-2026 21:13:15</t>
+          <t>16-02-2026 12:49:38</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4082,21 +4078,13 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>16-02-2026 21:11:12</t>
-        </is>
-      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4104,14 +4092,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26140522411330001499</t>
+          <t>26140522387570001473</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4128,12 +4116,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>344054</t>
+          <t>345602</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>87767</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4143,17 +4131,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SANDRA LETICIA</t>
+          <t>MARIA NATIVIDAD</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONTRERAS </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE SANTIAGO </t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4163,10 +4151,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6634313589</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6643774656</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>FCO I MADERO 6852 -B</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4174,56 +4166,64 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>04-05-2004</t>
+          <t>08-09-2003</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CONTRERASSANDRA149@GMAIL.COM</t>
+          <t>GUEVARAKINBOYU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>16-02-2026 12:48:08</t>
+          <t>22-02-2026 12:04:37</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>16-02-2026 12:49:38</t>
+          <t>22-02-2026 12:11:16</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>22-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>22-02-2026 12:09:53</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4231,19 +4231,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26140522387570001473</t>
+          <t>26140522562650001628</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4394,12 +4394,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>346950</t>
+          <t>345993</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>89115</t>
+          <t>88158</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4409,17 +4409,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDGAR FABIAN </t>
+          <t>JHOVANNY</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GALLEGOS</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>BENITEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6645182446</t>
+          <t>6643012921</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LOMA BONITA</t>
+          <t xml:space="preserve">PRIV SAN LUCAS </t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4444,17 +4444,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18-08-1989</t>
+          <t>25-09-1994</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>EDGARFAB123@GMAIL.COM</t>
+          <t>JHOVANNYTORRESBENITEZ031@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>27-02-2026 13:48:12</t>
+          <t>23-02-2026 18:36:29</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4479,17 +4479,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>27-02-2026 13:53:10</t>
+          <t>23-02-2026 18:41:47</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>27-02-2026 13:52:34</t>
+          <t>23-02-2026 18:40:26</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26140522711730001849</t>
+          <t>26140522596840001685</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4521,24 +4521,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>346979</t>
+          <t>346950</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>89144</t>
+          <t>89115</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4548,17 +4548,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ELIAM</t>
+          <t xml:space="preserve">EDGAR FABIAN </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>GALLEGOS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4568,10 +4568,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6648537656</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>6645182446</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4579,42 +4583,42 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>28-12-2008</t>
+          <t>18-08-1989</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ELIAMTIJ2017@GMAIL.COM</t>
+          <t>EDGARFAB123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>27-02-2026 15:30:07</t>
+          <t>27-02-2026 13:48:12</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>27-02-2026 15:32:24</t>
+          <t>27-02-2026 13:53:10</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4622,13 +4626,21 @@
           <t>27-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>27-02-2026 13:52:34</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4636,36 +4648,36 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26140522716110001855</t>
+          <t>26140522711730001849</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>345993</t>
+          <t>346979</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>88158</t>
+          <t>89144</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4675,17 +4687,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JHOVANNY</t>
+          <t>ELIAM</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BENITEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4695,14 +4707,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6643012921</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PRIV SAN LUCAS </t>
-        </is>
-      </c>
+          <t>6648537656</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4710,64 +4718,56 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>25-09-1994</t>
+          <t>28-12-2008</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>JHOVANNYTORRESBENITEZ031@GMAIL.COM</t>
+          <t>ELIAMTIJ2017@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>23-02-2026 18:36:29</t>
+          <t>27-02-2026 15:30:07</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>23-02-2026 18:41:47</t>
+          <t>27-02-2026 15:32:24</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>23-02-2026 18:40:26</t>
-        </is>
-      </c>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4775,14 +4775,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26140522596840001685</t>
+          <t>26140522716110001855</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4799,12 +4799,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>345989</t>
+          <t>345850</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>88154</t>
+          <t>88015</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4814,17 +4814,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">YOSELIN </t>
+          <t>ERICKA ISABEL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENCINAS </t>
+          <t xml:space="preserve">FUENTES </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MIRAMONTES</t>
+          <t>HERRAN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4834,10 +4834,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6644643065</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>6642294144</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE MA MORELOS </t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4845,56 +4849,64 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>24-04-2012</t>
+          <t>31-10-1995</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>TANIAMIRA758@GMAIL.COM</t>
+          <t>ERICKAFUENTES111@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>23-02-2026 18:30:03</t>
+          <t>23-02-2026 15:51:57</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>23-02-2026 18:32:11</t>
+          <t>25-02-2026 18:15:35</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>25-02-2026 18:06:31</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4902,19 +4914,23 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26140522595960001682</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
+          <t>26140522662810001783</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4926,12 +4942,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>345850</t>
+          <t>345989</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>88015</t>
+          <t>88154</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4941,17 +4957,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ERICKA ISABEL</t>
+          <t xml:space="preserve">YOSELIN </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">FUENTES </t>
+          <t xml:space="preserve">ENCINAS </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>HERRAN</t>
+          <t>MIRAMONTES</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4961,14 +4977,10 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6642294144</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JOSE MA MORELOS </t>
-        </is>
-      </c>
+          <t>6644643065</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4976,64 +4988,56 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>31-10-1995</t>
+          <t>24-04-2012</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ERICKAFUENTES111@GMAIL.COM</t>
+          <t>TANIAMIRA758@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>23-02-2026 15:51:57</t>
+          <t>23-02-2026 18:30:03</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>25-02-2026 18:15:35</t>
+          <t>23-02-2026 18:32:11</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>25-02-2026 18:06:31</t>
-        </is>
-      </c>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5041,23 +5045,19 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26140522662810001783</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26140522595960001682</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5069,12 +5069,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>346944</t>
+          <t>346512</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>89109</t>
+          <t>88677</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5084,17 +5084,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONICA GEORGINA </t>
+          <t>GLENDA ACEVER</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAÑA </t>
+          <t>AVITIA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5104,14 +5104,10 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4341160435</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOMA BONITA </t>
-        </is>
-      </c>
+          <t>6641171074</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5119,64 +5115,56 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>22-10-1997</t>
+          <t>07-10-1997</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>EFGM757@GMAIL.COM</t>
+          <t>GLEN412@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>27-02-2026 13:34:59</t>
+          <t>25-02-2026 15:39:54</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>27-02-2026 13:45:08</t>
+          <t>25-02-2026 15:41:38</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>27-02-2026 13:44:23</t>
-        </is>
-      </c>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5184,36 +5172,36 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26140522711590001848</t>
+          <t>26140522655870001771</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>346512</t>
+          <t>346944</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>88677</t>
+          <t>89109</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5223,17 +5211,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GLENDA ACEVER</t>
+          <t xml:space="preserve">MONICA GEORGINA </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AVITIA</t>
+          <t xml:space="preserve">MAGAÑA </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5243,10 +5231,14 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6641171074</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>4341160435</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOMA BONITA </t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5254,56 +5246,64 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>07-10-1997</t>
+          <t>22-10-1997</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>GLEN412@GMAIL.COM</t>
+          <t>EFGM757@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>25-02-2026 15:39:54</t>
+          <t>27-02-2026 13:34:59</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>25-02-2026 15:41:38</t>
+          <t>27-02-2026 13:45:08</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>27-02-2026 13:44:23</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5311,24 +5311,24 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26140522655870001771</t>
+          <t>26140522711590001848</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347385</t>
+          <t>347690</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89550</t>
+          <t>89855</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARCOANTONIO </t>
+          <t xml:space="preserve">GAEL </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAFOLLA </t>
+          <t>MANDUJANO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6643574689</t>
+          <t>6645422549</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -624,22 +624,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>03-07-2000</t>
+          <t>12-10-2004</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ELMARQUITOS06@HOTMAIL.COM</t>
+          <t>GAELFLORES661@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 05:22:28</t>
+          <t>02-03-2026 16:40:37</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -649,17 +649,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 05:24:18</t>
+          <t>02-03-2026 16:44:58</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -681,36 +681,36 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26140522773230001899</t>
+          <t>26140522802830001929</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347690</t>
+          <t>347708</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89855</t>
+          <t>89873</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAEL </t>
+          <t xml:space="preserve">SARAI </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t xml:space="preserve">ENCINAS </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MANDUJANO</t>
+          <t xml:space="preserve">MIRAMONTES </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,43 +740,47 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6645422549</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6643801936</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>C SAN LUCAS 4251</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>12-10-2004</t>
+          <t>27-12-2005</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>GAELFLORES661@GMAIL.COM</t>
+          <t>ENCINASY60@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 16:40:37</t>
+          <t>02-03-2026 16:51:08</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -786,7 +790,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 16:44:58</t>
+          <t>02-03-2026 17:00:49</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -794,13 +798,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:58:58</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -808,7 +820,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26140522802830001929</t>
+          <t>26140522804320001931</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -832,12 +844,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347708</t>
+          <t>347621</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89873</t>
+          <t>89786</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARAI </t>
+          <t xml:space="preserve">JUANA </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENCINAS </t>
+          <t xml:space="preserve">DE JESUS </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIRAMONTES </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -867,14 +879,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6643801936</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>C SAN LUCAS 4251</t>
-        </is>
-      </c>
+          <t>6647813719</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -882,64 +890,56 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>27-12-2005</t>
+          <t>27-02-1992</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ENCINASY60@GMAIL.COM</t>
+          <t>JUANITADEJESUSPEREZ7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 16:51:08</t>
+          <t>02-03-2026 15:16:59</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 17:00:49</t>
+          <t>02-03-2026 15:21:31</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:58:58</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -947,19 +947,19 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26140522804320001931</t>
+          <t>26140522797370001922</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Noemi Carolina Meza Arreola</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347621</t>
+          <t>347558</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89786</t>
+          <t>89723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUANA </t>
+          <t xml:space="preserve">ANA </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE JESUS </t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1006,28 +1006,28 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6647813719</t>
+          <t>6641890980</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>27-02-1992</t>
+          <t>13-01-2002</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>JUANITADEJESUSPEREZ7@GMAIL.COM</t>
+          <t>6641890980@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 15:16:59</t>
+          <t>02-03-2026 13:13:52</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1042,28 +1042,28 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 15:21:31</t>
+          <t>02-03-2026 13:15:03</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1074,36 +1074,36 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26140522797370001922</t>
+          <t>26140522792700001918</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Noemi Carolina Meza Arreola</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347558</t>
+          <t>347385</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89723</t>
+          <t>89550</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA </t>
+          <t xml:space="preserve">MARCOANTONIO </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t xml:space="preserve">TAFOLLA </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6641890980</t>
+          <t>6643574689</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,17 +1144,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>13-01-2002</t>
+          <t>03-07-2000</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6641890980@GMAIL.COM</t>
+          <t>ELMARQUITOS06@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 13:13:52</t>
+          <t>02-03-2026 05:22:28</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1169,17 +1169,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 13:15:03</t>
+          <t>02-03-2026 05:24:18</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1201,22 +1201,276 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26140522792700001918</t>
+          <t>26140522773230001899</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>348203</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>90368</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARLIZ CECILIA </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MINJAREZ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6644310740</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>24-01-1995</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>MARLIZ.MINJAREZ95@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:58:06</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:02:18</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>26140522853210001993</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>348225</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>90390</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROSA ISABEL </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>METIVIER</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6642338863</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>20-06-2010</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>SAUCEDO@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:19:46</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>399</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:36:35</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>26140522855760001998</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347690</t>
+          <t>344357</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89855</t>
+          <t>22174</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAEL </t>
+          <t>HUGO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MANDUJANO</t>
+          <t>PEINADO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6645422549</t>
+          <t>6644940031</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -624,22 +624,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>12-10-2004</t>
+          <t>22-12-2005</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>GAELFLORES661@GMAIL.COM</t>
+          <t>IMANOLPEINADO2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 16:40:37</t>
+          <t>16-02-2026 20:47:16</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -649,22 +649,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 16:44:58</t>
+          <t>04-03-2026 19:46:59</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -681,36 +681,40 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26140522802830001929</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+          <t>26140522898290002064</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347708</t>
+          <t>347558</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89873</t>
+          <t>89723</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARAI </t>
+          <t xml:space="preserve">ANA </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENCINAS </t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIRAMONTES </t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,57 +744,53 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6643801936</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>C SAN LUCAS 4251</t>
-        </is>
-      </c>
+          <t>6641890980</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>27-12-2005</t>
+          <t>13-01-2002</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ENCINASY60@GMAIL.COM</t>
+          <t>6641890980@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 16:51:08</t>
+          <t>02-03-2026 13:13:52</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 17:00:49</t>
+          <t>02-03-2026 13:15:03</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -798,21 +798,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:58:58</t>
-        </is>
-      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,36 +812,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26140522804320001931</t>
+          <t>26140522792700001918</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347621</t>
+          <t>347385</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89786</t>
+          <t>89550</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +851,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUANA </t>
+          <t xml:space="preserve">MARCOANTONIO </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE JESUS </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">TAFOLLA </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,28 +871,28 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6647813719</t>
+          <t>6643574689</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>27-02-1992</t>
+          <t>03-07-2000</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>JUANITADEJESUSPEREZ7@GMAIL.COM</t>
+          <t>ELMARQUITOS06@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 15:16:59</t>
+          <t>02-03-2026 05:22:28</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -915,28 +907,28 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 15:21:31</t>
+          <t>02-03-2026 05:24:18</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -947,36 +939,36 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26140522797370001922</t>
+          <t>26140522773230001899</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Noemi Carolina Meza Arreola</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347558</t>
+          <t>347621</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89723</t>
+          <t>89786</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -986,17 +978,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA </t>
+          <t xml:space="preserve">JUANA </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t xml:space="preserve">DE JESUS </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1006,28 +998,28 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6641890980</t>
+          <t>6647813719</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13-01-2002</t>
+          <t>27-02-1992</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6641890980@GMAIL.COM</t>
+          <t>JUANITADEJESUSPEREZ7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 13:13:52</t>
+          <t>02-03-2026 15:16:59</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1042,28 +1034,28 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 13:15:03</t>
+          <t>02-03-2026 15:21:31</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1074,36 +1066,36 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26140522792700001918</t>
+          <t>26140522797370001922</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Noemi Carolina Meza Arreola</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347385</t>
+          <t>348354</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89550</t>
+          <t>90519</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1113,17 +1105,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARCOANTONIO </t>
+          <t xml:space="preserve">FERNANDA </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">BERNAL </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAFOLLA </t>
+          <t xml:space="preserve">BALDERAS </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1133,33 +1125,33 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6643574689</t>
+          <t>6631072088</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>03-07-2000</t>
+          <t>14-09-2006</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ELMARQUITOS06@HOTMAIL.COM</t>
+          <t>FER185@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 05:22:28</t>
+          <t>04-03-2026 08:40:38</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1169,28 +1161,28 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 05:24:18</t>
+          <t>04-03-2026 08:42:01</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -1201,14 +1193,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26140522773230001899</t>
+          <t>26140522876280002030</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1225,12 +1217,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>348203</t>
+          <t>282289</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90368</t>
+          <t>79790</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1240,17 +1232,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARLIZ CECILIA </t>
+          <t>SAUL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MINJAREZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1260,33 +1252,33 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6644310740</t>
+          <t>6641223293</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24-01-1995</t>
+          <t>06-11-2010</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MARLIZ.MINJAREZ95@GMAIL.COM</t>
+          <t>REXER.GAMERPRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>03-03-2026 17:58:06</t>
+          <t>08-03-2025 10:55:28</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1296,22 +1288,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 18:02:18</t>
+          <t>05-03-2026 13:58:38</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1328,14 +1320,18 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26140522853210001993</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+          <t>26130522916360004109</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1352,12 +1348,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348225</t>
+          <t>348203</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90390</t>
+          <t>90368</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1367,17 +1363,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA ISABEL </t>
+          <t xml:space="preserve">MARLIZ CECILIA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>METIVIER</t>
+          <t>MINJAREZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1387,7 +1383,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6642338863</t>
+          <t>6644310740</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1398,17 +1394,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20-06-2010</t>
+          <t>24-01-1995</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>SAUCEDO@ICLOUD.COM</t>
+          <t>MARLIZ.MINJAREZ95@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-03-2026 18:19:46</t>
+          <t>03-03-2026 17:58:06</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1423,28 +1419,28 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 18:36:35</t>
+          <t>03-03-2026 18:02:18</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1455,22 +1451,542 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26140522855760001998</t>
+          <t>26140522853210001993</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Etzon  Pizano Cazares</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>348225</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>90390</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROSA ISABEL </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>METIVIER</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6642338863</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>20-06-2010</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>SAUCEDO@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:19:46</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>399</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:36:35</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26140522855760001998</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>347690</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>89855</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAEL </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FLORES </t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>MANDUJANO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6645422549</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>12-10-2004</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>GAELFLORES661@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:40:37</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:44:58</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26140522802830001929</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Etzon  Pizano Cazares</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>347708</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>89873</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SARAI </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENCINAS </t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIRAMONTES </t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6643801936</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>C SAN LUCAS 4251</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>27-12-2005</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ENCINASY60@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:51:08</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:00:49</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:58:58</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26140522804320001931</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Etzon  Pizano Cazares</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>348352</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90517</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HANNA </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPINOZA </t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLANUEVA </t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6637992698</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>02-03-2006</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ESPINOZAHANNA99@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:37:57</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:39:12</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26140522876200002029</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>344357</t>
+          <t>282289</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>79790</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HUGO</t>
+          <t>SAUL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PEINADO</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6644940031</t>
+          <t>6641223293</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -624,22 +624,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22-12-2005</t>
+          <t>06-11-2010</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>IMANOLPEINADO2@GMAIL.COM</t>
+          <t>REXER.GAMERPRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>16-02-2026 20:47:16</t>
+          <t>08-03-2025 10:55:28</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -649,17 +649,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>04-03-2026 19:46:59</t>
+          <t>05-03-2026 13:58:38</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26140522898290002064</t>
+          <t>26130522916360004109</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -692,7 +692,7 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347558</t>
+          <t>344357</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89723</t>
+          <t>22174</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA </t>
+          <t>HUGO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t>PEINADO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6641890980</t>
+          <t>6644940031</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -755,17 +755,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>13-01-2002</t>
+          <t>22-12-2005</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>6641890980@GMAIL.COM</t>
+          <t>IMANOLPEINADO2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 13:13:52</t>
+          <t>16-02-2026 20:47:16</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -780,22 +780,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 13:15:03</t>
+          <t>04-03-2026 19:46:59</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,14 +812,18 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26140522792700001918</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
+          <t>26140522898290002064</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -922,7 +926,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -963,12 +967,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347621</t>
+          <t>347690</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89786</t>
+          <t>89855</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,17 +982,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUANA </t>
+          <t xml:space="preserve">GAEL </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE JESUS </t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MANDUJANO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -998,33 +1002,33 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6647813719</t>
+          <t>6645422549</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>27-02-1992</t>
+          <t>12-10-2004</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>JUANITADEJESUSPEREZ7@GMAIL.COM</t>
+          <t>GAELFLORES661@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 15:16:59</t>
+          <t>02-03-2026 16:40:37</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1034,28 +1038,28 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 15:21:31</t>
+          <t>02-03-2026 16:44:58</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -1066,19 +1070,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26140522797370001922</t>
+          <t>26140522802830001929</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Noemi Carolina Meza Arreola</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1090,12 +1094,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>348354</t>
+          <t>347708</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90519</t>
+          <t>89873</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1105,17 +1109,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA </t>
+          <t xml:space="preserve">SARAI </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERNAL </t>
+          <t xml:space="preserve">ENCINAS </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALDERAS </t>
+          <t xml:space="preserve">MIRAMONTES </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1125,10 +1129,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6631072088</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6643801936</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>C SAN LUCAS 4251</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1136,32 +1144,32 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>14-09-2006</t>
+          <t>27-12-2005</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FER185@GMAIL.COM</t>
+          <t>ENCINASY60@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>04-03-2026 08:40:38</t>
+          <t>02-03-2026 16:51:08</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1171,21 +1179,29 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>04-03-2026 08:42:01</t>
+          <t>02-03-2026 17:00:49</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:58:58</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1193,7 +1209,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26140522876280002030</t>
+          <t>26140522804320001931</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1205,24 +1221,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>282289</t>
+          <t>347621</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79790</t>
+          <t>89786</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1232,17 +1248,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAUL</t>
+          <t xml:space="preserve">JUANA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">DE JESUS </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1252,33 +1268,33 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6641223293</t>
+          <t>6647813719</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>06-11-2010</t>
+          <t>27-02-1992</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>REXER.GAMERPRO@GMAIL.COM</t>
+          <t>JUANITADEJESUSPEREZ7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>08-03-2025 10:55:28</t>
+          <t>02-03-2026 15:16:59</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1288,28 +1304,28 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>05-03-2026 13:58:38</t>
+          <t>02-03-2026 15:21:31</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1320,40 +1336,36 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26130522916360004109</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26140522797370001922</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Noemi Carolina Meza Arreola</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348203</t>
+          <t>347558</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90368</t>
+          <t>89723</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1363,17 +1375,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARLIZ CECILIA </t>
+          <t xml:space="preserve">ANA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MINJAREZ</t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1383,28 +1395,28 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6644310740</t>
+          <t>6641890980</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>24-01-1995</t>
+          <t>13-01-2002</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MARLIZ.MINJAREZ95@GMAIL.COM</t>
+          <t>6641890980@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-03-2026 17:58:06</t>
+          <t>02-03-2026 13:13:52</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1419,22 +1431,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 18:02:18</t>
+          <t>02-03-2026 13:15:03</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1451,36 +1463,36 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26140522853210001993</t>
+          <t>26140522792700001918</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>348225</t>
+          <t>348352</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90390</t>
+          <t>90517</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1490,17 +1502,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA ISABEL </t>
+          <t xml:space="preserve">HANNA </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>METIVIER</t>
+          <t xml:space="preserve">ESPINOZA </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">VILLANUEVA </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1510,7 +1522,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6642338863</t>
+          <t>6637992698</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1521,22 +1533,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>20-06-2010</t>
+          <t>02-03-2006</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>SAUCEDO@ICLOUD.COM</t>
+          <t>ESPINOZAHANNA99@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-03-2026 18:19:46</t>
+          <t>04-03-2026 08:37:57</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1546,17 +1558,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 18:36:35</t>
+          <t>04-03-2026 08:39:12</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1567,7 +1579,7 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1578,14 +1590,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26140522855760001998</t>
+          <t>26140522876200002029</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1602,12 +1614,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347690</t>
+          <t>348225</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89855</t>
+          <t>90390</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1617,17 +1629,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAEL </t>
+          <t xml:space="preserve">ROSA ISABEL </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>METIVIER</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MANDUJANO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1637,33 +1649,33 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6645422549</t>
+          <t>6642338863</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>12-10-2004</t>
+          <t>20-06-2010</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>GAELFLORES661@GMAIL.COM</t>
+          <t>SAUCEDO@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:40:37</t>
+          <t>03-03-2026 18:19:46</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1673,17 +1685,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:44:58</t>
+          <t>03-03-2026 18:36:35</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1694,7 +1706,7 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1705,36 +1717,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26140522802830001929</t>
+          <t>26140522855760001998</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347708</t>
+          <t>348203</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89873</t>
+          <t>90368</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1744,17 +1756,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARAI </t>
+          <t xml:space="preserve">MARLIZ CECILIA </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENCINAS </t>
+          <t>MINJAREZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIRAMONTES </t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1764,14 +1776,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6643801936</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>C SAN LUCAS 4251</t>
-        </is>
-      </c>
+          <t>6644310740</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1779,64 +1787,56 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>27-12-2005</t>
+          <t>24-01-1995</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ENCINASY60@GMAIL.COM</t>
+          <t>MARLIZ.MINJAREZ95@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 16:51:08</t>
+          <t>03-03-2026 17:58:06</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:00:49</t>
+          <t>03-03-2026 18:02:18</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:58:58</t>
-        </is>
-      </c>
+          <t>02-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26140522804320001931</t>
+          <t>26140522853210001993</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348352</t>
+          <t>348354</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90517</t>
+          <t>90519</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1883,17 +1883,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HANNA </t>
+          <t xml:space="preserve">FERNANDA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOZA </t>
+          <t xml:space="preserve">BERNAL </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLANUEVA </t>
+          <t xml:space="preserve">BALDERAS </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6637992698</t>
+          <t>6631072088</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1914,17 +1914,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>02-03-2006</t>
+          <t>14-09-2006</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ESPINOZAHANNA99@GMAIL.COM</t>
+          <t>FER185@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>04-03-2026 08:37:57</t>
+          <t>04-03-2026 08:40:38</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1949,18 +1949,18 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-03-2026 08:39:12</t>
+          <t>04-03-2026 08:42:01</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26140522876200002029</t>
+          <t>26140522876280002030</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -1987,6 +1987,284 @@
         </is>
       </c>
       <c r="AC12" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>349023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>91188</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUILAR </t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>MARTIN DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6631223307</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>C GRUPO MORELOS 5023</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>01-10-2007</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0107MIGUELAGUILAR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>06-03-2026 18:24:18</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>06-03-2026 18:35:39</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>06-03-2026 18:34:23</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26140522958960002139</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>349152</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>91317</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HECTOR MARTIN </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LUCERO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>JAUREGUI</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6642804303</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOMA BONITA </t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>30-10-1966</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PARIENTE-JAUREGUI@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:40:36</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:43:05</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:42:14</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26140522975090002158</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,12 +697,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -828,24 +828,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347385</t>
+          <t>316032</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89550</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,17 +855,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARCOANTONIO </t>
+          <t>JORDI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>BAÑUELOS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAFOLLA </t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -875,10 +875,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6643574689</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>6645553383</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LIB SALVATIERRA EDIF C 7202 303</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -886,17 +890,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>03-07-2000</t>
+          <t>15-07-1999</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ELMARQUITOS06@HOTMAIL.COM</t>
+          <t>BANUELOSMENDEZ99@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 05:22:28</t>
+          <t>27-09-2025 10:53:11</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -906,36 +910,44 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 05:24:18</t>
+          <t>13-03-2026 20:56:11</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>13-03-2026 20:53:37</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -943,36 +955,40 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26140522773230001899</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+          <t>26140523165240002403</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Noemi Carolina Meza Arreola</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347690</t>
+          <t>347385</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89855</t>
+          <t>89550</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -982,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAEL </t>
+          <t xml:space="preserve">MARCOANTONIO </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MANDUJANO</t>
+          <t xml:space="preserve">TAFOLLA </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1002,7 +1018,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6645422549</t>
+          <t>6643574689</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,22 +1029,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>12-10-2004</t>
+          <t>03-07-2000</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>GAELFLORES661@GMAIL.COM</t>
+          <t>ELMARQUITOS06@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 16:40:37</t>
+          <t>02-03-2026 05:22:28</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1038,17 +1054,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 16:44:58</t>
+          <t>02-03-2026 05:24:18</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1070,19 +1086,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26140522802830001929</t>
+          <t>26140522773230001899</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1094,12 +1110,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347708</t>
+          <t>347420</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89873</t>
+          <t>89585</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,17 +1125,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARAI </t>
+          <t xml:space="preserve">BRUNO ALEJANDRO </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENCINAS </t>
+          <t xml:space="preserve">MOLINA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIRAMONTES </t>
+          <t xml:space="preserve">ALVAREZ </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1129,79 +1145,67 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6643801936</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>C SAN LUCAS 4251</t>
-        </is>
-      </c>
+          <t>6643490165</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>27-12-2005</t>
+          <t>03-12-2005</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ENCINASY60@GMAIL.COM</t>
+          <t>BRUNOALEJANDRO1349@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 16:51:08</t>
+          <t>02-03-2026 07:27:27</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 17:00:49</t>
+          <t>11-03-2026 09:23:46</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:58:58</t>
-        </is>
-      </c>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1209,19 +1213,27 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26140522804320001931</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26140523084710002292</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>MARIA LUISA VALDEZ MAYORGA</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1233,12 +1245,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347621</t>
+          <t>347690</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89786</t>
+          <t>89855</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1248,17 +1260,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUANA </t>
+          <t xml:space="preserve">GAEL </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE JESUS </t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MANDUJANO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1268,33 +1280,33 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6647813719</t>
+          <t>6645422549</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>27-02-1992</t>
+          <t>12-10-2004</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JUANITADEJESUSPEREZ7@GMAIL.COM</t>
+          <t>GAELFLORES661@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 15:16:59</t>
+          <t>02-03-2026 16:40:37</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1304,28 +1316,28 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 15:21:31</t>
+          <t>02-03-2026 16:44:58</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -1336,19 +1348,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26140522797370001922</t>
+          <t>26140522802830001929</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Noemi Carolina Meza Arreola</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1360,12 +1372,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347558</t>
+          <t>347708</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89723</t>
+          <t>89873</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1375,17 +1387,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA </t>
+          <t xml:space="preserve">SARAI </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t xml:space="preserve">ENCINAS </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOPEZ </t>
+          <t xml:space="preserve">MIRAMONTES </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1395,53 +1407,57 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6641890980</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6643801936</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>C SAN LUCAS 4251</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>13-01-2002</t>
+          <t>27-12-2005</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6641890980@GMAIL.COM</t>
+          <t>ENCINASY60@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 13:13:52</t>
+          <t>02-03-2026 16:51:08</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 13:15:03</t>
+          <t>02-03-2026 17:00:49</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1449,13 +1465,21 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:58:58</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1463,36 +1487,36 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26140522792700001918</t>
+          <t>26140522804320001931</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>348352</t>
+          <t>347558</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90517</t>
+          <t>89723</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1502,17 +1526,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HANNA </t>
+          <t xml:space="preserve">ANA </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOZA </t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLANUEVA </t>
+          <t xml:space="preserve">LOPEZ </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1522,33 +1546,33 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6637992698</t>
+          <t>6641890980</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>02-03-2006</t>
+          <t>13-01-2002</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ESPINOZAHANNA99@GMAIL.COM</t>
+          <t>6641890980@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>04-03-2026 08:37:57</t>
+          <t>02-03-2026 13:13:52</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1558,22 +1582,22 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>04-03-2026 08:39:12</t>
+          <t>02-03-2026 13:15:03</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1590,36 +1614,36 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26140522876200002029</t>
+          <t>26140522792700001918</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>348225</t>
+          <t>347621</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90390</t>
+          <t>89786</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1629,17 +1653,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA ISABEL </t>
+          <t xml:space="preserve">JUANA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>METIVIER</t>
+          <t xml:space="preserve">DE JESUS </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1649,7 +1673,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6642338863</t>
+          <t>6647813719</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1660,17 +1684,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>20-06-2010</t>
+          <t>27-02-1992</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>SAUCEDO@ICLOUD.COM</t>
+          <t>JUANITADEJESUSPEREZ7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-03-2026 18:19:46</t>
+          <t>02-03-2026 15:16:59</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1685,22 +1709,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 18:36:35</t>
+          <t>02-03-2026 15:21:31</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1717,36 +1741,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26140522855760001998</t>
+          <t>26140522797370001922</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Noemi Carolina Meza Arreola</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348203</t>
+          <t>347434</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90368</t>
+          <t>89599</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1756,17 +1780,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARLIZ CECILIA </t>
+          <t>LETICIA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MINJAREZ</t>
+          <t>RESENDIZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1776,10 +1800,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6644310740</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6642048891</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PALMA REAL </t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1787,56 +1815,64 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>24-01-1995</t>
+          <t>24-08-1964</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MARLIZ.MINJAREZ95@GMAIL.COM</t>
+          <t>LETICIARESENDIZ656Z64@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 17:58:06</t>
+          <t>02-03-2026 08:09:20</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 18:02:18</t>
+          <t>09-03-2026 08:07:53</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:07:17</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1844,19 +1880,27 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26140522853210001993</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26140522999900002169</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>MARIA LUISA VALDEZ MAYORGA</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1868,12 +1912,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348354</t>
+          <t>348203</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90519</t>
+          <t>90368</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1883,17 +1927,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA </t>
+          <t xml:space="preserve">MARLIZ CECILIA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERNAL </t>
+          <t>MINJAREZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALDERAS </t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1903,7 +1947,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6631072088</t>
+          <t>6644310740</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1914,22 +1958,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>14-09-2006</t>
+          <t>24-01-1995</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FER185@GMAIL.COM</t>
+          <t>MARLIZ.MINJAREZ95@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>04-03-2026 08:40:38</t>
+          <t>03-03-2026 17:58:06</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1939,28 +1983,28 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-03-2026 08:42:01</t>
+          <t>03-03-2026 18:02:18</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1971,36 +2015,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26140522876280002030</t>
+          <t>26140522853210001993</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>349023</t>
+          <t>348352</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>91188</t>
+          <t>90517</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2010,17 +2054,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL ANGEL </t>
+          <t xml:space="preserve">HANNA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILAR </t>
+          <t xml:space="preserve">ESPINOZA </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MARTIN DEL CAMPO</t>
+          <t xml:space="preserve">VILLANUEVA </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2030,47 +2074,43 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6631223307</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>C GRUPO MORELOS 5023</t>
-        </is>
-      </c>
+          <t>6637992698</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>01-10-2007</t>
+          <t>02-03-2006</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0107MIGUELAGUILAR@GMAIL.COM</t>
+          <t>ESPINOZAHANNA99@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>06-03-2026 18:24:18</t>
+          <t>04-03-2026 08:37:57</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2080,29 +2120,21 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>06-03-2026 18:35:39</t>
+          <t>04-03-2026 08:39:12</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>06-03-2026 18:34:23</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2110,7 +2142,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26140522958960002139</t>
+          <t>26140522876200002029</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2122,24 +2154,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>349152</t>
+          <t>348175</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>91317</t>
+          <t>90340</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2149,17 +2181,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">HECTOR MARTIN </t>
+          <t>DARIKSON YAMIL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LUCERO</t>
+          <t>ACEVEDO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>SIXTO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2169,14 +2201,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6642804303</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOMA BONITA </t>
-        </is>
-      </c>
+          <t>6643273790</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2184,32 +2212,32 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>30-10-1966</t>
+          <t>22-06-2012</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PARIENTE-JAUREGUI@HOTMAIL.COM</t>
+          <t>ACEVEDOYAMIL538@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>07-03-2026 12:40:36</t>
+          <t>03-03-2026 17:26:02</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2219,29 +2247,21 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>07-03-2026 12:43:05</t>
+          <t>10-03-2026 17:04:04</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>07-03-2026 12:42:14</t>
-        </is>
-      </c>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2249,10 +2269,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26140522975090002158</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+          <t>26140523058720002257</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2261,12 +2285,2751 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>348354</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90519</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDA </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BERNAL </t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BALDERAS </t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6631072088</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>14-09-2006</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>FER185@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:40:38</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>04-03-2026 08:42:01</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26140522876280002030</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348225</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90390</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROSA ISABEL </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>METIVIER</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6642338863</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>20-06-2010</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>SAUCEDO@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:19:46</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:36:35</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26140522855760001998</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>349152</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>91317</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HECTOR MARTIN </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LUCERO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>JAUREGUI</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6642804303</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOMA BONITA </t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>30-10-1966</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PARIENTE-JAUREGUI@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:40:36</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:43:05</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:42:14</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26140522975090002158</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>349418</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>91583</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIOLETA </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEDEZMA </t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6641132195</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>18-10-2010</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>IZHARIASDAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>09-03-2026 13:32:27</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>09-03-2026 13:33:53</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26140523007680002180</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>349464</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>91629</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CITLALI BERENICE </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MENDOZA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>QUINTERO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6633291344</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>05-02-2005</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>MENDOZACHAPIS479@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:55:15</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>09-03-2026 14:59:40</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26140523010330002184</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Noemi Carolina Meza Arreola</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>349023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>91188</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGUILAR </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MARTIN DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6631223307</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>C GRUPO MORELOS 5023</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>01-10-2007</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0107MIGUELAGUILAR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>06-03-2026 18:24:18</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>06-03-2026 18:35:39</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>06-03-2026 18:34:23</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26140522958960002139</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Noemi Carolina Meza Arreola</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>349674</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>91839</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VIVIAN ANAHI</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SANTOS</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>9611761766</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>15-08-1997</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>VIVIAN.SM15@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:30:18</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:32:36</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>08-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26140523028030002218</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Etzon  Pizano Cazares</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>349679</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>91844</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PATRICIA CAROLINA </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6647655615</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>03-05-1995</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PATR1Z@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:35:26</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:37:20</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>08-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26140523028280002219</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Etzon  Pizano Cazares</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>349619</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>91784</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KARIME </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PAREJA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>GIL</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6643569826</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>26-10-2011</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>KARIME100@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:42:10</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:46:33</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26140523024090002208</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>350244</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>92408</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>JOVAN HUMBERTO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6632136122</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>17-05-1997</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>JHLL2323@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>11-03-2026 20:59:39</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>11-03-2026 21:02:11</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26140523106750002325</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>349971</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>92136</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>KEILA MIREYA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALAZAR </t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6641750485</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>RAMPA ARTESANAL</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>29-12-1992</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>MIREYASALAZAR729@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:57:19</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:10:17</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:08:45</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26140523066930002268</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>350384</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>92548</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CRISTIAN </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ARREVILLAGA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6643884181</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>C DEL RIO BRAVO 3634 A</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>14-08-2006</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>CRISTJ1408@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>12-03-2026 16:58:50</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>12-03-2026 17:10:05</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>12-03-2026 17:09:02</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26140523127640002354</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>349755</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>91920</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSELIN </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUÑOZ </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VALDEZ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6643855282</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>25-01-2010</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>JOSELINMUÑOZVALDEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>10-03-2026 07:24:55</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>10-03-2026 07:27:23</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26140523043690002235</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>349753</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>91918</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NAOMI </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MUÑOZ </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALDEZ </t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6643698462</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>20-01-2009</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NAOMINUÑEVALDEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>10-03-2026 07:21:20</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>10-03-2026 07:23:21</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26140523043580002234</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>349833</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>91998</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DANNA SOFIA </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEGA </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESPINOZA </t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6646132576</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>16-11-2010</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DANNA.VEG445@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>10-03-2026 13:29:51</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>10-03-2026 13:32:15</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26140523051390002248</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>350235</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>92399</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESMERALDA AZUCENA </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDINA </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6634111647</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>31-01-2005</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>MEDINALUNAESMERALDA9@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>11-03-2026 20:18:19</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>12-03-2026 19:48:08</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26140523135550002367</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>350527</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>92691</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSELINE NOEMI </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RIVERA </t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6632010525</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>22-11-2000</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>JNPRYOACM@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>13-03-2026 09:52:03</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>13-03-2026 10:25:25</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>13-03-2026 10:24:59</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26140523149800002384</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>351443</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>93607</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEYRA AMERICA </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CENICEROS </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SANABRIA </t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6647479749</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>04-11-2008</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>KAYRACENICEROS3@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:44:28</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:45:56</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26140523248680002488</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>351316</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>93480</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JESUS OSVALDO </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUTIERREZ </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6647805209</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>CJON DE LA ESTRELLA MZ212 LT101</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>08-03-1988</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>JESUSOSVALDOGUTIERREZCASTRO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>16-03-2026 18:52:17</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>16-03-2026 18:58:03</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>16-03-2026 18:57:08</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26140523231800002462</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Noemi Carolina Meza Arreola</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>351440</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>93604</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MICHELL ESMERALDA </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASTRO </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORQUECHO </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6646368712</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>01-01-2008</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>PANQUESITOS123@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:39:03</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>17-03-2026 09:41:22</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26140523248550002487</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>351487</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>93651</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AILEEN RENEE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NERLICTFF</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6648313230</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>23-02-2010</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>AILEENALLTT@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:43:21</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>COBACH $399</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>17-03-2026 12:44:51</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26140523251920002497</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__LOMA BONITA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>282289</t>
+          <t>316032</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>79790</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAUL</t>
+          <t>JORDI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>BAÑUELOS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ACOSTA</t>
+          <t>MENDEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,10 +613,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6641223293</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>6645553383</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>LIB SALVATIERRA EDIF C 7202 303</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -624,56 +628,64 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>06-11-2010</t>
+          <t>15-07-1999</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>REXER.GAMERPRO@GMAIL.COM</t>
+          <t>BANUELOSMENDEZ99@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>08-03-2025 10:55:28</t>
+          <t>27-09-2025 10:53:11</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>05-03-2026 13:58:38</t>
+          <t>13-03-2026 20:56:11</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>13-03-2026 20:53:37</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -681,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26130522916360004109</t>
+          <t>26140523165240002403</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -692,12 +704,12 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Noemi Carolina Meza Arreola</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -709,12 +721,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>344357</t>
+          <t>282289</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>79790</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,17 +736,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HUGO</t>
+          <t>SAUL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PEINADO</t>
+          <t>ACOSTA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -744,7 +756,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6644940031</t>
+          <t>6641223293</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -755,22 +767,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22-12-2005</t>
+          <t>06-11-2010</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>IMANOLPEINADO2@GMAIL.COM</t>
+          <t>REXER.GAMERPRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>16-02-2026 20:47:16</t>
+          <t>08-03-2025 10:55:28</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -780,22 +792,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>04-03-2026 19:46:59</t>
+          <t>05-03-2026 13:58:38</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +824,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26140522898290002064</t>
+          <t>26130522916360004109</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -823,7 +835,7 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -840,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>316032</t>
+          <t>344357</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>22174</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>JORDI</t>
+          <t>HUGO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BAÑUELOS</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MENDEZ</t>
+          <t>PEINADO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -875,14 +887,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6645553383</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>LIB SALVATIERRA EDIF C 7202 303</t>
-        </is>
-      </c>
+          <t>6644940031</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -890,17 +898,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>15-07-1999</t>
+          <t>22-12-2005</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BANUELOSMENDEZ99@GMAIL.COM</t>
+          <t>IMANOLPEINADO2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>27-09-2025 10:53:11</t>
+          <t>16-02-2026 20:47:16</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -910,44 +918,36 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>13-03-2026 20:56:11</t>
+          <t>04-03-2026 19:46:59</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>12-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>13-03-2026 20:53:37</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -955,7 +955,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26140523165240002403</t>
+          <t>26140522898290002064</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -966,12 +966,12 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Noemi Carolina Meza Arreola</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1245,12 +1245,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347690</t>
+          <t>347434</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89855</t>
+          <t>89599</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1260,17 +1260,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAEL </t>
+          <t>LETICIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLORES </t>
+          <t>RESENDIZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MANDUJANO</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1280,43 +1280,47 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6645422549</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6642048891</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PALMA REAL </t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>12-10-2004</t>
+          <t>24-08-1964</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>GAELFLORES661@GMAIL.COM</t>
+          <t>LETICIARESENDIZ656Z64@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:40:37</t>
+          <t>02-03-2026 08:09:20</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1326,21 +1330,29 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:44:58</t>
+          <t>09-03-2026 08:07:53</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:07:17</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1348,11 +1360,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26140522802830001929</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26140522999900002169</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>MARIA LUISA VALDEZ MAYORGA</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>549</t>
@@ -1360,7 +1380,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1372,12 +1392,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347708</t>
+          <t>347621</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89873</t>
+          <t>89786</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1387,17 +1407,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARAI </t>
+          <t xml:space="preserve">JUANA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENCINAS </t>
+          <t xml:space="preserve">DE JESUS </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIRAMONTES </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1407,14 +1427,10 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6643801936</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>C SAN LUCAS 4251</t>
-        </is>
-      </c>
+          <t>6647813719</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1422,64 +1438,56 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>27-12-2005</t>
+          <t>27-02-1992</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ENCINASY60@GMAIL.COM</t>
+          <t>JUANITADEJESUSPEREZ7@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 16:51:08</t>
+          <t>02-03-2026 15:16:59</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 17:00:49</t>
+          <t>02-03-2026 15:21:31</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:58:58</t>
-        </is>
-      </c>
+          <t>01-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1487,19 +1495,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26140522804320001931</t>
+          <t>26140522797370001922</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Noemi Carolina Meza Arreola</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1638,12 +1646,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347621</t>
+          <t>347690</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89786</t>
+          <t>89855</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1653,17 +1661,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUANA </t>
+          <t xml:space="preserve">GAEL </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE JESUS </t>
+          <t xml:space="preserve">FLORES </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MANDUJANO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1673,33 +1681,33 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6647813719</t>
+          <t>6645422549</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>27-02-1992</t>
+          <t>12-10-2004</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>JUANITADEJESUSPEREZ7@GMAIL.COM</t>
+          <t>GAELFLORES661@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 15:16:59</t>
+          <t>02-03-2026 16:40:37</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1709,28 +1717,28 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 15:21:31</t>
+          <t>02-03-2026 16:44:58</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-06-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1741,19 +1749,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26140522797370001922</t>
+          <t>26140522802830001929</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Noemi Carolina Meza Arreola</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1765,12 +1773,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347434</t>
+          <t>347708</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89599</t>
+          <t>89873</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1780,17 +1788,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LETICIA</t>
+          <t xml:space="preserve">SARAI </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RESENDIZ</t>
+          <t xml:space="preserve">ENCINAS </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t xml:space="preserve">MIRAMONTES </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1800,12 +1808,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6642048891</t>
+          <t>6643801936</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PALMA REAL </t>
+          <t>C SAN LUCAS 4251</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1815,17 +1823,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>24-08-1964</t>
+          <t>27-12-2005</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>LETICIARESENDIZ656Z64@GMAIL.COM</t>
+          <t>ENCINASY60@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 08:09:20</t>
+          <t>02-03-2026 16:51:08</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1850,29 +1858,29 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>09-03-2026 08:07:53</t>
+          <t>02-03-2026 17:00:49</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>09-03-2026 08:07:17</t>
+          <t>02-03-2026 16:58:58</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1880,19 +1888,11 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26140522999900002169</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>MARIA LUISA VALDEZ MAYORGA</t>
-        </is>
-      </c>
+          <t>26140522804320001931</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>549</t>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1912,12 +1912,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348203</t>
+          <t>348354</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90368</t>
+          <t>90519</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1927,17 +1927,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARLIZ CECILIA </t>
+          <t xml:space="preserve">FERNANDA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MINJAREZ</t>
+          <t xml:space="preserve">BERNAL </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t xml:space="preserve">BALDERAS </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6644310740</t>
+          <t>6631072088</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>24-01-1995</t>
+          <t>14-09-2006</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>MARLIZ.MINJAREZ95@GMAIL.COM</t>
+          <t>FER185@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 17:58:06</t>
+          <t>04-03-2026 08:40:38</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1983,28 +1983,28 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 18:02:18</t>
+          <t>04-03-2026 08:42:01</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-06-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -2015,19 +2015,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26140522853210001993</t>
+          <t>26140522876280002030</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2166,12 +2166,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348175</t>
+          <t>348606</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90340</t>
+          <t>90771</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DARIKSON YAMIL</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ACEVEDO</t>
+          <t>YAÑEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SIXTO</t>
+          <t>GUEVARA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6643273790</t>
+          <t>6642864455</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2212,22 +2212,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22-06-2012</t>
+          <t>27-01-2009</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ACEVEDOYAMIL538@GMAIL.COM</t>
+          <t>HGUYDGCUYWEYFU@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 17:26:02</t>
+          <t>04-03-2026 21:59:04</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2237,22 +2237,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>10-03-2026 17:04:04</t>
+          <t>24-03-2026 12:56:53</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>23-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26140523058720002257</t>
+          <t>26140523465830002745</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2280,29 +2280,29 @@
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348354</t>
+          <t>348175</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90519</t>
+          <t>90340</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2312,17 +2312,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA </t>
+          <t>DARIKSON YAMIL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERNAL </t>
+          <t>ACEVEDO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">BALDERAS </t>
+          <t>SIXTO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2332,28 +2332,28 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6631072088</t>
+          <t>6643273790</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>14-09-2006</t>
+          <t>22-06-2012</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>FER185@GMAIL.COM</t>
+          <t>ACEVEDOYAMIL538@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>04-03-2026 08:40:38</t>
+          <t>03-03-2026 17:26:02</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2378,18 +2378,18 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>04-03-2026 08:42:01</t>
+          <t>10-03-2026 17:04:04</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2400,10 +2400,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26140522876280002030</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+          <t>26140523058720002257</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2424,12 +2428,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348225</t>
+          <t>349152</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90390</t>
+          <t>91317</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2439,17 +2443,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA ISABEL </t>
+          <t xml:space="preserve">HECTOR MARTIN </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>METIVIER</t>
+          <t>LUCERO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>JAUREGUI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2459,67 +2463,79 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6642338863</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>6642804303</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOMA BONITA </t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20-06-2010</t>
+          <t>30-10-1966</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>SAUCEDO@ICLOUD.COM</t>
+          <t>PARIENTE-JAUREGUI@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 18:19:46</t>
+          <t>07-03-2026 12:40:36</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 18:36:35</t>
+          <t>07-03-2026 12:43:05</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>07-03-2026 12:42:14</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2527,14 +2543,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26140522855760001998</t>
+          <t>26140522975090002158</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2551,12 +2567,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>349152</t>
+          <t>348225</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>91317</t>
+          <t>90390</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2566,17 +2582,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">HECTOR MARTIN </t>
+          <t xml:space="preserve">ROSA ISABEL </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LUCERO</t>
+          <t>METIVIER</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JAUREGUI</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2586,79 +2602,67 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6642804303</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOMA BONITA </t>
-        </is>
-      </c>
+          <t>6642338863</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30-10-1966</t>
+          <t>20-06-2010</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PARIENTE-JAUREGUI@HOTMAIL.COM</t>
+          <t>SAUCEDO@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>07-03-2026 12:40:36</t>
+          <t>03-03-2026 18:19:46</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>07-03-2026 12:43:05</t>
+          <t>03-03-2026 18:36:35</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>07-03-2026 12:42:14</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2666,14 +2670,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26140522975090002158</t>
+          <t>26140522855760001998</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2690,12 +2694,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>349418</t>
+          <t>348203</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>91583</t>
+          <t>90368</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2705,17 +2709,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIOLETA </t>
+          <t xml:space="preserve">MARLIZ CECILIA </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MINJAREZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEDEZMA </t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2725,7 +2729,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6641132195</t>
+          <t>6644310740</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2736,17 +2740,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18-10-2010</t>
+          <t>24-01-1995</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>IZHARIASDAS@GMAIL.COM</t>
+          <t>MARLIZ.MINJAREZ95@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>09-03-2026 13:32:27</t>
+          <t>03-03-2026 17:58:06</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2761,22 +2765,22 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>09-03-2026 13:33:53</t>
+          <t>03-03-2026 18:02:18</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>02-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2793,19 +2797,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26140523007680002180</t>
+          <t>26140522853210001993</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2817,12 +2821,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>349464</t>
+          <t>349418</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>91629</t>
+          <t>91583</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2832,17 +2836,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CITLALI BERENICE </t>
+          <t xml:space="preserve">VIOLETA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t xml:space="preserve">LEDEZMA </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2852,7 +2856,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6633291344</t>
+          <t>6641132195</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2863,17 +2867,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>05-02-2005</t>
+          <t>18-10-2010</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MENDOZACHAPIS479@GMAIL.COM</t>
+          <t>IZHARIASDAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>09-03-2026 14:55:15</t>
+          <t>09-03-2026 13:32:27</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2888,17 +2892,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>09-03-2026 14:59:40</t>
+          <t>09-03-2026 13:33:53</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2920,14 +2924,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26140523010330002184</t>
+          <t>26140523007680002180</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -2944,12 +2948,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>349023</t>
+          <t>349464</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>91188</t>
+          <t>91629</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2959,17 +2963,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL ANGEL </t>
+          <t xml:space="preserve">CITLALI BERENICE </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILAR </t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MARTIN DEL CAMPO</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2979,79 +2983,67 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6631223307</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>C GRUPO MORELOS 5023</t>
-        </is>
-      </c>
+          <t>6633291344</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>01-10-2007</t>
+          <t>05-02-2005</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0107MIGUELAGUILAR@GMAIL.COM</t>
+          <t>MENDOZACHAPIS479@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>06-03-2026 18:24:18</t>
+          <t>09-03-2026 14:55:15</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>06-03-2026 18:35:39</t>
+          <t>09-03-2026 14:59:40</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>06-03-2026 18:34:23</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3059,14 +3051,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26140522958960002139</t>
+          <t>26140523010330002184</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3083,12 +3075,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>349674</t>
+          <t>349619</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>91839</t>
+          <t>91784</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3098,17 +3090,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VIVIAN ANAHI</t>
+          <t xml:space="preserve">KARIME </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>PAREJA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GIL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3118,7 +3110,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>9611761766</t>
+          <t>6643569826</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3129,22 +3121,22 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>15-08-1997</t>
+          <t>26-10-2011</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>VIVIAN.SM15@OUTLOOK.COM</t>
+          <t>KARIME100@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-03-2026 19:30:18</t>
+          <t>09-03-2026 18:42:10</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3154,22 +3146,22 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-03-2026 19:32:36</t>
+          <t>09-03-2026 18:46:33</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>08-06-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -3186,19 +3178,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26140523028030002218</t>
+          <t>26140523024090002208</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3210,12 +3202,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>349679</t>
+          <t>349023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>91844</t>
+          <t>91188</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3225,17 +3217,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">PATRICIA CAROLINA </t>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>MARTIN DEL CAMPO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3245,67 +3237,79 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6647655615</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6631223307</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>C GRUPO MORELOS 5023</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>03-05-1995</t>
+          <t>01-10-2007</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>PATR1Z@HOTMAIL.COM</t>
+          <t>0107MIGUELAGUILAR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>09-03-2026 19:35:26</t>
+          <t>06-03-2026 18:24:18</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>09-03-2026 19:37:20</t>
+          <t>06-03-2026 18:35:39</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>08-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>06-03-2026 18:34:23</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3313,19 +3317,19 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26140523028280002219</t>
+          <t>26140522958960002139</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Etzon  Pizano Cazares</t>
+          <t>Noemi Carolina Meza Arreola</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3337,12 +3341,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>349619</t>
+          <t>350244</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>91784</t>
+          <t>92408</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3352,17 +3356,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">KARIME </t>
+          <t>JOVAN HUMBERTO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PAREJA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GIL</t>
+          <t>LEON</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3372,33 +3376,33 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6643569826</t>
+          <t>6632136122</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>26-10-2011</t>
+          <t>17-05-1997</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>KARIME100@GMAIL.COM</t>
+          <t>JHLL2323@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-03-2026 18:42:10</t>
+          <t>11-03-2026 20:59:39</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3408,28 +3412,28 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-03-2026 18:46:33</t>
+          <t>11-03-2026 21:02:11</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>10-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V23" t="inlineStr"/>
@@ -3440,14 +3444,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26140523024090002208</t>
+          <t>26140523106750002325</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3464,12 +3468,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>350244</t>
+          <t>349971</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>92408</t>
+          <t>92136</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3479,17 +3483,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>JOVAN HUMBERTO</t>
+          <t>KEILA MIREYA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">SALAZAR </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LEON</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3499,67 +3503,79 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6632136122</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>6641750485</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>RAMPA ARTESANAL</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>17-05-1997</t>
+          <t>29-12-1992</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>JHLL2323@ICLOUD.COM</t>
+          <t>MIREYASALAZAR729@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>11-03-2026 20:59:39</t>
+          <t>10-03-2026 18:57:19</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>11-03-2026 21:02:11</t>
+          <t>10-03-2026 19:10:17</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>10-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:08:45</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3567,14 +3583,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26140523106750002325</t>
+          <t>26140523066930002268</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3591,12 +3607,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>349971</t>
+          <t>349674</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>92136</t>
+          <t>91839</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3606,17 +3622,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KEILA MIREYA</t>
+          <t>VIVIAN ANAHI</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALAZAR </t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3626,14 +3642,10 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6641750485</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>RAMPA ARTESANAL</t>
-        </is>
-      </c>
+          <t>9611761766</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3641,64 +3653,56 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>29-12-1992</t>
+          <t>15-08-1997</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>MIREYASALAZAR729@GMAIL.COM</t>
+          <t>VIVIAN.SM15@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10-03-2026 18:57:19</t>
+          <t>09-03-2026 19:30:18</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10-03-2026 19:10:17</t>
+          <t>09-03-2026 19:32:36</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>10-03-2026 19:08:45</t>
-        </is>
-      </c>
+          <t>08-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3706,19 +3710,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26140523066930002268</t>
+          <t>26140523028030002218</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3730,12 +3734,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>350384</t>
+          <t>349679</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>92548</t>
+          <t>91844</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3745,17 +3749,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRISTIAN </t>
+          <t xml:space="preserve">PATRICIA CAROLINA </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ARREVILLAGA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3765,32 +3769,28 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6643884181</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>C DEL RIO BRAVO 3634 A</t>
-        </is>
-      </c>
+          <t>6647655615</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>14-08-2006</t>
+          <t>03-05-1995</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CRISTJ1408@GMAIL.COM</t>
+          <t>PATR1Z@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>12-03-2026 16:58:50</t>
+          <t>09-03-2026 19:35:26</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3800,44 +3800,36 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>12-03-2026 17:10:05</t>
+          <t>09-03-2026 19:37:20</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>12-03-2026 17:09:02</t>
-        </is>
-      </c>
+          <t>08-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3845,19 +3837,19 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26140523127640002354</t>
+          <t>26140523028280002219</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Etzon  Pizano Cazares</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3996,12 +3988,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>349753</t>
+          <t>351443</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>91918</t>
+          <t>93607</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4011,17 +4003,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAOMI </t>
+          <t xml:space="preserve">KEYRA AMERICA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">MUÑOZ </t>
+          <t xml:space="preserve">CENICEROS </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALDEZ </t>
+          <t xml:space="preserve">SANABRIA </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4031,7 +4023,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6643698462</t>
+          <t>6647479749</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4042,17 +4034,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>20-01-2009</t>
+          <t>04-11-2008</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>NAOMINUÑEVALDEZ@GMAIL.COM</t>
+          <t>KAYRACENICEROS3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>10-03-2026 07:21:20</t>
+          <t>17-03-2026 09:44:28</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4077,12 +4069,12 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>10-03-2026 07:23:21</t>
+          <t>17-03-2026 09:45:56</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
+          <t>16-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -4099,7 +4091,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26140523043580002234</t>
+          <t>26140523248680002488</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4111,24 +4103,24 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>349833</t>
+          <t>350527</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>91998</t>
+          <t>92691</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4138,17 +4130,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANNA SOFIA </t>
+          <t xml:space="preserve">JOSELINE NOEMI </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEGA </t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESPINOZA </t>
+          <t xml:space="preserve">RIVERA </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4158,10 +4150,14 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6646132576</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>6632010525</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4169,56 +4165,64 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>16-11-2010</t>
+          <t>22-11-2000</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>DANNA.VEG445@GMAIL.COM</t>
+          <t>JNPRYOACM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10-03-2026 13:29:51</t>
+          <t>13-03-2026 09:52:03</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>COBACH $399</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10-03-2026 13:32:15</t>
+          <t>13-03-2026 10:25:25</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>13-03-2026 10:24:59</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4226,14 +4230,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26140523051390002248</t>
+          <t>26140523149800002384</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4250,12 +4254,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>350235</t>
+          <t>350384</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>92399</t>
+          <t>92548</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4265,17 +4269,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESMERALDA AZUCENA </t>
+          <t xml:space="preserve">CRISTIAN </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>ARREVILLAGA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LUNA</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4285,28 +4289,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6634111647</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6643884181</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>C DEL RIO BRAVO 3634 A</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>31-01-2005</t>
+          <t>14-08-2006</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MEDINALUNAESMERALDA9@GMAIL.COM</t>
+          <t>CRISTJ1408@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>11-03-2026 20:18:19</t>
+          <t>12-03-2026 16:58:50</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4316,22 +4324,22 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>12-03-2026 19:48:08</t>
+          <t>12-03-2026 17:10:05</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4339,13 +4347,21 @@
           <t>11-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>12-03-2026 17:09:02</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4353,14 +4369,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26140523135550002367</t>
+          <t>26140523127640002354</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4377,12 +4393,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>350527</t>
+          <t>351316</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>92691</t>
+          <t>93480</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4392,17 +4408,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSELINE NOEMI </t>
+          <t xml:space="preserve">JESUS OSVALDO </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">RIVERA </t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4412,67 +4428,67 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6632010525</t>
+          <t>6647805209</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LOMA BONITA</t>
+          <t>CJON DE LA ESTRELLA MZ212 LT101</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>22-11-2000</t>
+          <t>08-03-1988</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>JNPRYOACM@GMAIL.COM</t>
+          <t>JESUSOSVALDOGUTIERREZCASTRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>13-03-2026 09:52:03</t>
+          <t>16-03-2026 18:52:17</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>13-03-2026 10:25:25</t>
+          <t>16-03-2026 18:58:03</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>12-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>13-03-2026 10:24:59</t>
+          <t>16-03-2026 18:57:08</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4482,7 +4498,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4492,19 +4508,19 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26140523149800002384</t>
+          <t>26140523231800002462</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>Noemi Carolina Meza Arreola</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4516,12 +4532,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>351443</t>
+          <t>349753</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>93607</t>
+          <t>91918</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4531,17 +4547,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEYRA AMERICA </t>
+          <t xml:space="preserve">NAOMI </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">CENICEROS </t>
+          <t xml:space="preserve">MUÑOZ </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANABRIA </t>
+          <t xml:space="preserve">VALDEZ </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4551,7 +4567,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6647479749</t>
+          <t>6643698462</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4562,17 +4578,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>04-11-2008</t>
+          <t>20-01-2009</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>KAYRACENICEROS3@GMAIL.COM</t>
+          <t>NAOMINUÑEVALDEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>17-03-2026 09:44:28</t>
+          <t>10-03-2026 07:21:20</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4597,12 +4613,12 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>17-03-2026 09:45:56</t>
+          <t>10-03-2026 07:23:21</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>09-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -4619,7 +4635,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26140523248680002488</t>
+          <t>26140523043580002234</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4631,24 +4647,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Saul  Ramirez Damian</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>351316</t>
+          <t>349833</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>93480</t>
+          <t>91998</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4658,17 +4674,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS OSVALDO </t>
+          <t xml:space="preserve">DANNA SOFIA </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t xml:space="preserve">VEGA </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">ESPINOZA </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4678,32 +4694,28 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6647805209</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>CJON DE LA ESTRELLA MZ212 LT101</t>
-        </is>
-      </c>
+          <t>6646132576</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>08-03-1988</t>
+          <t>16-11-2010</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>JESUSOSVALDOGUTIERREZCASTRO@GMAIL.COM</t>
+          <t>DANNA.VEG445@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>16-03-2026 18:52:17</t>
+          <t>10-03-2026 13:29:51</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4713,44 +4725,36 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>COBACH $399</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>16-03-2026 18:58:03</t>
+          <t>10-03-2026 13:32:15</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>16-03-2026 18:57:08</t>
-        </is>
-      </c>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4758,19 +4762,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26140523231800002462</t>
+          <t>26140523051390002248</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>399</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Noemi Carolina Meza Arreola</t>
+          <t>Saul  Ramirez Damian</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -5030,6 +5034,1443 @@
       <c r="AC35" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>352722</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>94886</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DARLEN</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>GONZALEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>GONZALEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6647510036</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Osamayor 5006</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>31-12-9999</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>cherrdarlingg@gmail.com</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>23-03-2026 10:58:03</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>23-03-2026 10:58:03</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26140523422330002685</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>350235</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>92399</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESMERALDA AZUCENA </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDINA </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>LUNA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6634111647</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>31-01-2005</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>MEDINALUNAESMERALDA9@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>11-03-2026 20:18:19</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>12-03-2026 19:48:08</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26140523135550002367</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>352946</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>95110</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAMIAN YAHIR </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAMOS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>VACA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6643506288</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>AV PADRE SALVATIERRA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>19-10-2002</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>RAMOSVACADAMIANYAHIR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>23-03-2026 19:20:58</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>23-03-2026 19:26:21</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>23-03-2026 19:25:09</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26140523444350002719</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>354403</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>96567</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUIS EDUARDO </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUZMAN </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ARREOLA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6643479705</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>03-06-2001</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>LUISGUZMAN12@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:06:28</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:08:44</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26140523645710002980</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>353039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>95203</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ALMA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AGUILAR CONDE</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>AGUILAR CONDE</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6641373693</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Calle guelatao 5341</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>31-12-9999</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>almaaguilar6922@gmail.com</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>24-03-2026 09:17:11</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>24-03-2026 09:17:12</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26140523461740002736</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>354422</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>96586</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ELIAS YERAY</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>EDMUNDS</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6646100974</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>18-10-2013</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>ELIAS.EDMUNDS@MENTORMEXICANO.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:27:52</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:30:34</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26140523647460002984</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>354127</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>96291</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JARITZI </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OLMAN </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUASTEGUI </t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>7421076526</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>03-12-2005</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>OLMANSUASTEGUI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>30-03-2026 10:10:01</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2 MESES X $ 1250</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>30-03-2026 10:12:05</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>29-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26140523622780002934</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Saul  Ramirez Damian</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>354183</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>96347</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STEFANI ALEJANDRA </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORALES </t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6647945045</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOMA BONITA </t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>04-08-2008</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>STEFANI040808@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>30-03-2026 12:33:58</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>30-03-2026 12:38:50</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>30-03-2026 12:37:35</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26140523626570002942</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>354380</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>96544</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BILEIDY</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALVARADO </t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>LOZANO</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6631607270</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>26-09-2010</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>BILY020007@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>30-03-2026 18:41:09</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>30-03-2026 18:42:40</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26140523643640002971</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>352658</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>94822</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMILA IVANOVA </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROMAN </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>MARENTES</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6648005581</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NUEVA AURORA </t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>10-10-2004</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>MARENTESIVANOVA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>23-03-2026 07:42:52</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>23-03-2026 07:47:23</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>23-03-2026 07:46:31</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26140523417380002671</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>353574</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>95738</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LOMA BONITA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DANIELA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ESPAÑA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ZUNO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6646400908</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>PRIV OMETEPE 1611</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>02-07-2000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>DANIELASPAIN1416@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>26-03-2026 15:23:25</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>26-03-2026 15:30:11</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>26-03-2026 15:28:56</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26140523536430002830</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
